--- a/Behind/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/Behind/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8118B325-606F-4E01-9F01-5B11115C6DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622E9A1F-B1A0-4911-A0E4-F0F574C1BCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2926,7 +2926,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3285,13 +3285,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3300,13 +3297,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3327,6 +3327,7 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3645,14 +3646,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP800"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.26953125" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" style="8" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="19.26953125" style="48" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.26953125" customWidth="1"/>
     <col min="8" max="8" width="16.7265625" customWidth="1"/>
@@ -3692,47 +3694,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="134" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="134" t="s">
+      <c r="A1" s="138" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="134" t="s">
+      <c r="C1" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="134" t="s">
+      <c r="D1" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="134" t="s">
+      <c r="E1" s="138" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="134" t="s">
+      <c r="F1" s="138" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="134" t="s">
+      <c r="G1" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="134" t="s">
+      <c r="H1" s="138" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J1" s="41"/>
-      <c r="K1" s="134" t="s">
+      <c r="K1" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="135" t="s">
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="137" t="s">
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="136" t="s">
         <v>10</v>
       </c>
       <c r="T1" s="139" t="s">
@@ -3747,61 +3749,61 @@
       <c r="Y1" s="139"/>
       <c r="Z1" s="139"/>
       <c r="AA1" s="139"/>
-      <c r="AB1" s="137" t="s">
+      <c r="AB1" s="136" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="137" t="s">
+      <c r="AC1" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="137" t="s">
+      <c r="AD1" s="136" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="137" t="s">
+      <c r="AE1" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="137" t="s">
+      <c r="AF1" s="136" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="137" t="s">
+      <c r="AG1" s="136" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="80">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="137" t="s">
+      <c r="AI1" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="137" t="s">
+      <c r="AJ1" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="137" t="s">
+      <c r="AK1" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="137" t="s">
+      <c r="AL1" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="137" t="s">
+      <c r="AM1" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="140" t="s">
+      <c r="AN1" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="140" t="s">
+      <c r="AO1" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="137" t="s">
+      <c r="AP1" s="136" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="134"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
+    <row r="2" spans="1:42" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="138"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -3832,7 +3834,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="138"/>
+      <c r="S2" s="137"/>
       <c r="T2" s="79" t="s">
         <v>73</v>
       </c>
@@ -3857,23 +3859,23 @@
       <c r="AA2" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="138"/>
+      <c r="AB2" s="137"/>
+      <c r="AC2" s="137"/>
+      <c r="AD2" s="137"/>
+      <c r="AE2" s="137"/>
+      <c r="AF2" s="137"/>
+      <c r="AG2" s="137"/>
       <c r="AH2" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="138"/>
-      <c r="AJ2" s="138"/>
-      <c r="AK2" s="138"/>
-      <c r="AL2" s="138"/>
-      <c r="AM2" s="138"/>
-      <c r="AN2" s="141"/>
-      <c r="AO2" s="141"/>
-      <c r="AP2" s="138"/>
+      <c r="AI2" s="137"/>
+      <c r="AJ2" s="137"/>
+      <c r="AK2" s="137"/>
+      <c r="AL2" s="137"/>
+      <c r="AM2" s="137"/>
+      <c r="AN2" s="135"/>
+      <c r="AO2" s="135"/>
+      <c r="AP2" s="137"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="81">
@@ -5284,7 +5286,7 @@
       </c>
       <c r="AP15" s="88"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="81">
         <v>46204</v>
       </c>
@@ -5382,7 +5384,7 @@
       </c>
       <c r="AP16" s="88"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="81">
         <v>46204</v>
       </c>
@@ -5480,7 +5482,7 @@
       </c>
       <c r="AP17" s="88"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="81">
         <v>46204</v>
       </c>
@@ -5582,7 +5584,7 @@
       </c>
       <c r="AP18" s="88"/>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="81">
         <v>46204</v>
       </c>
@@ -5684,7 +5686,7 @@
       </c>
       <c r="AP19" s="88"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="81">
         <v>46204</v>
       </c>
@@ -5790,7 +5792,7 @@
       </c>
       <c r="AP20" s="88"/>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="81">
         <v>46204</v>
       </c>
@@ -5890,7 +5892,7 @@
       </c>
       <c r="AP21" s="88"/>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="81">
         <v>46204</v>
       </c>
@@ -5992,7 +5994,7 @@
       </c>
       <c r="AP22" s="88"/>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="81">
         <v>46204</v>
       </c>
@@ -6090,7 +6092,7 @@
       </c>
       <c r="AP23" s="88"/>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="81">
         <v>46204</v>
       </c>
@@ -6192,7 +6194,7 @@
       </c>
       <c r="AP24" s="88"/>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="81">
         <v>46204</v>
       </c>
@@ -6290,7 +6292,7 @@
       </c>
       <c r="AP25" s="88"/>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="81">
         <v>46204</v>
       </c>
@@ -6390,7 +6392,7 @@
       </c>
       <c r="AP26" s="88"/>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="81">
         <v>46204</v>
       </c>
@@ -6488,7 +6490,7 @@
       </c>
       <c r="AP27" s="88"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="81">
         <v>46204</v>
       </c>
@@ -6590,7 +6592,7 @@
       </c>
       <c r="AP28" s="88"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="81">
         <v>46204</v>
       </c>
@@ -6690,7 +6692,7 @@
       </c>
       <c r="AP29" s="88"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="81">
         <v>46204</v>
       </c>
@@ -6788,7 +6790,7 @@
       </c>
       <c r="AP30" s="88"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="81">
         <v>46204</v>
       </c>
@@ -6886,7 +6888,7 @@
       </c>
       <c r="AP31" s="88"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="81">
         <v>46204</v>
       </c>
@@ -6984,7 +6986,7 @@
       </c>
       <c r="AP32" s="88"/>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="81">
         <v>46204</v>
       </c>
@@ -7092,7 +7094,7 @@
       </c>
       <c r="AP33" s="88"/>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="81">
         <v>46204</v>
       </c>
@@ -7190,7 +7192,7 @@
       </c>
       <c r="AP34" s="88"/>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="81">
         <v>46204</v>
       </c>
@@ -7288,7 +7290,7 @@
       </c>
       <c r="AP35" s="88"/>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="81">
         <v>46204</v>
       </c>
@@ -7392,7 +7394,7 @@
       </c>
       <c r="AP36" s="88"/>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="81">
         <v>46204</v>
       </c>
@@ -7494,7 +7496,7 @@
       </c>
       <c r="AP37" s="88"/>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="81">
         <v>46204</v>
       </c>
@@ -7596,7 +7598,7 @@
       </c>
       <c r="AP38" s="88"/>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="81">
         <v>46205</v>
       </c>
@@ -7704,7 +7706,7 @@
       </c>
       <c r="AP39" s="88"/>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="81">
         <v>46205</v>
       </c>
@@ -7808,7 +7810,7 @@
       </c>
       <c r="AP40" s="88"/>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="81">
         <v>46205</v>
       </c>
@@ -7910,7 +7912,7 @@
       </c>
       <c r="AP41" s="88"/>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="81">
         <v>46205</v>
       </c>
@@ -8012,7 +8014,7 @@
       </c>
       <c r="AP42" s="88"/>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="81">
         <v>46205</v>
       </c>
@@ -8113,7 +8115,7 @@
       </c>
       <c r="AP43" s="88"/>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="81">
         <v>46205</v>
       </c>
@@ -8221,7 +8223,7 @@
       </c>
       <c r="AP44" s="88"/>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="81">
         <v>46205</v>
       </c>
@@ -8323,7 +8325,7 @@
       </c>
       <c r="AP45" s="88"/>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="81">
         <v>46205</v>
       </c>
@@ -8425,7 +8427,7 @@
       </c>
       <c r="AP46" s="88"/>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="81">
         <v>46205</v>
       </c>
@@ -8525,7 +8527,7 @@
       </c>
       <c r="AP47" s="88"/>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="81">
         <v>46205</v>
       </c>
@@ -8627,7 +8629,7 @@
       </c>
       <c r="AP48" s="88"/>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="81">
         <v>46205</v>
       </c>
@@ -8725,7 +8727,7 @@
       </c>
       <c r="AP49" s="88"/>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="81">
         <v>46205</v>
       </c>
@@ -8827,7 +8829,7 @@
       </c>
       <c r="AP50" s="88"/>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="81">
         <v>46205</v>
       </c>
@@ -8935,7 +8937,7 @@
       </c>
       <c r="AP51" s="88"/>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="81">
         <v>46205</v>
       </c>
@@ -9039,7 +9041,7 @@
       </c>
       <c r="AP52" s="88"/>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="81">
         <v>46205</v>
       </c>
@@ -9145,7 +9147,7 @@
       </c>
       <c r="AP53" s="88"/>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="81">
         <v>46205</v>
       </c>
@@ -9253,7 +9255,7 @@
       </c>
       <c r="AP54" s="88"/>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="81">
         <v>46205</v>
       </c>
@@ -9361,7 +9363,7 @@
       </c>
       <c r="AP55" s="88"/>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="81">
         <v>46205</v>
       </c>
@@ -9469,7 +9471,7 @@
       </c>
       <c r="AP56" s="88"/>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="81">
         <v>46205</v>
       </c>
@@ -9567,7 +9569,7 @@
       </c>
       <c r="AP57" s="88"/>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="81">
         <v>46205</v>
       </c>
@@ -9667,7 +9669,7 @@
       </c>
       <c r="AP58" s="88"/>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="81">
         <v>46205</v>
       </c>
@@ -9765,7 +9767,7 @@
       </c>
       <c r="AP59" s="88"/>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="81">
         <v>46205</v>
       </c>
@@ -9863,7 +9865,7 @@
       </c>
       <c r="AP60" s="88"/>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="81">
         <v>46205</v>
       </c>
@@ -9961,7 +9963,7 @@
       </c>
       <c r="AP61" s="88"/>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="81">
         <v>46205</v>
       </c>
@@ -10059,7 +10061,7 @@
       </c>
       <c r="AP62" s="88"/>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="81">
         <v>46205</v>
       </c>
@@ -10157,7 +10159,7 @@
       </c>
       <c r="AP63" s="88"/>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="81">
         <v>46205</v>
       </c>
@@ -10255,7 +10257,7 @@
       </c>
       <c r="AP64" s="88"/>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="81">
         <v>46205</v>
       </c>
@@ -10353,7 +10355,7 @@
       </c>
       <c r="AP65" s="88"/>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="81">
         <v>46205</v>
       </c>
@@ -10453,7 +10455,7 @@
       </c>
       <c r="AP66" s="88"/>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="81">
         <v>46205</v>
       </c>
@@ -10555,7 +10557,7 @@
       </c>
       <c r="AP67" s="88"/>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="81">
         <v>46205</v>
       </c>
@@ -10657,7 +10659,7 @@
       </c>
       <c r="AP68" s="88"/>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="81">
         <v>46205</v>
       </c>
@@ -10765,7 +10767,7 @@
       </c>
       <c r="AP69" s="88"/>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="81">
         <v>46205</v>
       </c>
@@ -10871,7 +10873,7 @@
       </c>
       <c r="AP70" s="88"/>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="81">
         <v>46205</v>
       </c>
@@ -10969,7 +10971,7 @@
       </c>
       <c r="AP71" s="88"/>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="81">
         <v>46205</v>
       </c>
@@ -11067,7 +11069,7 @@
       </c>
       <c r="AP72" s="88"/>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="81">
         <v>46205</v>
       </c>
@@ -11897,7 +11899,7 @@
       </c>
       <c r="AP80" s="88"/>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="81">
         <v>46206</v>
       </c>
@@ -11999,7 +12001,7 @@
       </c>
       <c r="AP81" s="88"/>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="81">
         <v>46206</v>
       </c>
@@ -12097,7 +12099,7 @@
       </c>
       <c r="AP82" s="88"/>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="81">
         <v>46206</v>
       </c>
@@ -12199,7 +12201,7 @@
       </c>
       <c r="AP83" s="88"/>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="81">
         <v>46206</v>
       </c>
@@ -12299,7 +12301,7 @@
       </c>
       <c r="AP84" s="88"/>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="81">
         <v>46206</v>
       </c>
@@ -12401,7 +12403,7 @@
       </c>
       <c r="AP85" s="88"/>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="81">
         <v>46206</v>
       </c>
@@ -12503,7 +12505,7 @@
       </c>
       <c r="AP86" s="88"/>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="81">
         <v>46206</v>
       </c>
@@ -12603,7 +12605,7 @@
       </c>
       <c r="AP87" s="88"/>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="81">
         <v>46206</v>
       </c>
@@ -12705,7 +12707,7 @@
       </c>
       <c r="AP88" s="88"/>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="81">
         <v>46206</v>
       </c>
@@ -12807,7 +12809,7 @@
       </c>
       <c r="AP89" s="88"/>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="81">
         <v>46206</v>
       </c>
@@ -12905,7 +12907,7 @@
       </c>
       <c r="AP90" s="88"/>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="81">
         <v>46206</v>
       </c>
@@ -13007,7 +13009,7 @@
       </c>
       <c r="AP91" s="88"/>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="81">
         <v>46206</v>
       </c>
@@ -13109,7 +13111,7 @@
       </c>
       <c r="AP92" s="88"/>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="81">
         <v>46206</v>
       </c>
@@ -13213,7 +13215,7 @@
       </c>
       <c r="AP93" s="88"/>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="81">
         <v>46206</v>
       </c>
@@ -13311,7 +13313,7 @@
       </c>
       <c r="AP94" s="88"/>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="81">
         <v>46206</v>
       </c>
@@ -13419,7 +13421,7 @@
       </c>
       <c r="AP95" s="88"/>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="81">
         <v>46206</v>
       </c>
@@ -13523,7 +13525,7 @@
       </c>
       <c r="AP96" s="88"/>
     </row>
-    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="81">
         <v>46206</v>
       </c>
@@ -13627,7 +13629,7 @@
       </c>
       <c r="AP97" s="88"/>
     </row>
-    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="81">
         <v>46206</v>
       </c>
@@ -13725,7 +13727,7 @@
       </c>
       <c r="AP98" s="88"/>
     </row>
-    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="81">
         <v>46206</v>
       </c>
@@ -13825,7 +13827,7 @@
       </c>
       <c r="AP99" s="88"/>
     </row>
-    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="81">
         <v>46206</v>
       </c>
@@ -13923,7 +13925,7 @@
       </c>
       <c r="AP100" s="88"/>
     </row>
-    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="81">
         <v>46206</v>
       </c>
@@ -14021,7 +14023,7 @@
       </c>
       <c r="AP101" s="88"/>
     </row>
-    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="81">
         <v>46206</v>
       </c>
@@ -14123,7 +14125,7 @@
       </c>
       <c r="AP102" s="88"/>
     </row>
-    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="81">
         <v>46206</v>
       </c>
@@ -14231,7 +14233,7 @@
       </c>
       <c r="AP103" s="88"/>
     </row>
-    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="81">
         <v>46206</v>
       </c>
@@ -14333,7 +14335,7 @@
       </c>
       <c r="AP104" s="88"/>
     </row>
-    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="81">
         <v>46206</v>
       </c>
@@ -14431,7 +14433,7 @@
       </c>
       <c r="AP105" s="88"/>
     </row>
-    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="81">
         <v>46206</v>
       </c>
@@ -14529,7 +14531,7 @@
       </c>
       <c r="AP106" s="88"/>
     </row>
-    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="81">
         <v>46206</v>
       </c>
@@ -14631,7 +14633,7 @@
       </c>
       <c r="AP107" s="88"/>
     </row>
-    <row r="108" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="81">
         <v>46206</v>
       </c>
@@ -14733,7 +14735,7 @@
       </c>
       <c r="AP108" s="88"/>
     </row>
-    <row r="109" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="81">
         <v>46206</v>
       </c>
@@ -14835,7 +14837,7 @@
       </c>
       <c r="AP109" s="88"/>
     </row>
-    <row r="110" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="81">
         <v>46206</v>
       </c>
@@ -14937,7 +14939,7 @@
       </c>
       <c r="AP110" s="88"/>
     </row>
-    <row r="111" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="81">
         <v>46206</v>
       </c>
@@ -15035,7 +15037,7 @@
       </c>
       <c r="AP111" s="88"/>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="81">
         <v>46206</v>
       </c>
@@ -15139,7 +15141,7 @@
       </c>
       <c r="AP112" s="88"/>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="81">
         <v>46206</v>
       </c>
@@ -15241,7 +15243,7 @@
       </c>
       <c r="AP113" s="88"/>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="81">
         <v>46206</v>
       </c>
@@ -15341,7 +15343,7 @@
       </c>
       <c r="AP114" s="88"/>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="81">
         <v>46206</v>
       </c>
@@ -15443,7 +15445,7 @@
       </c>
       <c r="AP115" s="88"/>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="81">
         <v>46206</v>
       </c>
@@ -15547,7 +15549,7 @@
       </c>
       <c r="AP116" s="88"/>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="81">
         <v>46207</v>
       </c>
@@ -15627,7 +15629,7 @@
       <c r="AL117" s="102"/>
       <c r="AP117" s="105"/>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="81">
         <v>46207</v>
       </c>
@@ -15729,7 +15731,7 @@
       </c>
       <c r="AP118" s="88"/>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="81">
         <v>46207</v>
       </c>
@@ -15833,7 +15835,7 @@
       </c>
       <c r="AP119" s="88"/>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="81">
         <v>46207</v>
       </c>
@@ -15937,7 +15939,7 @@
       </c>
       <c r="AP120" s="88"/>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="81">
         <v>46207</v>
       </c>
@@ -16039,7 +16041,7 @@
       </c>
       <c r="AP121" s="88"/>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="81">
         <v>46207</v>
       </c>
@@ -16143,7 +16145,7 @@
       </c>
       <c r="AP122" s="88"/>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="81">
         <v>46207</v>
       </c>
@@ -16251,7 +16253,7 @@
       </c>
       <c r="AP123" s="88"/>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="81">
         <v>46207</v>
       </c>
@@ -16353,7 +16355,7 @@
       </c>
       <c r="AP124" s="88"/>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="81">
         <v>46207</v>
       </c>
@@ -16455,7 +16457,7 @@
       </c>
       <c r="AP125" s="88"/>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="81">
         <v>46207</v>
       </c>
@@ -16555,7 +16557,7 @@
       </c>
       <c r="AP126" s="88"/>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="81">
         <v>46207</v>
       </c>
@@ -16653,7 +16655,7 @@
       </c>
       <c r="AP127" s="88"/>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="81">
         <v>46207</v>
       </c>
@@ -16751,7 +16753,7 @@
       </c>
       <c r="AP128" s="88"/>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="81">
         <v>46207</v>
       </c>
@@ -16849,7 +16851,7 @@
       </c>
       <c r="AP129" s="88"/>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="81">
         <v>46207</v>
       </c>
@@ -16947,7 +16949,7 @@
       </c>
       <c r="AP130" s="88"/>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="81">
         <v>46207</v>
       </c>
@@ -17045,7 +17047,7 @@
       </c>
       <c r="AP131" s="88"/>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="81">
         <v>46207</v>
       </c>
@@ -17143,7 +17145,7 @@
       </c>
       <c r="AP132" s="88"/>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="81">
         <v>46207</v>
       </c>
@@ -17241,7 +17243,7 @@
       </c>
       <c r="AP133" s="88"/>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="81">
         <v>46207</v>
       </c>
@@ -17345,7 +17347,7 @@
       </c>
       <c r="AP134" s="88"/>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="81">
         <v>46207</v>
       </c>
@@ -17445,7 +17447,7 @@
       </c>
       <c r="AP135" s="88"/>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="81">
         <v>46207</v>
       </c>
@@ -17547,7 +17549,7 @@
       </c>
       <c r="AP136" s="88"/>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="81">
         <v>46207</v>
       </c>
@@ -17651,7 +17653,7 @@
       </c>
       <c r="AP137" s="88"/>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="81">
         <v>46207</v>
       </c>
@@ -17749,7 +17751,7 @@
       </c>
       <c r="AP138" s="88"/>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="81">
         <v>46207</v>
       </c>
@@ -17851,7 +17853,7 @@
       </c>
       <c r="AP139" s="88"/>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="81">
         <v>46207</v>
       </c>
@@ -17953,7 +17955,7 @@
       </c>
       <c r="AP140" s="88"/>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="81">
         <v>46207</v>
       </c>
@@ -18057,7 +18059,7 @@
       </c>
       <c r="AP141" s="88"/>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="81">
         <v>46207</v>
       </c>
@@ -18155,7 +18157,7 @@
       </c>
       <c r="AP142" s="88"/>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="81">
         <v>46207</v>
       </c>
@@ -18257,7 +18259,7 @@
       </c>
       <c r="AP143" s="88"/>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="81">
         <v>46209</v>
       </c>
@@ -18359,7 +18361,7 @@
       </c>
       <c r="AP144" s="88"/>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="81">
         <v>46209</v>
       </c>
@@ -18461,7 +18463,7 @@
       </c>
       <c r="AP145" s="88"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="81">
         <v>46209</v>
       </c>
@@ -18567,7 +18569,7 @@
       </c>
       <c r="AP146" s="88"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="81">
         <v>46209</v>
       </c>
@@ -18665,7 +18667,7 @@
       </c>
       <c r="AP147" s="88"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="81">
         <v>46209</v>
       </c>
@@ -18765,7 +18767,7 @@
       </c>
       <c r="AP148" s="88"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="81">
         <v>46209</v>
       </c>
@@ -18867,7 +18869,7 @@
       </c>
       <c r="AP149" s="88"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="81">
         <v>46209</v>
       </c>
@@ -18965,7 +18967,7 @@
       </c>
       <c r="AP150" s="88"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="81">
         <v>46209</v>
       </c>
@@ -19067,7 +19069,7 @@
       </c>
       <c r="AP151" s="88"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="81">
         <v>46209</v>
       </c>
@@ -19169,7 +19171,7 @@
       </c>
       <c r="AP152" s="88"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="81">
         <v>46209</v>
       </c>
@@ -19271,7 +19273,7 @@
       </c>
       <c r="AP153" s="88"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="81">
         <v>46209</v>
       </c>
@@ -19377,7 +19379,7 @@
       </c>
       <c r="AP154" s="88"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="81">
         <v>46209</v>
       </c>
@@ -19485,7 +19487,7 @@
       </c>
       <c r="AP155" s="88"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="81">
         <v>46209</v>
       </c>
@@ -19587,7 +19589,7 @@
       </c>
       <c r="AP156" s="88"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="81">
         <v>46209</v>
       </c>
@@ -19693,7 +19695,7 @@
       </c>
       <c r="AP157" s="88"/>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="81">
         <v>46209</v>
       </c>
@@ -19791,7 +19793,7 @@
       </c>
       <c r="AP158" s="88"/>
     </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="81">
         <v>46209</v>
       </c>
@@ -19889,7 +19891,7 @@
       </c>
       <c r="AP159" s="88"/>
     </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="81">
         <v>46209</v>
       </c>
@@ -19987,7 +19989,7 @@
       </c>
       <c r="AP160" s="88"/>
     </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="81">
         <v>46209</v>
       </c>
@@ -20091,7 +20093,7 @@
       </c>
       <c r="AP161" s="88"/>
     </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="81">
         <v>46209</v>
       </c>
@@ -20189,7 +20191,7 @@
       </c>
       <c r="AP162" s="88"/>
     </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="81">
         <v>46209</v>
       </c>
@@ -20287,7 +20289,7 @@
       </c>
       <c r="AP163" s="88"/>
     </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="81">
         <v>46209</v>
       </c>
@@ -20385,7 +20387,7 @@
       </c>
       <c r="AP164" s="88"/>
     </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="81">
         <v>46209</v>
       </c>
@@ -20483,7 +20485,7 @@
       </c>
       <c r="AP165" s="88"/>
     </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="81">
         <v>46209</v>
       </c>
@@ -20581,7 +20583,7 @@
       </c>
       <c r="AP166" s="88"/>
     </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="81">
         <v>46209</v>
       </c>
@@ -20685,7 +20687,7 @@
       </c>
       <c r="AP167" s="88"/>
     </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="81">
         <v>46210</v>
       </c>
@@ -20785,7 +20787,7 @@
       </c>
       <c r="AP168" s="88"/>
     </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="81">
         <v>46210</v>
       </c>
@@ -20885,7 +20887,7 @@
       </c>
       <c r="AP169" s="88"/>
     </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="81">
         <v>46210</v>
       </c>
@@ -20983,7 +20985,7 @@
       </c>
       <c r="AP170" s="88"/>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="81">
         <v>46210</v>
       </c>
@@ -21091,7 +21093,7 @@
       </c>
       <c r="AP171" s="88"/>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="81">
         <v>46210</v>
       </c>
@@ -21189,7 +21191,7 @@
       </c>
       <c r="AP172" s="88"/>
     </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="81">
         <v>46210</v>
       </c>
@@ -21291,7 +21293,7 @@
       </c>
       <c r="AP173" s="88"/>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="81">
         <v>46210</v>
       </c>
@@ -21393,7 +21395,7 @@
       </c>
       <c r="AP174" s="88"/>
     </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="81">
         <v>46210</v>
       </c>
@@ -21495,7 +21497,7 @@
       </c>
       <c r="AP175" s="88"/>
     </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="81">
         <v>46210</v>
       </c>
@@ -21597,7 +21599,7 @@
       </c>
       <c r="AP176" s="88"/>
     </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="81">
         <v>46210</v>
       </c>
@@ -21697,7 +21699,7 @@
       </c>
       <c r="AP177" s="88"/>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="81">
         <v>46210</v>
       </c>
@@ -21797,7 +21799,7 @@
       </c>
       <c r="AP178" s="88"/>
     </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="81">
         <v>46210</v>
       </c>
@@ -21895,7 +21897,7 @@
       </c>
       <c r="AP179" s="88"/>
     </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="81">
         <v>46210</v>
       </c>
@@ -21997,7 +21999,7 @@
       </c>
       <c r="AP180" s="88"/>
     </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="81">
         <v>46210</v>
       </c>
@@ -22101,7 +22103,7 @@
       </c>
       <c r="AP181" s="88"/>
     </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="81">
         <v>46210</v>
       </c>
@@ -22207,7 +22209,7 @@
       </c>
       <c r="AP182" s="88"/>
     </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="81">
         <v>46210</v>
       </c>
@@ -22309,7 +22311,7 @@
       </c>
       <c r="AP183" s="88"/>
     </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="81">
         <v>46210</v>
       </c>
@@ -22411,7 +22413,7 @@
       </c>
       <c r="AP184" s="88"/>
     </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="81">
         <v>46210</v>
       </c>
@@ -22513,7 +22515,7 @@
       </c>
       <c r="AP185" s="88"/>
     </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="81">
         <v>46210</v>
       </c>
@@ -22611,7 +22613,7 @@
       </c>
       <c r="AP186" s="88"/>
     </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="81">
         <v>46210</v>
       </c>
@@ -22709,7 +22711,7 @@
       </c>
       <c r="AP187" s="88"/>
     </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="81">
         <v>46210</v>
       </c>
@@ -22807,7 +22809,7 @@
       </c>
       <c r="AP188" s="88"/>
     </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="81">
         <v>46210</v>
       </c>
@@ -22905,7 +22907,7 @@
       </c>
       <c r="AP189" s="88"/>
     </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="81">
         <v>46210</v>
       </c>
@@ -23009,7 +23011,7 @@
       </c>
       <c r="AP190" s="88"/>
     </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="81">
         <v>46210</v>
       </c>
@@ -23107,7 +23109,7 @@
       </c>
       <c r="AP191" s="88"/>
     </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="81">
         <v>46210</v>
       </c>
@@ -23205,7 +23207,7 @@
       </c>
       <c r="AP192" s="88"/>
     </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="81">
         <v>46210</v>
       </c>
@@ -23303,7 +23305,7 @@
       </c>
       <c r="AP193" s="88"/>
     </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="81">
         <v>46210</v>
       </c>
@@ -23401,7 +23403,7 @@
       </c>
       <c r="AP194" s="88"/>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="81">
         <v>46210</v>
       </c>
@@ -23499,7 +23501,7 @@
       </c>
       <c r="AP195" s="88"/>
     </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="81">
         <v>46210</v>
       </c>
@@ -23597,7 +23599,7 @@
       </c>
       <c r="AP196" s="88"/>
     </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="81">
         <v>46210</v>
       </c>
@@ -23699,7 +23701,7 @@
       </c>
       <c r="AP197" s="88"/>
     </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="81">
         <v>46210</v>
       </c>
@@ -23797,7 +23799,7 @@
       </c>
       <c r="AP198" s="88"/>
     </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="81">
         <v>46210</v>
       </c>
@@ -23895,7 +23897,7 @@
       </c>
       <c r="AP199" s="88"/>
     </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="81">
         <v>46210</v>
       </c>
@@ -23993,7 +23995,7 @@
       </c>
       <c r="AP200" s="88"/>
     </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="81">
         <v>46210</v>
       </c>
@@ -24091,7 +24093,7 @@
       </c>
       <c r="AP201" s="88"/>
     </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="81">
         <v>46211</v>
       </c>
@@ -24189,7 +24191,7 @@
       </c>
       <c r="AP202" s="88"/>
     </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="81">
         <v>46211</v>
       </c>
@@ -24287,7 +24289,7 @@
       </c>
       <c r="AP203" s="88"/>
     </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="81">
         <v>46211</v>
       </c>
@@ -24387,7 +24389,7 @@
       </c>
       <c r="AP204" s="88"/>
     </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="81">
         <v>46211</v>
       </c>
@@ -24489,7 +24491,7 @@
       </c>
       <c r="AP205" s="88"/>
     </row>
-    <row r="206" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="81">
         <v>46211</v>
       </c>
@@ -24591,7 +24593,7 @@
       </c>
       <c r="AP206" s="88"/>
     </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="81">
         <v>46211</v>
       </c>
@@ -24695,7 +24697,7 @@
       </c>
       <c r="AP207" s="88"/>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="81">
         <v>46211</v>
       </c>
@@ -24793,7 +24795,7 @@
       </c>
       <c r="AP208" s="88"/>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="81">
         <v>46211</v>
       </c>
@@ -24891,7 +24893,7 @@
       </c>
       <c r="AP209" s="88"/>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="81">
         <v>46211</v>
       </c>
@@ -24989,7 +24991,7 @@
       </c>
       <c r="AP210" s="88"/>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="81">
         <v>46211</v>
       </c>
@@ -25087,7 +25089,7 @@
       </c>
       <c r="AP211" s="88"/>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="81">
         <v>46211</v>
       </c>
@@ -25189,7 +25191,7 @@
       </c>
       <c r="AP212" s="88"/>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="81">
         <v>46211</v>
       </c>
@@ -25293,7 +25295,7 @@
       </c>
       <c r="AP213" s="88"/>
     </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="81">
         <v>46211</v>
       </c>
@@ -25397,7 +25399,7 @@
       </c>
       <c r="AP214" s="88"/>
     </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="81">
         <v>46211</v>
       </c>
@@ -25495,7 +25497,7 @@
       </c>
       <c r="AP215" s="88"/>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="81">
         <v>46211</v>
       </c>
@@ -25593,7 +25595,7 @@
       </c>
       <c r="AP216" s="88"/>
     </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="81">
         <v>46211</v>
       </c>
@@ -25695,7 +25697,7 @@
       </c>
       <c r="AP217" s="88"/>
     </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="81">
         <v>46211</v>
       </c>
@@ -25793,7 +25795,7 @@
       </c>
       <c r="AP218" s="88"/>
     </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="81">
         <v>46211</v>
       </c>
@@ -25895,7 +25897,7 @@
       </c>
       <c r="AP219" s="88"/>
     </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="81">
         <v>46211</v>
       </c>
@@ -25999,7 +26001,7 @@
       </c>
       <c r="AP220" s="88"/>
     </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="81">
         <v>46211</v>
       </c>
@@ -26097,7 +26099,7 @@
       </c>
       <c r="AP221" s="88"/>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="81">
         <v>46211</v>
       </c>
@@ -26195,7 +26197,7 @@
       </c>
       <c r="AP222" s="88"/>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="81">
         <v>46211</v>
       </c>
@@ -26293,7 +26295,7 @@
       </c>
       <c r="AP223" s="88"/>
     </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="81">
         <v>46211</v>
       </c>
@@ -26391,7 +26393,7 @@
       </c>
       <c r="AP224" s="88"/>
     </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="81">
         <v>46211</v>
       </c>
@@ -26489,7 +26491,7 @@
       </c>
       <c r="AP225" s="88"/>
     </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="81">
         <v>46211</v>
       </c>
@@ -26587,7 +26589,7 @@
       </c>
       <c r="AP226" s="88"/>
     </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="81">
         <v>46211</v>
       </c>
@@ -26691,7 +26693,7 @@
       </c>
       <c r="AP227" s="88"/>
     </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="81">
         <v>46211</v>
       </c>
@@ -27099,7 +27101,7 @@
       </c>
       <c r="AP231" s="88"/>
     </row>
-    <row r="232" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="81">
         <v>46212</v>
       </c>
@@ -27197,7 +27199,7 @@
       </c>
       <c r="AP232" s="88"/>
     </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="81">
         <v>46212</v>
       </c>
@@ -27299,7 +27301,7 @@
       </c>
       <c r="AP233" s="88"/>
     </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="81">
         <v>46212</v>
       </c>
@@ -27399,7 +27401,7 @@
       </c>
       <c r="AP234" s="88"/>
     </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="81">
         <v>46212</v>
       </c>
@@ -27507,7 +27509,7 @@
       </c>
       <c r="AP235" s="88"/>
     </row>
-    <row r="236" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="81">
         <v>46212</v>
       </c>
@@ -27611,7 +27613,7 @@
       </c>
       <c r="AP236" s="88"/>
     </row>
-    <row r="237" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="81">
         <v>46212</v>
       </c>
@@ -27711,7 +27713,7 @@
       </c>
       <c r="AP237" s="88"/>
     </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="81">
         <v>46212</v>
       </c>
@@ -27813,7 +27815,7 @@
       </c>
       <c r="AP238" s="88"/>
     </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="81">
         <v>46212</v>
       </c>
@@ -27915,7 +27917,7 @@
       </c>
       <c r="AP239" s="88"/>
     </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="81">
         <v>46212</v>
       </c>
@@ -28015,7 +28017,7 @@
       </c>
       <c r="AP240" s="88"/>
     </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="81">
         <v>46212</v>
       </c>
@@ -28117,7 +28119,7 @@
       </c>
       <c r="AP241" s="88"/>
     </row>
-    <row r="242" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="81">
         <v>46212</v>
       </c>
@@ -28215,7 +28217,7 @@
       </c>
       <c r="AP242" s="88"/>
     </row>
-    <row r="243" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="81">
         <v>46212</v>
       </c>
@@ -28317,7 +28319,7 @@
       </c>
       <c r="AP243" s="88"/>
     </row>
-    <row r="244" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="81">
         <v>46212</v>
       </c>
@@ -28417,7 +28419,7 @@
       </c>
       <c r="AP244" s="88"/>
     </row>
-    <row r="245" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="81">
         <v>46212</v>
       </c>
@@ -28515,7 +28517,7 @@
       </c>
       <c r="AP245" s="88"/>
     </row>
-    <row r="246" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="81">
         <v>46212</v>
       </c>
@@ -28617,7 +28619,7 @@
       </c>
       <c r="AP246" s="88"/>
     </row>
-    <row r="247" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="81">
         <v>46212</v>
       </c>
@@ -28719,7 +28721,7 @@
       </c>
       <c r="AP247" s="88"/>
     </row>
-    <row r="248" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="81">
         <v>46212</v>
       </c>
@@ -28821,7 +28823,7 @@
       </c>
       <c r="AP248" s="88"/>
     </row>
-    <row r="249" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="81">
         <v>46212</v>
       </c>
@@ -28923,7 +28925,7 @@
       </c>
       <c r="AP249" s="88"/>
     </row>
-    <row r="250" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="81">
         <v>46212</v>
       </c>
@@ -29023,7 +29025,7 @@
       </c>
       <c r="AP250" s="88"/>
     </row>
-    <row r="251" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="81">
         <v>46212</v>
       </c>
@@ -29123,7 +29125,7 @@
       </c>
       <c r="AP251" s="88"/>
     </row>
-    <row r="252" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="81">
         <v>46212</v>
       </c>
@@ -29225,7 +29227,7 @@
       </c>
       <c r="AP252" s="88"/>
     </row>
-    <row r="253" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="81">
         <v>46212</v>
       </c>
@@ -29329,7 +29331,7 @@
       </c>
       <c r="AP253" s="88"/>
     </row>
-    <row r="254" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="81">
         <v>46212</v>
       </c>
@@ -29431,7 +29433,7 @@
       </c>
       <c r="AP254" s="88"/>
     </row>
-    <row r="255" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="81">
         <v>46212</v>
       </c>
@@ -30157,7 +30159,7 @@
       </c>
       <c r="AP261" s="88"/>
     </row>
-    <row r="262" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="81">
         <v>46213</v>
       </c>
@@ -30259,7 +30261,7 @@
       </c>
       <c r="AP262" s="88"/>
     </row>
-    <row r="263" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="81">
         <v>46213</v>
       </c>
@@ -30357,7 +30359,7 @@
       </c>
       <c r="AP263" s="88"/>
     </row>
-    <row r="264" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="81">
         <v>46213</v>
       </c>
@@ -30457,7 +30459,7 @@
       </c>
       <c r="AP264" s="88"/>
     </row>
-    <row r="265" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="81">
         <v>46213</v>
       </c>
@@ -30557,7 +30559,7 @@
       </c>
       <c r="AP265" s="88"/>
     </row>
-    <row r="266" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="81">
         <v>46213</v>
       </c>
@@ -30659,7 +30661,7 @@
       </c>
       <c r="AP266" s="88"/>
     </row>
-    <row r="267" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="81">
         <v>46213</v>
       </c>
@@ -30767,7 +30769,7 @@
       </c>
       <c r="AP267" s="88"/>
     </row>
-    <row r="268" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="81">
         <v>46213</v>
       </c>
@@ -30869,7 +30871,7 @@
       </c>
       <c r="AP268" s="88"/>
     </row>
-    <row r="269" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="81">
         <v>46213</v>
       </c>
@@ -30971,7 +30973,7 @@
       </c>
       <c r="AP269" s="88"/>
     </row>
-    <row r="270" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="81">
         <v>46213</v>
       </c>
@@ -31069,7 +31071,7 @@
       </c>
       <c r="AP270" s="88"/>
     </row>
-    <row r="271" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="81">
         <v>46213</v>
       </c>
@@ -31167,7 +31169,7 @@
       </c>
       <c r="AP271" s="88"/>
     </row>
-    <row r="272" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="81">
         <v>46213</v>
       </c>
@@ -31265,7 +31267,7 @@
       </c>
       <c r="AP272" s="88"/>
     </row>
-    <row r="273" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="81">
         <v>46213</v>
       </c>
@@ -31363,7 +31365,7 @@
       </c>
       <c r="AP273" s="88"/>
     </row>
-    <row r="274" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="81">
         <v>46213</v>
       </c>
@@ -31461,7 +31463,7 @@
       </c>
       <c r="AP274" s="88"/>
     </row>
-    <row r="275" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="81">
         <v>46213</v>
       </c>
@@ -31569,7 +31571,7 @@
       </c>
       <c r="AP275" s="88"/>
     </row>
-    <row r="276" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="81">
         <v>46213</v>
       </c>
@@ -31667,7 +31669,7 @@
       </c>
       <c r="AP276" s="88"/>
     </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="81">
         <v>46213</v>
       </c>
@@ -31765,7 +31767,7 @@
       </c>
       <c r="AP277" s="88"/>
     </row>
-    <row r="278" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="81">
         <v>46213</v>
       </c>
@@ -31863,7 +31865,7 @@
       </c>
       <c r="AP278" s="88"/>
     </row>
-    <row r="279" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="81">
         <v>46214</v>
       </c>
@@ -31965,7 +31967,7 @@
       </c>
       <c r="AP279" s="88"/>
     </row>
-    <row r="280" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="81">
         <v>46214</v>
       </c>
@@ -32071,7 +32073,7 @@
       </c>
       <c r="AP280" s="88"/>
     </row>
-    <row r="281" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="81">
         <v>46214</v>
       </c>
@@ -32173,7 +32175,7 @@
       </c>
       <c r="AP281" s="88"/>
     </row>
-    <row r="282" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="81">
         <v>46214</v>
       </c>
@@ -32271,7 +32273,7 @@
       </c>
       <c r="AP282" s="88"/>
     </row>
-    <row r="283" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="81">
         <v>46214</v>
       </c>
@@ -32379,7 +32381,7 @@
       </c>
       <c r="AP283" s="88"/>
     </row>
-    <row r="284" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="81">
         <v>46214</v>
       </c>
@@ -32479,7 +32481,7 @@
       </c>
       <c r="AP284" s="88"/>
     </row>
-    <row r="285" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="81">
         <v>46214</v>
       </c>
@@ -32579,7 +32581,7 @@
       </c>
       <c r="AP285" s="88"/>
     </row>
-    <row r="286" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="81">
         <v>46214</v>
       </c>
@@ -32681,7 +32683,7 @@
       </c>
       <c r="AP286" s="88"/>
     </row>
-    <row r="287" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="81">
         <v>46214</v>
       </c>
@@ -32789,7 +32791,7 @@
       </c>
       <c r="AP287" s="88"/>
     </row>
-    <row r="288" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="81">
         <v>46214</v>
       </c>
@@ -32897,7 +32899,7 @@
       </c>
       <c r="AP288" s="88"/>
     </row>
-    <row r="289" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="81">
         <v>46214</v>
       </c>
@@ -32999,7 +33001,7 @@
       </c>
       <c r="AP289" s="88"/>
     </row>
-    <row r="290" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="81">
         <v>46214</v>
       </c>
@@ -33101,7 +33103,7 @@
       </c>
       <c r="AP290" s="88"/>
     </row>
-    <row r="291" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="81">
         <v>46214</v>
       </c>
@@ -33203,7 +33205,7 @@
       </c>
       <c r="AP291" s="88"/>
     </row>
-    <row r="292" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="81">
         <v>46214</v>
       </c>
@@ -33305,7 +33307,7 @@
       </c>
       <c r="AP292" s="88"/>
     </row>
-    <row r="293" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="81">
         <v>46214</v>
       </c>
@@ -33405,7 +33407,7 @@
       </c>
       <c r="AP293" s="88"/>
     </row>
-    <row r="294" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="81">
         <v>46214</v>
       </c>
@@ -33511,7 +33513,7 @@
       </c>
       <c r="AP294" s="88"/>
     </row>
-    <row r="295" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="81">
         <v>46214</v>
       </c>
@@ -33611,7 +33613,7 @@
       </c>
       <c r="AP295" s="88"/>
     </row>
-    <row r="296" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="81">
         <v>46214</v>
       </c>
@@ -33711,7 +33713,7 @@
       </c>
       <c r="AP296" s="88"/>
     </row>
-    <row r="297" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="81">
         <v>46214</v>
       </c>
@@ -33815,7 +33817,7 @@
       </c>
       <c r="AP297" s="88"/>
     </row>
-    <row r="298" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="81">
         <v>46214</v>
       </c>
@@ -33913,7 +33915,7 @@
       </c>
       <c r="AP298" s="88"/>
     </row>
-    <row r="299" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="81">
         <v>46214</v>
       </c>
@@ -34015,7 +34017,7 @@
       </c>
       <c r="AP299" s="88"/>
     </row>
-    <row r="300" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="81">
         <v>46214</v>
       </c>
@@ -34123,7 +34125,7 @@
       </c>
       <c r="AP300" s="88"/>
     </row>
-    <row r="301" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="81">
         <v>46214</v>
       </c>
@@ -34225,7 +34227,7 @@
       </c>
       <c r="AP301" s="88"/>
     </row>
-    <row r="302" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="81">
         <v>46214</v>
       </c>
@@ -34325,7 +34327,7 @@
       </c>
       <c r="AP302" s="88"/>
     </row>
-    <row r="303" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="81">
         <v>46214</v>
       </c>
@@ -34423,7 +34425,7 @@
       </c>
       <c r="AP303" s="88"/>
     </row>
-    <row r="304" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="81">
         <v>46214</v>
       </c>
@@ -34521,7 +34523,7 @@
       </c>
       <c r="AP304" s="88"/>
     </row>
-    <row r="305" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="81">
         <v>46214</v>
       </c>
@@ -34619,7 +34621,7 @@
       </c>
       <c r="AP305" s="88"/>
     </row>
-    <row r="306" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="81">
         <v>46214</v>
       </c>
@@ -34717,7 +34719,7 @@
       </c>
       <c r="AP306" s="88"/>
     </row>
-    <row r="307" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="81">
         <v>46214</v>
       </c>
@@ -34815,7 +34817,7 @@
       </c>
       <c r="AP307" s="88"/>
     </row>
-    <row r="308" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="81">
         <v>46214</v>
       </c>
@@ -34913,7 +34915,7 @@
       </c>
       <c r="AP308" s="88"/>
     </row>
-    <row r="309" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="81">
         <v>46214</v>
       </c>
@@ -35427,7 +35429,7 @@
       </c>
       <c r="AP313" s="88"/>
     </row>
-    <row r="314" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="81">
         <v>46214</v>
       </c>
@@ -35525,7 +35527,7 @@
       </c>
       <c r="AP314" s="88"/>
     </row>
-    <row r="315" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="81">
         <v>46205</v>
       </c>
@@ -35731,7 +35733,7 @@
       </c>
       <c r="AP316" s="7"/>
     </row>
-    <row r="317" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="81">
         <v>46216</v>
       </c>
@@ -35827,7 +35829,7 @@
       </c>
       <c r="AP317" s="7"/>
     </row>
-    <row r="318" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="81">
         <v>46216</v>
       </c>
@@ -35917,7 +35919,7 @@
       </c>
       <c r="AP318" s="7"/>
     </row>
-    <row r="319" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="81">
         <v>46216</v>
       </c>
@@ -36011,7 +36013,7 @@
       </c>
       <c r="AP319" s="7"/>
     </row>
-    <row r="320" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="81">
         <v>46216</v>
       </c>
@@ -36109,7 +36111,7 @@
       </c>
       <c r="AP320" s="7"/>
     </row>
-    <row r="321" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="81">
         <v>46216</v>
       </c>
@@ -36199,7 +36201,7 @@
       </c>
       <c r="AP321" s="7"/>
     </row>
-    <row r="322" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="81">
         <v>46216</v>
       </c>
@@ -36291,7 +36293,7 @@
       </c>
       <c r="AP322" s="7"/>
     </row>
-    <row r="323" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="81">
         <v>46216</v>
       </c>
@@ -36381,7 +36383,7 @@
       </c>
       <c r="AP323" s="7"/>
     </row>
-    <row r="324" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="81">
         <v>46216</v>
       </c>
@@ -36477,7 +36479,7 @@
       </c>
       <c r="AP324" s="7"/>
     </row>
-    <row r="325" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="81">
         <v>46216</v>
       </c>
@@ -36573,7 +36575,7 @@
       </c>
       <c r="AP325" s="7"/>
     </row>
-    <row r="326" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="81">
         <v>46216</v>
       </c>
@@ -36663,7 +36665,7 @@
       </c>
       <c r="AP326" s="7"/>
     </row>
-    <row r="327" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="81">
         <v>46216</v>
       </c>
@@ -36753,7 +36755,7 @@
       </c>
       <c r="AP327" s="7"/>
     </row>
-    <row r="328" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="81">
         <v>46216</v>
       </c>
@@ -36851,7 +36853,7 @@
       </c>
       <c r="AP328" s="7"/>
     </row>
-    <row r="329" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="81">
         <v>46216</v>
       </c>
@@ -36941,7 +36943,7 @@
       </c>
       <c r="AP329" s="7"/>
     </row>
-    <row r="330" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="81">
         <v>46216</v>
       </c>
@@ -37041,7 +37043,7 @@
       </c>
       <c r="AP330" s="7"/>
     </row>
-    <row r="331" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="81">
         <v>46216</v>
       </c>
@@ -37141,7 +37143,7 @@
       </c>
       <c r="AP331" s="7"/>
     </row>
-    <row r="332" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="81">
         <v>46216</v>
       </c>
@@ -37231,7 +37233,7 @@
       </c>
       <c r="AP332" s="7"/>
     </row>
-    <row r="333" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="81">
         <v>46216</v>
       </c>
@@ -37995,7 +37997,7 @@
       </c>
       <c r="AP340" s="7"/>
     </row>
-    <row r="341" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="81">
         <v>46217</v>
       </c>
@@ -38087,7 +38089,7 @@
       </c>
       <c r="AP341" s="7"/>
     </row>
-    <row r="342" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="81">
         <v>46217</v>
       </c>
@@ -38183,7 +38185,7 @@
       </c>
       <c r="AP342" s="7"/>
     </row>
-    <row r="343" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="81">
         <v>46217</v>
       </c>
@@ -38273,7 +38275,7 @@
       </c>
       <c r="AP343" s="7"/>
     </row>
-    <row r="344" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="81">
         <v>46217</v>
       </c>
@@ -38365,7 +38367,7 @@
       </c>
       <c r="AP344" s="7"/>
     </row>
-    <row r="345" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="81">
         <v>46217</v>
       </c>
@@ -38455,7 +38457,7 @@
       </c>
       <c r="AP345" s="7"/>
     </row>
-    <row r="346" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="81">
         <v>46217</v>
       </c>
@@ -38551,7 +38553,7 @@
       </c>
       <c r="AP346" s="7"/>
     </row>
-    <row r="347" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="81">
         <v>46217</v>
       </c>
@@ -38645,7 +38647,7 @@
       </c>
       <c r="AP347" s="7"/>
     </row>
-    <row r="348" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="81">
         <v>46217</v>
       </c>
@@ -38739,7 +38741,7 @@
       </c>
       <c r="AP348" s="7"/>
     </row>
-    <row r="349" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="81">
         <v>46217</v>
       </c>
@@ -38829,7 +38831,7 @@
       </c>
       <c r="AP349" s="7"/>
     </row>
-    <row r="350" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="81">
         <v>46217</v>
       </c>
@@ -38921,7 +38923,7 @@
       </c>
       <c r="AP350" s="7"/>
     </row>
-    <row r="351" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="81">
         <v>46217</v>
       </c>
@@ -39015,7 +39017,7 @@
       </c>
       <c r="AP351" s="7"/>
     </row>
-    <row r="352" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="81">
         <v>46217</v>
       </c>
@@ -39107,7 +39109,7 @@
       </c>
       <c r="AP352" s="7"/>
     </row>
-    <row r="353" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="81">
         <v>46217</v>
       </c>
@@ -39197,7 +39199,7 @@
       </c>
       <c r="AP353" s="7"/>
     </row>
-    <row r="354" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="81">
         <v>46217</v>
       </c>
@@ -39291,7 +39293,7 @@
       </c>
       <c r="AP354" s="7"/>
     </row>
-    <row r="355" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="81">
         <v>46217</v>
       </c>
@@ -39385,7 +39387,7 @@
       </c>
       <c r="AP355" s="7"/>
     </row>
-    <row r="356" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="81">
         <v>46217</v>
       </c>
@@ -39477,7 +39479,7 @@
       </c>
       <c r="AP356" s="7"/>
     </row>
-    <row r="357" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="81">
         <v>46217</v>
       </c>
@@ -39567,7 +39569,7 @@
       </c>
       <c r="AP357" s="7"/>
     </row>
-    <row r="358" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="81">
         <v>46217</v>
       </c>
@@ -39657,7 +39659,7 @@
       </c>
       <c r="AP358" s="7"/>
     </row>
-    <row r="359" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="81">
         <v>46217</v>
       </c>
@@ -39747,7 +39749,7 @@
       </c>
       <c r="AP359" s="7"/>
     </row>
-    <row r="360" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="81">
         <v>46217</v>
       </c>
@@ -39837,7 +39839,7 @@
       </c>
       <c r="AP360" s="7"/>
     </row>
-    <row r="361" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="81">
         <v>46217</v>
       </c>
@@ -39927,7 +39929,7 @@
       </c>
       <c r="AP361" s="7"/>
     </row>
-    <row r="362" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="81">
         <v>46217</v>
       </c>
@@ -40017,7 +40019,7 @@
       </c>
       <c r="AP362" s="7"/>
     </row>
-    <row r="363" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="81">
         <v>46217</v>
       </c>
@@ -40109,7 +40111,7 @@
       </c>
       <c r="AP363" s="7"/>
     </row>
-    <row r="364" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="81">
         <v>46217</v>
       </c>
@@ -40199,7 +40201,7 @@
       </c>
       <c r="AP364" s="7"/>
     </row>
-    <row r="365" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="81">
         <v>46217</v>
       </c>
@@ -40293,7 +40295,7 @@
       </c>
       <c r="AP365" s="7"/>
     </row>
-    <row r="366" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="81">
         <v>46217</v>
       </c>
@@ -40387,7 +40389,7 @@
       </c>
       <c r="AP366" s="7"/>
     </row>
-    <row r="367" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="81">
         <v>46217</v>
       </c>
@@ -40477,7 +40479,7 @@
       </c>
       <c r="AP367" s="7"/>
     </row>
-    <row r="368" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="81">
         <v>46217</v>
       </c>
@@ -40567,7 +40569,7 @@
       </c>
       <c r="AP368" s="7"/>
     </row>
-    <row r="369" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="81">
         <v>46217</v>
       </c>
@@ -40657,7 +40659,7 @@
       </c>
       <c r="AP369" s="7"/>
     </row>
-    <row r="370" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="81">
         <v>46217</v>
       </c>
@@ -40747,7 +40749,7 @@
       </c>
       <c r="AP370" s="7"/>
     </row>
-    <row r="371" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="81">
         <v>46217</v>
       </c>
@@ -40837,7 +40839,7 @@
       </c>
       <c r="AP371" s="7"/>
     </row>
-    <row r="372" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="81">
         <v>46217</v>
       </c>
@@ -40927,7 +40929,7 @@
       </c>
       <c r="AP372" s="7"/>
     </row>
-    <row r="373" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="81">
         <v>46217</v>
       </c>
@@ -41017,7 +41019,7 @@
       </c>
       <c r="AP373" s="7"/>
     </row>
-    <row r="374" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="81">
         <v>46217</v>
       </c>
@@ -41107,7 +41109,7 @@
       </c>
       <c r="AP374" s="7"/>
     </row>
-    <row r="375" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="81">
         <v>46217</v>
       </c>
@@ -41197,7 +41199,7 @@
       </c>
       <c r="AP375" s="7"/>
     </row>
-    <row r="376" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="81">
         <v>46217</v>
       </c>
@@ -41291,7 +41293,7 @@
       </c>
       <c r="AP376" s="7"/>
     </row>
-    <row r="377" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="81">
         <v>46217</v>
       </c>
@@ -41389,7 +41391,7 @@
       </c>
       <c r="AP377" s="7"/>
     </row>
-    <row r="378" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="81">
         <v>46217</v>
       </c>
@@ -41489,7 +41491,7 @@
       </c>
       <c r="AP378" s="7"/>
     </row>
-    <row r="379" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="81">
         <v>46217</v>
       </c>
@@ -41579,7 +41581,7 @@
       </c>
       <c r="AP379" s="7"/>
     </row>
-    <row r="380" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="81">
         <v>46217</v>
       </c>
@@ -41669,7 +41671,7 @@
       </c>
       <c r="AP380" s="7"/>
     </row>
-    <row r="381" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="81">
         <v>46217</v>
       </c>
@@ -41759,7 +41761,7 @@
       </c>
       <c r="AP381" s="7"/>
     </row>
-    <row r="382" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="81">
         <v>46217</v>
       </c>
@@ -41849,7 +41851,7 @@
       </c>
       <c r="AP382" s="7"/>
     </row>
-    <row r="383" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="81">
         <v>46217</v>
       </c>
@@ -41939,7 +41941,7 @@
       </c>
       <c r="AP383" s="7"/>
     </row>
-    <row r="384" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="81">
         <v>46218</v>
       </c>
@@ -42033,7 +42035,7 @@
       </c>
       <c r="AP384" s="7"/>
     </row>
-    <row r="385" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="81">
         <v>46218</v>
       </c>
@@ -42123,7 +42125,7 @@
       </c>
       <c r="AP385" s="7"/>
     </row>
-    <row r="386" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="81">
         <v>46218</v>
       </c>
@@ -42217,7 +42219,7 @@
       </c>
       <c r="AP386" s="7"/>
     </row>
-    <row r="387" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="81">
         <v>46218</v>
       </c>
@@ -42309,7 +42311,7 @@
       </c>
       <c r="AP387" s="7"/>
     </row>
-    <row r="388" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="81">
         <v>46218</v>
       </c>
@@ -42403,7 +42405,7 @@
       </c>
       <c r="AP388" s="7"/>
     </row>
-    <row r="389" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="81">
         <v>46218</v>
       </c>
@@ -42503,7 +42505,7 @@
       </c>
       <c r="AP389" s="7"/>
     </row>
-    <row r="390" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="81">
         <v>46218</v>
       </c>
@@ -42595,7 +42597,7 @@
       </c>
       <c r="AP390" s="7"/>
     </row>
-    <row r="391" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="81">
         <v>46218</v>
       </c>
@@ -42689,7 +42691,7 @@
       </c>
       <c r="AP391" s="7"/>
     </row>
-    <row r="392" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="81">
         <v>46218</v>
       </c>
@@ -42783,7 +42785,7 @@
       </c>
       <c r="AP392" s="7"/>
     </row>
-    <row r="393" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="81">
         <v>46218</v>
       </c>
@@ -42883,7 +42885,7 @@
       </c>
       <c r="AP393" s="7"/>
     </row>
-    <row r="394" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="81">
         <v>46218</v>
       </c>
@@ -42983,7 +42985,7 @@
       </c>
       <c r="AP394" s="7"/>
     </row>
-    <row r="395" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="81">
         <v>46218</v>
       </c>
@@ -43083,7 +43085,7 @@
       </c>
       <c r="AP395" s="7"/>
     </row>
-    <row r="396" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="81">
         <v>46218</v>
       </c>
@@ -43175,7 +43177,7 @@
       </c>
       <c r="AP396" s="7"/>
     </row>
-    <row r="397" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="81">
         <v>46218</v>
       </c>
@@ -43265,7 +43267,7 @@
       </c>
       <c r="AP397" s="7"/>
     </row>
-    <row r="398" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="81">
         <v>46218</v>
       </c>
@@ -43355,7 +43357,7 @@
       </c>
       <c r="AP398" s="7"/>
     </row>
-    <row r="399" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="81">
         <v>46218</v>
       </c>
@@ -43447,7 +43449,7 @@
       </c>
       <c r="AP399" s="7"/>
     </row>
-    <row r="400" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="81">
         <v>46218</v>
       </c>
@@ -43537,7 +43539,7 @@
       </c>
       <c r="AP400" s="7"/>
     </row>
-    <row r="401" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="81">
         <v>46218</v>
       </c>
@@ -43631,7 +43633,7 @@
       </c>
       <c r="AP401" s="7"/>
     </row>
-    <row r="402" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="81">
         <v>46218</v>
       </c>
@@ -43725,7 +43727,7 @@
       </c>
       <c r="AP402" s="7"/>
     </row>
-    <row r="403" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="81">
         <v>46218</v>
       </c>
@@ -43817,7 +43819,7 @@
       </c>
       <c r="AP403" s="7"/>
     </row>
-    <row r="404" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="81">
         <v>46218</v>
       </c>
@@ -43909,7 +43911,7 @@
       </c>
       <c r="AP404" s="7"/>
     </row>
-    <row r="405" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="81">
         <v>46218</v>
       </c>
@@ -44001,7 +44003,7 @@
       </c>
       <c r="AP405" s="7"/>
     </row>
-    <row r="406" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="81">
         <v>46218</v>
       </c>
@@ -44093,7 +44095,7 @@
       </c>
       <c r="AP406" s="7"/>
     </row>
-    <row r="407" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="81">
         <v>46218</v>
       </c>
@@ -44183,7 +44185,7 @@
       </c>
       <c r="AP407" s="7"/>
     </row>
-    <row r="408" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="81">
         <v>46218</v>
       </c>
@@ -44277,7 +44279,7 @@
       </c>
       <c r="AP408" s="7"/>
     </row>
-    <row r="409" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="81">
         <v>46218</v>
       </c>
@@ -44367,7 +44369,7 @@
       </c>
       <c r="AP409" s="7"/>
     </row>
-    <row r="410" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="81">
         <v>46218</v>
       </c>
@@ -44457,7 +44459,7 @@
       </c>
       <c r="AP410" s="7"/>
     </row>
-    <row r="411" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="81">
         <v>46218</v>
       </c>
@@ -44547,7 +44549,7 @@
       </c>
       <c r="AP411" s="7"/>
     </row>
-    <row r="412" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="81">
         <v>46218</v>
       </c>
@@ -44637,7 +44639,7 @@
       </c>
       <c r="AP412" s="7"/>
     </row>
-    <row r="413" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="81">
         <v>46218</v>
       </c>
@@ -44832,7 +44834,7 @@
       </c>
       <c r="AP414" s="7"/>
     </row>
-    <row r="415" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="81">
         <v>46219</v>
       </c>
@@ -44926,7 +44928,7 @@
       </c>
       <c r="AP415" s="7"/>
     </row>
-    <row r="416" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="81">
         <v>46219</v>
       </c>
@@ -45016,7 +45018,7 @@
       </c>
       <c r="AP416" s="7"/>
     </row>
-    <row r="417" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="81">
         <v>46219</v>
       </c>
@@ -45108,7 +45110,7 @@
       </c>
       <c r="AP417" s="7"/>
     </row>
-    <row r="418" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="81">
         <v>46219</v>
       </c>
@@ -45198,7 +45200,7 @@
       </c>
       <c r="AP418" s="7"/>
     </row>
-    <row r="419" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="81">
         <v>46219</v>
       </c>
@@ -45290,7 +45292,7 @@
       </c>
       <c r="AP419" s="7"/>
     </row>
-    <row r="420" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="81">
         <v>46219</v>
       </c>
@@ -45382,7 +45384,7 @@
       </c>
       <c r="AP420" s="7"/>
     </row>
-    <row r="421" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="81">
         <v>46219</v>
       </c>
@@ -45474,7 +45476,7 @@
       </c>
       <c r="AP421" s="7"/>
     </row>
-    <row r="422" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="81">
         <v>46219</v>
       </c>
@@ -45566,7 +45568,7 @@
       </c>
       <c r="AP422" s="7"/>
     </row>
-    <row r="423" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="81">
         <v>46219</v>
       </c>
@@ -45658,7 +45660,7 @@
       </c>
       <c r="AP423" s="7"/>
     </row>
-    <row r="424" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="81">
         <v>46219</v>
       </c>
@@ -45750,7 +45752,7 @@
       </c>
       <c r="AP424" s="7"/>
     </row>
-    <row r="425" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="81">
         <v>46219</v>
       </c>
@@ -45842,7 +45844,7 @@
       </c>
       <c r="AP425" s="7"/>
     </row>
-    <row r="426" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="81">
         <v>46219</v>
       </c>
@@ -45932,7 +45934,7 @@
       </c>
       <c r="AP426" s="7"/>
     </row>
-    <row r="427" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="81">
         <v>46219</v>
       </c>
@@ -46024,7 +46026,7 @@
       </c>
       <c r="AP427" s="7"/>
     </row>
-    <row r="428" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="81">
         <v>46219</v>
       </c>
@@ -46114,7 +46116,7 @@
       </c>
       <c r="AP428" s="7"/>
     </row>
-    <row r="429" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="81">
         <v>46219</v>
       </c>
@@ -46204,7 +46206,7 @@
       </c>
       <c r="AP429" s="7"/>
     </row>
-    <row r="430" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="81">
         <v>46219</v>
       </c>
@@ -46294,7 +46296,7 @@
       </c>
       <c r="AP430" s="7"/>
     </row>
-    <row r="431" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="81">
         <v>46219</v>
       </c>
@@ -46386,7 +46388,7 @@
       </c>
       <c r="AP431" s="7"/>
     </row>
-    <row r="432" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="81">
         <v>46219</v>
       </c>
@@ -46476,7 +46478,7 @@
       </c>
       <c r="AP432" s="7"/>
     </row>
-    <row r="433" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="81">
         <v>46219</v>
       </c>
@@ -46566,7 +46568,7 @@
       </c>
       <c r="AP433" s="7"/>
     </row>
-    <row r="434" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="81">
         <v>46219</v>
       </c>
@@ -47138,7 +47140,7 @@
       </c>
       <c r="AP439" s="7"/>
     </row>
-    <row r="440" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="81">
         <v>46220</v>
       </c>
@@ -47230,7 +47232,7 @@
       </c>
       <c r="AP440" s="7"/>
     </row>
-    <row r="441" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="81">
         <v>46220</v>
       </c>
@@ -47322,7 +47324,7 @@
       </c>
       <c r="AP441" s="7"/>
     </row>
-    <row r="442" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="81">
         <v>46220</v>
       </c>
@@ -47416,7 +47418,7 @@
       </c>
       <c r="AP442" s="7"/>
     </row>
-    <row r="443" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="81">
         <v>46220</v>
       </c>
@@ -47508,7 +47510,7 @@
       </c>
       <c r="AP443" s="7"/>
     </row>
-    <row r="444" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="81">
         <v>46220</v>
       </c>
@@ -47602,7 +47604,7 @@
       </c>
       <c r="AP444" s="7"/>
     </row>
-    <row r="445" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="81">
         <v>46220</v>
       </c>
@@ -47700,7 +47702,7 @@
       </c>
       <c r="AP445" s="7"/>
     </row>
-    <row r="446" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="81">
         <v>46220</v>
       </c>
@@ -47790,7 +47792,7 @@
       </c>
       <c r="AP446" s="7"/>
     </row>
-    <row r="447" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="81">
         <v>46220</v>
       </c>
@@ -47880,7 +47882,7 @@
       </c>
       <c r="AP447" s="7"/>
     </row>
-    <row r="448" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" s="81">
         <v>46220</v>
       </c>
@@ -47970,7 +47972,7 @@
       </c>
       <c r="AP448" s="7"/>
     </row>
-    <row r="449" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="81">
         <v>46220</v>
       </c>
@@ -48060,7 +48062,7 @@
       </c>
       <c r="AP449" s="7"/>
     </row>
-    <row r="450" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="81">
         <v>46220</v>
       </c>
@@ -48152,7 +48154,7 @@
       </c>
       <c r="AP450" s="7"/>
     </row>
-    <row r="451" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="81">
         <v>46220</v>
       </c>
@@ -48242,7 +48244,7 @@
       </c>
       <c r="AP451" s="7"/>
     </row>
-    <row r="452" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="81">
         <v>46220</v>
       </c>
@@ -48332,7 +48334,7 @@
       </c>
       <c r="AP452" s="7"/>
     </row>
-    <row r="453" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="81">
         <v>46220</v>
       </c>
@@ -48422,7 +48424,7 @@
       </c>
       <c r="AP453" s="7"/>
     </row>
-    <row r="454" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="81">
         <v>46220</v>
       </c>
@@ -48512,7 +48514,7 @@
       </c>
       <c r="AP454" s="7"/>
     </row>
-    <row r="455" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="81">
         <v>46220</v>
       </c>
@@ -48606,7 +48608,7 @@
       </c>
       <c r="AP455" s="7"/>
     </row>
-    <row r="456" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="81">
         <v>46220</v>
       </c>
@@ -48696,7 +48698,7 @@
       </c>
       <c r="AP456" s="7"/>
     </row>
-    <row r="457" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="81">
         <v>46220</v>
       </c>
@@ -48786,7 +48788,7 @@
       </c>
       <c r="AP457" s="7"/>
     </row>
-    <row r="458" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="81">
         <v>46220</v>
       </c>
@@ -48880,7 +48882,7 @@
       </c>
       <c r="AP458" s="7"/>
     </row>
-    <row r="459" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="81">
         <v>46220</v>
       </c>
@@ -48975,7 +48977,7 @@
       </c>
       <c r="AP459" s="7"/>
     </row>
-    <row r="460" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="81">
         <v>46220</v>
       </c>
@@ -49077,7 +49079,7 @@
       </c>
       <c r="AP460" s="7"/>
     </row>
-    <row r="461" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="81">
         <v>46220</v>
       </c>
@@ -49171,7 +49173,7 @@
       </c>
       <c r="AP461" s="7"/>
     </row>
-    <row r="462" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="81">
         <v>46220</v>
       </c>
@@ -49269,7 +49271,7 @@
       </c>
       <c r="AP462" s="7"/>
     </row>
-    <row r="463" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="81">
         <v>46220</v>
       </c>
@@ -49367,7 +49369,7 @@
       </c>
       <c r="AP463" s="7"/>
     </row>
-    <row r="464" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="81">
         <v>46220</v>
       </c>
@@ -49457,7 +49459,7 @@
       </c>
       <c r="AP464" s="7"/>
     </row>
-    <row r="465" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" s="81">
         <v>46220</v>
       </c>
@@ -49547,7 +49549,7 @@
       </c>
       <c r="AP465" s="7"/>
     </row>
-    <row r="466" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="81">
         <v>46220</v>
       </c>
@@ -49637,7 +49639,7 @@
       </c>
       <c r="AP466" s="7"/>
     </row>
-    <row r="467" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="81">
         <v>46220</v>
       </c>
@@ -49727,7 +49729,7 @@
       </c>
       <c r="AP467" s="7"/>
     </row>
-    <row r="468" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="81">
         <v>46220</v>
       </c>
@@ -49817,7 +49819,7 @@
       </c>
       <c r="AP468" s="7"/>
     </row>
-    <row r="469" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="81">
         <v>46220</v>
       </c>
@@ -49907,7 +49909,7 @@
       </c>
       <c r="AP469" s="7"/>
     </row>
-    <row r="470" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="81">
         <v>46220</v>
       </c>
@@ -49969,7 +49971,7 @@
       <c r="AL470" s="102"/>
       <c r="AP470" s="7"/>
     </row>
-    <row r="471" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="81">
         <v>46220</v>
       </c>
@@ -50031,7 +50033,7 @@
       <c r="AL471" s="102"/>
       <c r="AP471" s="7"/>
     </row>
-    <row r="472" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="81">
         <v>46220</v>
       </c>
@@ -50093,7 +50095,7 @@
       <c r="AL472" s="102"/>
       <c r="AP472" s="7"/>
     </row>
-    <row r="473" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="81">
         <v>46220</v>
       </c>
@@ -50155,7 +50157,7 @@
       <c r="AL473" s="102"/>
       <c r="AP473" s="7"/>
     </row>
-    <row r="474" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="81">
         <v>46220</v>
       </c>
@@ -50225,7 +50227,7 @@
       <c r="AL474" s="102"/>
       <c r="AP474" s="7"/>
     </row>
-    <row r="475" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" s="81">
         <v>46220</v>
       </c>
@@ -50761,7 +50763,7 @@
       <c r="AL482" s="102"/>
       <c r="AP482" s="7"/>
     </row>
-    <row r="483" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="81">
         <v>46221</v>
       </c>
@@ -50825,7 +50827,7 @@
       <c r="AL483" s="102"/>
       <c r="AP483" s="7"/>
     </row>
-    <row r="484" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="81">
         <v>46221</v>
       </c>
@@ -50891,7 +50893,7 @@
       <c r="AL484" s="102"/>
       <c r="AP484" s="7"/>
     </row>
-    <row r="485" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" s="81">
         <v>46221</v>
       </c>
@@ -50953,7 +50955,7 @@
       <c r="AL485" s="102"/>
       <c r="AP485" s="7"/>
     </row>
-    <row r="486" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="81">
         <v>46221</v>
       </c>
@@ -51023,7 +51025,7 @@
       <c r="AL486" s="102"/>
       <c r="AP486" s="7"/>
     </row>
-    <row r="487" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="81">
         <v>46221</v>
       </c>
@@ -51085,7 +51087,7 @@
       <c r="AL487" s="102"/>
       <c r="AP487" s="7"/>
     </row>
-    <row r="488" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="81">
         <v>46221</v>
       </c>
@@ -51151,7 +51153,7 @@
       <c r="AL488" s="102"/>
       <c r="AP488" s="7"/>
     </row>
-    <row r="489" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="81">
         <v>46221</v>
       </c>
@@ -51215,7 +51217,7 @@
       <c r="AL489" s="102"/>
       <c r="AP489" s="7"/>
     </row>
-    <row r="490" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="81">
         <v>46221</v>
       </c>
@@ -51281,7 +51283,7 @@
       <c r="AL490" s="102"/>
       <c r="AP490" s="7"/>
     </row>
-    <row r="491" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="81">
         <v>46221</v>
       </c>
@@ -51405,7 +51407,7 @@
       <c r="AL492" s="102"/>
       <c r="AP492" s="7"/>
     </row>
-    <row r="493" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="81">
         <v>46221</v>
       </c>
@@ -51469,7 +51471,7 @@
       <c r="AL493" s="102"/>
       <c r="AP493" s="7"/>
     </row>
-    <row r="494" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="81">
         <v>46221</v>
       </c>
@@ -51533,7 +51535,7 @@
       <c r="AL494" s="102"/>
       <c r="AP494" s="7"/>
     </row>
-    <row r="495" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="81">
         <v>46221</v>
       </c>
@@ -51597,7 +51599,7 @@
       <c r="AL495" s="102"/>
       <c r="AP495" s="7"/>
     </row>
-    <row r="496" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="81">
         <v>46221</v>
       </c>
@@ -51659,7 +51661,7 @@
       <c r="AL496" s="102"/>
       <c r="AP496" s="7"/>
     </row>
-    <row r="497" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="81">
         <v>46221</v>
       </c>
@@ -51725,7 +51727,7 @@
       <c r="AL497" s="102"/>
       <c r="AP497" s="7"/>
     </row>
-    <row r="498" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" s="81">
         <v>46221</v>
       </c>
@@ -51795,7 +51797,7 @@
       <c r="AL498" s="102"/>
       <c r="AP498" s="7"/>
     </row>
-    <row r="499" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" s="81">
         <v>46221</v>
       </c>
@@ -51857,7 +51859,7 @@
       <c r="AL499" s="102"/>
       <c r="AP499" s="7"/>
     </row>
-    <row r="500" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="81">
         <v>46221</v>
       </c>
@@ -51919,7 +51921,7 @@
       <c r="AL500" s="102"/>
       <c r="AP500" s="7"/>
     </row>
-    <row r="501" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" s="81">
         <v>46221</v>
       </c>
@@ -51981,7 +51983,7 @@
       <c r="AL501" s="102"/>
       <c r="AP501" s="7"/>
     </row>
-    <row r="502" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="81">
         <v>46221</v>
       </c>
@@ -52043,7 +52045,7 @@
       <c r="AL502" s="102"/>
       <c r="AP502" s="7"/>
     </row>
-    <row r="503" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="81">
         <v>46221</v>
       </c>
@@ -52105,7 +52107,7 @@
       <c r="AL503" s="102"/>
       <c r="AP503" s="7"/>
     </row>
-    <row r="504" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="81">
         <v>46221</v>
       </c>
@@ -52167,7 +52169,7 @@
       <c r="AL504" s="102"/>
       <c r="AP504" s="7"/>
     </row>
-    <row r="505" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" s="81">
         <v>46221</v>
       </c>
@@ -52229,7 +52231,7 @@
       <c r="AL505" s="102"/>
       <c r="AP505" s="7"/>
     </row>
-    <row r="506" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="81">
         <v>46221</v>
       </c>
@@ -52291,7 +52293,7 @@
       <c r="AL506" s="102"/>
       <c r="AP506" s="7"/>
     </row>
-    <row r="507" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="81">
         <v>46221</v>
       </c>
@@ -52353,7 +52355,7 @@
       <c r="AL507" s="102"/>
       <c r="AP507" s="7"/>
     </row>
-    <row r="508" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" s="81">
         <v>46221</v>
       </c>
@@ -52415,7 +52417,7 @@
       <c r="AL508" s="102"/>
       <c r="AP508" s="7"/>
     </row>
-    <row r="509" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="81">
         <v>46221</v>
       </c>
@@ -52477,7 +52479,7 @@
       <c r="AL509" s="102"/>
       <c r="AP509" s="7"/>
     </row>
-    <row r="510" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="81">
         <v>46221</v>
       </c>
@@ -52539,7 +52541,7 @@
       <c r="AL510" s="102"/>
       <c r="AP510" s="7"/>
     </row>
-    <row r="511" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="81">
         <v>46221</v>
       </c>
@@ -52743,7 +52745,7 @@
       <c r="AL513" s="102"/>
       <c r="AP513" s="7"/>
     </row>
-    <row r="514" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="81">
         <v>46223</v>
       </c>
@@ -52807,7 +52809,7 @@
       <c r="AL514" s="102"/>
       <c r="AP514" s="7"/>
     </row>
-    <row r="515" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" s="81">
         <v>46223</v>
       </c>
@@ -52869,7 +52871,7 @@
       <c r="AL515" s="102"/>
       <c r="AP515" s="7"/>
     </row>
-    <row r="516" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="81">
         <v>46223</v>
       </c>
@@ -52933,7 +52935,7 @@
       <c r="AL516" s="102"/>
       <c r="AP516" s="7"/>
     </row>
-    <row r="517" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="81">
         <v>46223</v>
       </c>
@@ -52995,7 +52997,7 @@
       <c r="AL517" s="102"/>
       <c r="AP517" s="7"/>
     </row>
-    <row r="518" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" s="81">
         <v>46223</v>
       </c>
@@ -53057,7 +53059,7 @@
       <c r="AL518" s="102"/>
       <c r="AP518" s="7"/>
     </row>
-    <row r="519" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="81">
         <v>46223</v>
       </c>
@@ -53123,7 +53125,7 @@
       <c r="AL519" s="102"/>
       <c r="AP519" s="7"/>
     </row>
-    <row r="520" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="81">
         <v>46223</v>
       </c>
@@ -53185,7 +53187,7 @@
       <c r="AL520" s="102"/>
       <c r="AP520" s="7"/>
     </row>
-    <row r="521" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="81">
         <v>46223</v>
       </c>
@@ -53251,7 +53253,7 @@
       <c r="AL521" s="102"/>
       <c r="AP521" s="7"/>
     </row>
-    <row r="522" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="81">
         <v>46223</v>
       </c>
@@ -53313,7 +53315,7 @@
       <c r="AL522" s="102"/>
       <c r="AP522" s="7"/>
     </row>
-    <row r="523" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="81">
         <v>46223</v>
       </c>
@@ -53375,7 +53377,7 @@
       <c r="AL523" s="102"/>
       <c r="AP523" s="7"/>
     </row>
-    <row r="524" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="81">
         <v>46223</v>
       </c>
@@ -53439,7 +53441,7 @@
       <c r="AL524" s="102"/>
       <c r="AP524" s="7"/>
     </row>
-    <row r="525" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="81">
         <v>46223</v>
       </c>
@@ -53501,7 +53503,7 @@
       <c r="AL525" s="102"/>
       <c r="AP525" s="7"/>
     </row>
-    <row r="526" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="81">
         <v>46223</v>
       </c>
@@ -53563,7 +53565,7 @@
       <c r="AL526" s="102"/>
       <c r="AP526" s="7"/>
     </row>
-    <row r="527" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="81">
         <v>46223</v>
       </c>
@@ -53625,7 +53627,7 @@
       <c r="AL527" s="102"/>
       <c r="AP527" s="7"/>
     </row>
-    <row r="528" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="81">
         <v>46223</v>
       </c>
@@ -53687,7 +53689,7 @@
       <c r="AL528" s="102"/>
       <c r="AP528" s="7"/>
     </row>
-    <row r="529" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="81">
         <v>46223</v>
       </c>
@@ -53749,7 +53751,7 @@
       <c r="AL529" s="102"/>
       <c r="AP529" s="7"/>
     </row>
-    <row r="530" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" s="81">
         <v>46223</v>
       </c>
@@ -53811,7 +53813,7 @@
       <c r="AL530" s="102"/>
       <c r="AP530" s="7"/>
     </row>
-    <row r="531" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="81">
         <v>46223</v>
       </c>
@@ -53873,7 +53875,7 @@
       <c r="AL531" s="102"/>
       <c r="AP531" s="7"/>
     </row>
-    <row r="532" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="81">
         <v>46223</v>
       </c>
@@ -53943,7 +53945,7 @@
       <c r="AL532" s="102"/>
       <c r="AP532" s="7"/>
     </row>
-    <row r="533" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="81">
         <v>46223</v>
       </c>
@@ -54005,7 +54007,7 @@
       <c r="AL533" s="102"/>
       <c r="AP533" s="7"/>
     </row>
-    <row r="534" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="81">
         <v>46223</v>
       </c>
@@ -54067,7 +54069,7 @@
       <c r="AL534" s="102"/>
       <c r="AP534" s="7"/>
     </row>
-    <row r="535" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" s="81">
         <v>46223</v>
       </c>
@@ -54129,7 +54131,7 @@
       <c r="AL535" s="102"/>
       <c r="AP535" s="7"/>
     </row>
-    <row r="536" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="81">
         <v>46223</v>
       </c>
@@ -54191,7 +54193,7 @@
       <c r="AL536" s="102"/>
       <c r="AP536" s="7"/>
     </row>
-    <row r="537" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="81">
         <v>46223</v>
       </c>
@@ -54613,7 +54615,7 @@
       <c r="AL542" s="102"/>
       <c r="AP542" s="7"/>
     </row>
-    <row r="543" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="81">
         <v>46224</v>
       </c>
@@ -54686,7 +54688,7 @@
       <c r="AL543" s="102"/>
       <c r="AP543" s="7"/>
     </row>
-    <row r="544" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="81">
         <v>46224</v>
       </c>
@@ -54752,7 +54754,7 @@
       <c r="AL544" s="102"/>
       <c r="AP544" s="7"/>
     </row>
-    <row r="545" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="81">
         <v>46224</v>
       </c>
@@ -54818,7 +54820,7 @@
       <c r="AL545" s="102"/>
       <c r="AP545" s="7"/>
     </row>
-    <row r="546" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="81">
         <v>46224</v>
       </c>
@@ -54880,7 +54882,7 @@
       <c r="AL546" s="102"/>
       <c r="AP546" s="7"/>
     </row>
-    <row r="547" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="81">
         <v>46224</v>
       </c>
@@ -54942,7 +54944,7 @@
       <c r="AL547" s="102"/>
       <c r="AP547" s="7"/>
     </row>
-    <row r="548" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="81">
         <v>46224</v>
       </c>
@@ -55014,7 +55016,7 @@
       <c r="AL548" s="102"/>
       <c r="AP548" s="7"/>
     </row>
-    <row r="549" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="81">
         <v>46224</v>
       </c>
@@ -55080,7 +55082,7 @@
       <c r="AL549" s="102"/>
       <c r="AP549" s="7"/>
     </row>
-    <row r="550" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="81">
         <v>46224</v>
       </c>
@@ -55146,7 +55148,7 @@
       <c r="AL550" s="102"/>
       <c r="AP550" s="7"/>
     </row>
-    <row r="551" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="81">
         <v>46224</v>
       </c>
@@ -55212,7 +55214,7 @@
       <c r="AL551" s="102"/>
       <c r="AP551" s="7"/>
     </row>
-    <row r="552" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="81">
         <v>46224</v>
       </c>
@@ -55278,7 +55280,7 @@
       <c r="AL552" s="102"/>
       <c r="AP552" s="7"/>
     </row>
-    <row r="553" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="81">
         <v>46224</v>
       </c>
@@ -55340,7 +55342,7 @@
       <c r="AL553" s="102"/>
       <c r="AP553" s="7"/>
     </row>
-    <row r="554" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="81">
         <v>46224</v>
       </c>
@@ -55404,7 +55406,7 @@
       <c r="AL554" s="102"/>
       <c r="AP554" s="7"/>
     </row>
-    <row r="555" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="81">
         <v>46224</v>
       </c>
@@ -55470,7 +55472,7 @@
       <c r="AL555" s="102"/>
       <c r="AP555" s="7"/>
     </row>
-    <row r="556" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="81">
         <v>46224</v>
       </c>
@@ -55532,7 +55534,7 @@
       <c r="AL556" s="102"/>
       <c r="AP556" s="7"/>
     </row>
-    <row r="557" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="81">
         <v>46224</v>
       </c>
@@ -55594,7 +55596,7 @@
       <c r="AL557" s="102"/>
       <c r="AP557" s="7"/>
     </row>
-    <row r="558" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="81">
         <v>46224</v>
       </c>
@@ -55656,7 +55658,7 @@
       <c r="AL558" s="102"/>
       <c r="AP558" s="7"/>
     </row>
-    <row r="559" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="81">
         <v>46224</v>
       </c>
@@ -55724,7 +55726,7 @@
       <c r="AL559" s="102"/>
       <c r="AP559" s="7"/>
     </row>
-    <row r="560" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="81">
         <v>46224</v>
       </c>
@@ -55786,7 +55788,7 @@
       <c r="AL560" s="102"/>
       <c r="AP560" s="7"/>
     </row>
-    <row r="561" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" s="81">
         <v>46224</v>
       </c>
@@ -55848,7 +55850,7 @@
       <c r="AL561" s="102"/>
       <c r="AP561" s="7"/>
     </row>
-    <row r="562" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="81">
         <v>46224</v>
       </c>
@@ -55910,7 +55912,7 @@
       <c r="AL562" s="102"/>
       <c r="AP562" s="7"/>
     </row>
-    <row r="563" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="81">
         <v>46224</v>
       </c>
@@ -55972,7 +55974,7 @@
       <c r="AL563" s="102"/>
       <c r="AP563" s="7"/>
     </row>
-    <row r="564" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="81">
         <v>46224</v>
       </c>
@@ -56034,7 +56036,7 @@
       <c r="AL564" s="102"/>
       <c r="AP564" s="7"/>
     </row>
-    <row r="565" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="81">
         <v>46224</v>
       </c>
@@ -56096,7 +56098,7 @@
       <c r="AL565" s="102"/>
       <c r="AP565" s="7"/>
     </row>
-    <row r="566" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" s="81">
         <v>46224</v>
       </c>
@@ -56158,7 +56160,7 @@
       <c r="AL566" s="102"/>
       <c r="AP566" s="7"/>
     </row>
-    <row r="567" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="81">
         <v>46224</v>
       </c>
@@ -56220,7 +56222,7 @@
       <c r="AL567" s="102"/>
       <c r="AP567" s="7"/>
     </row>
-    <row r="568" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="81">
         <v>46224</v>
       </c>
@@ -56288,7 +56290,7 @@
       <c r="AL568" s="102"/>
       <c r="AP568" s="7"/>
     </row>
-    <row r="569" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="81">
         <v>46225</v>
       </c>
@@ -56354,7 +56356,7 @@
       <c r="AL569" s="102"/>
       <c r="AP569" s="7"/>
     </row>
-    <row r="570" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="81">
         <v>46225</v>
       </c>
@@ -56416,7 +56418,7 @@
       <c r="AL570" s="102"/>
       <c r="AP570" s="7"/>
     </row>
-    <row r="571" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="81">
         <v>46225</v>
       </c>
@@ -56478,7 +56480,7 @@
       <c r="AL571" s="102"/>
       <c r="AP571" s="7"/>
     </row>
-    <row r="572" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="81">
         <v>46225</v>
       </c>
@@ -56540,7 +56542,7 @@
       <c r="AL572" s="102"/>
       <c r="AP572" s="7"/>
     </row>
-    <row r="573" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="81">
         <v>46225</v>
       </c>
@@ -56604,7 +56606,7 @@
       <c r="AL573" s="102"/>
       <c r="AP573" s="7"/>
     </row>
-    <row r="574" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="81">
         <v>46225</v>
       </c>
@@ -56668,7 +56670,7 @@
       <c r="AL574" s="102"/>
       <c r="AP574" s="7"/>
     </row>
-    <row r="575" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="81">
         <v>46225</v>
       </c>
@@ -56732,7 +56734,7 @@
       <c r="AL575" s="102"/>
       <c r="AP575" s="7"/>
     </row>
-    <row r="576" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="81">
         <v>46225</v>
       </c>
@@ -56798,7 +56800,7 @@
       <c r="AL576" s="102"/>
       <c r="AP576" s="7"/>
     </row>
-    <row r="577" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="81">
         <v>46225</v>
       </c>
@@ -56860,7 +56862,7 @@
       <c r="AL577" s="102"/>
       <c r="AP577" s="7"/>
     </row>
-    <row r="578" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="81">
         <v>46225</v>
       </c>
@@ -56922,7 +56924,7 @@
       <c r="AL578" s="102"/>
       <c r="AP578" s="7"/>
     </row>
-    <row r="579" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="81">
         <v>46225</v>
       </c>
@@ -56984,7 +56986,7 @@
       <c r="AL579" s="102"/>
       <c r="AP579" s="7"/>
     </row>
-    <row r="580" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="81">
         <v>46225</v>
       </c>
@@ -57046,7 +57048,7 @@
       <c r="AL580" s="102"/>
       <c r="AP580" s="7"/>
     </row>
-    <row r="581" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="81">
         <v>46225</v>
       </c>
@@ -57112,7 +57114,7 @@
       <c r="AL581" s="102"/>
       <c r="AP581" s="7"/>
     </row>
-    <row r="582" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" s="81">
         <v>46225</v>
       </c>
@@ -57174,7 +57176,7 @@
       <c r="AL582" s="102"/>
       <c r="AP582" s="7"/>
     </row>
-    <row r="583" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" s="81">
         <v>46225</v>
       </c>
@@ -57236,7 +57238,7 @@
       <c r="AL583" s="102"/>
       <c r="AP583" s="7"/>
     </row>
-    <row r="584" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="81">
         <v>46225</v>
       </c>
@@ -57298,7 +57300,7 @@
       <c r="AL584" s="102"/>
       <c r="AP584" s="7"/>
     </row>
-    <row r="585" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="81">
         <v>46225</v>
       </c>
@@ -57364,7 +57366,7 @@
       <c r="AL585" s="102"/>
       <c r="AP585" s="7"/>
     </row>
-    <row r="586" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="81">
         <v>46225</v>
       </c>
@@ -57426,7 +57428,7 @@
       <c r="AL586" s="102"/>
       <c r="AP586" s="7"/>
     </row>
-    <row r="587" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="81">
         <v>46225</v>
       </c>
@@ -57488,7 +57490,7 @@
       <c r="AL587" s="102"/>
       <c r="AP587" s="7"/>
     </row>
-    <row r="588" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="81">
         <v>46225</v>
       </c>
@@ -57550,7 +57552,7 @@
       <c r="AL588" s="102"/>
       <c r="AP588" s="7"/>
     </row>
-    <row r="589" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="81">
         <v>46225</v>
       </c>
@@ -57612,7 +57614,7 @@
       <c r="AL589" s="102"/>
       <c r="AP589" s="7"/>
     </row>
-    <row r="590" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" s="81">
         <v>46225</v>
       </c>
@@ -57674,7 +57676,7 @@
       <c r="AL590" s="102"/>
       <c r="AP590" s="7"/>
     </row>
-    <row r="591" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" s="81">
         <v>46225</v>
       </c>
@@ -57738,7 +57740,7 @@
       <c r="AL591" s="102"/>
       <c r="AP591" s="7"/>
     </row>
-    <row r="592" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="81">
         <v>46225</v>
       </c>
@@ -58416,7 +58418,7 @@
       <c r="AL601" s="102"/>
       <c r="AP601" s="7"/>
     </row>
-    <row r="602" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="81">
         <v>46226</v>
       </c>
@@ -58480,7 +58482,7 @@
       <c r="AL602" s="102"/>
       <c r="AP602" s="7"/>
     </row>
-    <row r="603" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="81">
         <v>46226</v>
       </c>
@@ -58546,7 +58548,7 @@
       <c r="AL603" s="102"/>
       <c r="AP603" s="7"/>
     </row>
-    <row r="604" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="81">
         <v>46226</v>
       </c>
@@ -58612,7 +58614,7 @@
       <c r="AL604" s="102"/>
       <c r="AP604" s="7"/>
     </row>
-    <row r="605" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="81">
         <v>46226</v>
       </c>
@@ -58678,7 +58680,7 @@
       <c r="AL605" s="102"/>
       <c r="AP605" s="7"/>
     </row>
-    <row r="606" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="81">
         <v>46226</v>
       </c>
@@ -58740,7 +58742,7 @@
       <c r="AL606" s="102"/>
       <c r="AP606" s="7"/>
     </row>
-    <row r="607" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="81">
         <v>46226</v>
       </c>
@@ -58802,7 +58804,7 @@
       <c r="AL607" s="102"/>
       <c r="AP607" s="7"/>
     </row>
-    <row r="608" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="81">
         <v>46226</v>
       </c>
@@ -58870,7 +58872,7 @@
       <c r="AL608" s="102"/>
       <c r="AP608" s="7"/>
     </row>
-    <row r="609" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="81">
         <v>46226</v>
       </c>
@@ -58936,7 +58938,7 @@
       <c r="AL609" s="102"/>
       <c r="AP609" s="7"/>
     </row>
-    <row r="610" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="81">
         <v>46226</v>
       </c>
@@ -59004,7 +59006,7 @@
       <c r="AL610" s="102"/>
       <c r="AP610" s="7"/>
     </row>
-    <row r="611" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" s="81">
         <v>46226</v>
       </c>
@@ -59076,7 +59078,7 @@
       <c r="AL611" s="102"/>
       <c r="AP611" s="7"/>
     </row>
-    <row r="612" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="81">
         <v>46226</v>
       </c>
@@ -59424,7 +59426,7 @@
       <c r="AL616" s="102"/>
       <c r="AP616" s="7"/>
     </row>
-    <row r="617" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="81">
         <v>46227</v>
       </c>
@@ -59490,7 +59492,7 @@
       <c r="AL617" s="102"/>
       <c r="AP617" s="7"/>
     </row>
-    <row r="618" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="81">
         <v>46227</v>
       </c>
@@ -59562,7 +59564,7 @@
       <c r="AL618" s="102"/>
       <c r="AP618" s="7"/>
     </row>
-    <row r="619" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619" s="81">
         <v>46228</v>
       </c>
@@ -60034,7 +60036,7 @@
       <c r="AL625" s="102"/>
       <c r="AP625" s="7"/>
     </row>
-    <row r="626" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A626" s="81">
         <v>46230</v>
       </c>
@@ -60102,7 +60104,7 @@
       <c r="AL626" s="102"/>
       <c r="AP626" s="7"/>
     </row>
-    <row r="627" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A627" s="81">
         <v>46230</v>
       </c>
@@ -60168,7 +60170,7 @@
       <c r="AL627" s="102"/>
       <c r="AP627" s="7"/>
     </row>
-    <row r="628" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A628" s="81">
         <v>46230</v>
       </c>
@@ -60236,7 +60238,7 @@
       <c r="AL628" s="102"/>
       <c r="AP628" s="7"/>
     </row>
-    <row r="629" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A629" s="81">
         <v>46230</v>
       </c>
@@ -60302,7 +60304,7 @@
       <c r="AL629" s="102"/>
       <c r="AP629" s="7"/>
     </row>
-    <row r="630" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630" s="81">
         <v>46230</v>
       </c>
@@ -60364,7 +60366,7 @@
       <c r="AL630" s="102"/>
       <c r="AP630" s="7"/>
     </row>
-    <row r="631" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631" s="81">
         <v>46230</v>
       </c>
@@ -60426,7 +60428,7 @@
       <c r="AL631" s="102"/>
       <c r="AP631" s="7"/>
     </row>
-    <row r="632" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A632" s="81">
         <v>46230</v>
       </c>
@@ -60498,7 +60500,7 @@
       <c r="AL632" s="102"/>
       <c r="AP632" s="7"/>
     </row>
-    <row r="633" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A633" s="81">
         <v>46230</v>
       </c>
@@ -60566,7 +60568,7 @@
       <c r="AL633" s="102"/>
       <c r="AP633" s="7"/>
     </row>
-    <row r="634" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A634" s="81">
         <v>46230</v>
       </c>
@@ -60632,7 +60634,7 @@
       <c r="AL634" s="102"/>
       <c r="AP634" s="7"/>
     </row>
-    <row r="635" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A635" s="81">
         <v>46230</v>
       </c>
@@ -60700,7 +60702,7 @@
       <c r="AL635" s="102"/>
       <c r="AP635" s="7"/>
     </row>
-    <row r="636" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A636" s="81">
         <v>46230</v>
       </c>
@@ -60770,7 +60772,7 @@
       <c r="AL636" s="102"/>
       <c r="AP636" s="7"/>
     </row>
-    <row r="637" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A637" s="81">
         <v>46230</v>
       </c>
@@ -60836,7 +60838,7 @@
       <c r="AL637" s="102"/>
       <c r="AP637" s="7"/>
     </row>
-    <row r="638" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A638" s="81">
         <v>46230</v>
       </c>
@@ -60898,7 +60900,7 @@
       <c r="AL638" s="102"/>
       <c r="AP638" s="7"/>
     </row>
-    <row r="639" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A639" s="81">
         <v>46230</v>
       </c>
@@ -60960,7 +60962,7 @@
       <c r="AL639" s="102"/>
       <c r="AP639" s="7"/>
     </row>
-    <row r="640" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640" s="81">
         <v>46230</v>
       </c>
@@ -61028,7 +61030,7 @@
       <c r="AL640" s="102"/>
       <c r="AP640" s="7"/>
     </row>
-    <row r="641" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641" s="81">
         <v>46230</v>
       </c>
@@ -61100,7 +61102,7 @@
       <c r="AL641" s="102"/>
       <c r="AP641" s="7"/>
     </row>
-    <row r="642" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642" s="81">
         <v>46230</v>
       </c>
@@ -61172,7 +61174,7 @@
       <c r="AL642" s="102"/>
       <c r="AP642" s="7"/>
     </row>
-    <row r="643" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A643" s="81">
         <v>46230</v>
       </c>
@@ -61234,7 +61236,7 @@
       <c r="AL643" s="102"/>
       <c r="AP643" s="7"/>
     </row>
-    <row r="644" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A644" s="81">
         <v>46230</v>
       </c>
@@ -61296,7 +61298,7 @@
       <c r="AL644" s="102"/>
       <c r="AP644" s="7"/>
     </row>
-    <row r="645" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A645" s="81">
         <v>46230</v>
       </c>
@@ -61638,7 +61640,7 @@
       <c r="AL649" s="102"/>
       <c r="AP649" s="7"/>
     </row>
-    <row r="650" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A650" s="81">
         <v>46231</v>
       </c>
@@ -61706,7 +61708,7 @@
       <c r="AL650" s="102"/>
       <c r="AP650" s="7"/>
     </row>
-    <row r="651" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A651" s="81">
         <v>46231</v>
       </c>
@@ -61774,7 +61776,7 @@
       <c r="AL651" s="102"/>
       <c r="AP651" s="7"/>
     </row>
-    <row r="652" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A652" s="81">
         <v>46231</v>
       </c>
@@ -61844,7 +61846,7 @@
       <c r="AL652" s="102"/>
       <c r="AP652" s="7"/>
     </row>
-    <row r="653" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A653" s="81">
         <v>46231</v>
       </c>
@@ -61914,7 +61916,7 @@
       <c r="AL653" s="102"/>
       <c r="AP653" s="7"/>
     </row>
-    <row r="654" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A654" s="81">
         <v>46231</v>
       </c>
@@ -61978,7 +61980,7 @@
       <c r="AL654" s="102"/>
       <c r="AP654" s="7"/>
     </row>
-    <row r="655" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A655" s="81">
         <v>46231</v>
       </c>
@@ -62044,7 +62046,7 @@
       <c r="AL655" s="102"/>
       <c r="AP655" s="7"/>
     </row>
-    <row r="656" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656" s="81">
         <v>46231</v>
       </c>
@@ -62106,7 +62108,7 @@
       <c r="AL656" s="102"/>
       <c r="AP656" s="7"/>
     </row>
-    <row r="657" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657" s="81">
         <v>46231</v>
       </c>
@@ -62178,7 +62180,7 @@
       <c r="AL657" s="102"/>
       <c r="AP657" s="7"/>
     </row>
-    <row r="658" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658" s="81">
         <v>46231</v>
       </c>
@@ -62246,7 +62248,7 @@
       <c r="AL658" s="102"/>
       <c r="AP658" s="7"/>
     </row>
-    <row r="659" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659" s="81">
         <v>46231</v>
       </c>
@@ -62312,7 +62314,7 @@
       <c r="AL659" s="102"/>
       <c r="AP659" s="7"/>
     </row>
-    <row r="660" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660" s="81">
         <v>46231</v>
       </c>
@@ -62384,7 +62386,7 @@
       <c r="AL660" s="102"/>
       <c r="AP660" s="7"/>
     </row>
-    <row r="661" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A661" s="81">
         <v>46231</v>
       </c>
@@ -62446,7 +62448,7 @@
       <c r="AL661" s="102"/>
       <c r="AP661" s="7"/>
     </row>
-    <row r="662" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A662" s="81">
         <v>46231</v>
       </c>
@@ -62508,7 +62510,7 @@
       <c r="AL662" s="102"/>
       <c r="AP662" s="7"/>
     </row>
-    <row r="663" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A663" s="81">
         <v>46231</v>
       </c>
@@ -62580,7 +62582,7 @@
       <c r="AL663" s="102"/>
       <c r="AP663" s="7"/>
     </row>
-    <row r="664" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="81">
         <v>46232</v>
       </c>
@@ -62648,7 +62650,7 @@
       <c r="AL664" s="102"/>
       <c r="AP664" s="7"/>
     </row>
-    <row r="665" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="81">
         <v>46232</v>
       </c>
@@ -62712,7 +62714,7 @@
       <c r="AL665" s="102"/>
       <c r="AP665" s="7"/>
     </row>
-    <row r="666" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A666" s="81">
         <v>46232</v>
       </c>
@@ -62778,7 +62780,7 @@
       <c r="AL666" s="102"/>
       <c r="AP666" s="7"/>
     </row>
-    <row r="667" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="81">
         <v>46232</v>
       </c>
@@ -62840,7 +62842,7 @@
       <c r="AL667" s="102"/>
       <c r="AP667" s="7"/>
     </row>
-    <row r="668" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A668" s="81">
         <v>46232</v>
       </c>
@@ -62912,7 +62914,7 @@
       <c r="AL668" s="102"/>
       <c r="AP668" s="7"/>
     </row>
-    <row r="669" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A669" s="81">
         <v>46232</v>
       </c>
@@ -62978,7 +62980,7 @@
       <c r="AL669" s="102"/>
       <c r="AP669" s="7"/>
     </row>
-    <row r="670" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A670" s="81">
         <v>46232</v>
       </c>
@@ -63044,7 +63046,7 @@
       <c r="AL670" s="102"/>
       <c r="AP670" s="7"/>
     </row>
-    <row r="671" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A671" s="81">
         <v>46232</v>
       </c>
@@ -63106,7 +63108,7 @@
       <c r="AL671" s="102"/>
       <c r="AP671" s="7"/>
     </row>
-    <row r="672" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A672" s="81">
         <v>46232</v>
       </c>
@@ -63168,7 +63170,7 @@
       <c r="AL672" s="102"/>
       <c r="AP672" s="7"/>
     </row>
-    <row r="673" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673" s="81">
         <v>46232</v>
       </c>
@@ -63236,7 +63238,7 @@
       <c r="AL673" s="102"/>
       <c r="AP673" s="7"/>
     </row>
-    <row r="674" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="81">
         <v>46232</v>
       </c>
@@ -63302,7 +63304,7 @@
       <c r="AL674" s="102"/>
       <c r="AP674" s="7"/>
     </row>
-    <row r="675" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675" s="81">
         <v>46232</v>
       </c>
@@ -63368,7 +63370,7 @@
       <c r="AL675" s="102"/>
       <c r="AP675" s="7"/>
     </row>
-    <row r="676" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676" s="81">
         <v>46232</v>
       </c>
@@ -63430,7 +63432,7 @@
       <c r="AL676" s="102"/>
       <c r="AP676" s="7"/>
     </row>
-    <row r="677" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A677" s="81">
         <v>46232</v>
       </c>
@@ -63492,7 +63494,7 @@
       <c r="AL677" s="102"/>
       <c r="AP677" s="7"/>
     </row>
-    <row r="678" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A678" s="81">
         <v>46232</v>
       </c>
@@ -63554,7 +63556,7 @@
       <c r="AL678" s="102"/>
       <c r="AP678" s="7"/>
     </row>
-    <row r="679" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A679" s="81">
         <v>46232</v>
       </c>
@@ -63620,7 +63622,7 @@
       <c r="AL679" s="102"/>
       <c r="AP679" s="7"/>
     </row>
-    <row r="680" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A680" s="81">
         <v>46232</v>
       </c>
@@ -63686,7 +63688,7 @@
       <c r="AL680" s="102"/>
       <c r="AP680" s="7"/>
     </row>
-    <row r="681" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A681" s="81">
         <v>46232</v>
       </c>
@@ -63748,7 +63750,7 @@
       <c r="AL681" s="102"/>
       <c r="AP681" s="7"/>
     </row>
-    <row r="682" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A682" s="81">
         <v>46232</v>
       </c>
@@ -63810,7 +63812,7 @@
       <c r="AL682" s="102"/>
       <c r="AP682" s="7"/>
     </row>
-    <row r="683" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A683" s="81">
         <v>46232</v>
       </c>
@@ -63874,7 +63876,7 @@
       <c r="AL683" s="102"/>
       <c r="AP683" s="7"/>
     </row>
-    <row r="684" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A684" s="81">
         <v>46232</v>
       </c>
@@ -64010,7 +64012,7 @@
       <c r="AL685" s="102"/>
       <c r="AP685" s="7"/>
     </row>
-    <row r="686" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A686" s="81">
         <v>46233</v>
       </c>
@@ -64076,7 +64078,7 @@
       <c r="AL686" s="102"/>
       <c r="AP686" s="7"/>
     </row>
-    <row r="687" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A687" s="81">
         <v>46233</v>
       </c>
@@ -64144,7 +64146,7 @@
       <c r="AL687" s="102"/>
       <c r="AP687" s="7"/>
     </row>
-    <row r="688" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A688" s="81">
         <v>46233</v>
       </c>
@@ -64206,7 +64208,7 @@
       <c r="AL688" s="102"/>
       <c r="AP688" s="7"/>
     </row>
-    <row r="689" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A689" s="81">
         <v>46233</v>
       </c>
@@ -64270,7 +64272,7 @@
       <c r="AL689" s="102"/>
       <c r="AP689" s="7"/>
     </row>
-    <row r="690" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A690" s="81">
         <v>46233</v>
       </c>
@@ -64336,7 +64338,7 @@
       <c r="AL690" s="102"/>
       <c r="AP690" s="7"/>
     </row>
-    <row r="691" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A691" s="81">
         <v>46233</v>
       </c>
@@ -64408,7 +64410,7 @@
       <c r="AL691" s="102"/>
       <c r="AP691" s="7"/>
     </row>
-    <row r="692" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A692" s="81">
         <v>46233</v>
       </c>
@@ -64470,7 +64472,7 @@
       <c r="AL692" s="102"/>
       <c r="AP692" s="7"/>
     </row>
-    <row r="693" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A693" s="81">
         <v>46233</v>
       </c>
@@ -64534,7 +64536,7 @@
       <c r="AL693" s="102"/>
       <c r="AP693" s="7"/>
     </row>
-    <row r="694" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A694" s="81">
         <v>46233</v>
       </c>
@@ -64596,7 +64598,7 @@
       <c r="AL694" s="102"/>
       <c r="AP694" s="7"/>
     </row>
-    <row r="695" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A695" s="81">
         <v>46233</v>
       </c>
@@ -64658,7 +64660,7 @@
       <c r="AL695" s="102"/>
       <c r="AP695" s="7"/>
     </row>
-    <row r="696" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A696" s="81">
         <v>46233</v>
       </c>
@@ -64724,7 +64726,7 @@
       <c r="AL696" s="102"/>
       <c r="AP696" s="7"/>
     </row>
-    <row r="697" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A697" s="81">
         <v>46233</v>
       </c>
@@ -64786,7 +64788,7 @@
       <c r="AL697" s="102"/>
       <c r="AP697" s="7"/>
     </row>
-    <row r="698" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A698" s="81">
         <v>46233</v>
       </c>
@@ -64848,7 +64850,7 @@
       <c r="AL698" s="102"/>
       <c r="AP698" s="7"/>
     </row>
-    <row r="699" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A699" s="81">
         <v>46233</v>
       </c>
@@ -64910,7 +64912,7 @@
       <c r="AL699" s="102"/>
       <c r="AP699" s="7"/>
     </row>
-    <row r="700" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A700" s="81">
         <v>46233</v>
       </c>
@@ -64976,7 +64978,7 @@
       <c r="AL700" s="102"/>
       <c r="AP700" s="7"/>
     </row>
-    <row r="701" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A701" s="81">
         <v>46233</v>
       </c>
@@ -65038,7 +65040,7 @@
       <c r="AL701" s="102"/>
       <c r="AP701" s="7"/>
     </row>
-    <row r="702" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A702" s="81">
         <v>46233</v>
       </c>
@@ -65100,7 +65102,7 @@
       <c r="AL702" s="102"/>
       <c r="AP702" s="7"/>
     </row>
-    <row r="703" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A703" s="81">
         <v>46233</v>
       </c>
@@ -65168,7 +65170,7 @@
       <c r="AL703" s="102"/>
       <c r="AP703" s="7"/>
     </row>
-    <row r="704" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A704" s="81">
         <v>46233</v>
       </c>
@@ -65230,7 +65232,7 @@
       <c r="AL704" s="102"/>
       <c r="AP704" s="7"/>
     </row>
-    <row r="705" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A705" s="81">
         <v>46233</v>
       </c>
@@ -65292,7 +65294,7 @@
       <c r="AL705" s="102"/>
       <c r="AP705" s="7"/>
     </row>
-    <row r="706" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A706" s="81">
         <v>46233</v>
       </c>
@@ -65354,7 +65356,7 @@
       <c r="AL706" s="102"/>
       <c r="AP706" s="7"/>
     </row>
-    <row r="707" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A707" s="81">
         <v>46233</v>
       </c>
@@ -65416,7 +65418,7 @@
       <c r="AL707" s="102"/>
       <c r="AP707" s="7"/>
     </row>
-    <row r="708" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A708" s="81">
         <v>46233</v>
       </c>
@@ -65480,7 +65482,7 @@
       <c r="AL708" s="102"/>
       <c r="AP708" s="7"/>
     </row>
-    <row r="709" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A709" s="81">
         <v>46233</v>
       </c>
@@ -65546,7 +65548,7 @@
       <c r="AL709" s="102"/>
       <c r="AP709" s="7"/>
     </row>
-    <row r="710" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A710" s="81">
         <v>46233</v>
       </c>
@@ -65612,7 +65614,7 @@
       <c r="AL710" s="102"/>
       <c r="AP710" s="7"/>
     </row>
-    <row r="711" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A711" s="81">
         <v>46233</v>
       </c>
@@ -65684,7 +65686,7 @@
       <c r="AL711" s="102"/>
       <c r="AP711" s="7"/>
     </row>
-    <row r="712" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712" s="81">
         <v>46233</v>
       </c>
@@ -65828,7 +65830,7 @@
       <c r="AL713" s="102"/>
       <c r="AP713" s="7"/>
     </row>
-    <row r="714" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A714" s="81">
         <v>46234</v>
       </c>
@@ -65918,7 +65920,7 @@
       <c r="F715" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="G715" s="90" t="s">
+      <c r="G715" s="148" t="s">
         <v>347</v>
       </c>
       <c r="H715" s="90" t="s">
@@ -66200,7 +66202,7 @@
       <c r="F719" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="G719" s="90" t="s">
+      <c r="G719" s="148" t="s">
         <v>727</v>
       </c>
       <c r="H719" s="90" t="s">
@@ -66519,7 +66521,7 @@
       <c r="AL723" s="102"/>
       <c r="AP723" s="7"/>
     </row>
-    <row r="724" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A724" s="81">
         <v>46234</v>
       </c>
@@ -66581,7 +66583,7 @@
       <c r="AL724" s="102"/>
       <c r="AP724" s="7"/>
     </row>
-    <row r="725" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A725" s="81">
         <v>46234</v>
       </c>
@@ -66653,7 +66655,7 @@
       <c r="AL725" s="102"/>
       <c r="AP725" s="7"/>
     </row>
-    <row r="726" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A726" s="81">
         <v>46234</v>
       </c>
@@ -66717,7 +66719,7 @@
       <c r="AL726" s="102"/>
       <c r="AP726" s="7"/>
     </row>
-    <row r="727" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A727" s="81">
         <v>46234</v>
       </c>
@@ -66783,7 +66785,7 @@
       <c r="AL727" s="102"/>
       <c r="AP727" s="7"/>
     </row>
-    <row r="728" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A728" s="81">
         <v>46234</v>
       </c>
@@ -66913,7 +66915,7 @@
       <c r="AL729" s="102"/>
       <c r="AP729" s="7"/>
     </row>
-    <row r="730" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A730" s="120">
         <v>46234</v>
       </c>
@@ -66981,7 +66983,7 @@
       <c r="AL730" s="102"/>
       <c r="AP730" s="7"/>
     </row>
-    <row r="731" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A731" s="81">
         <v>46234</v>
       </c>
@@ -67047,7 +67049,7 @@
       <c r="AL731" s="102"/>
       <c r="AP731" s="7"/>
     </row>
-    <row r="732" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A732" s="81">
         <v>46234</v>
       </c>
@@ -67109,7 +67111,7 @@
       <c r="AL732" s="102"/>
       <c r="AP732" s="7"/>
     </row>
-    <row r="733" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A733" s="81">
         <v>46234</v>
       </c>
@@ -67175,7 +67177,7 @@
       <c r="AL733" s="102"/>
       <c r="AP733" s="7"/>
     </row>
-    <row r="734" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A734" s="109">
         <v>46234</v>
       </c>
@@ -67241,7 +67243,7 @@
       <c r="AL734" s="102"/>
       <c r="AP734" s="7"/>
     </row>
-    <row r="735" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A735" s="109">
         <v>46234</v>
       </c>
@@ -67305,7 +67307,7 @@
       <c r="AL735" s="102"/>
       <c r="AP735" s="7"/>
     </row>
-    <row r="736" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A736" s="109">
         <v>46234</v>
       </c>
@@ -67373,7 +67375,7 @@
       <c r="AL736" s="102"/>
       <c r="AP736" s="7"/>
     </row>
-    <row r="737" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A737" s="109">
         <v>46234</v>
       </c>
@@ -67439,7 +67441,7 @@
       <c r="AL737" s="102"/>
       <c r="AP737" s="7"/>
     </row>
-    <row r="738" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A738" s="109">
         <v>46234</v>
       </c>
@@ -67503,7 +67505,7 @@
       <c r="AL738" s="102"/>
       <c r="AP738" s="7"/>
     </row>
-    <row r="739" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A739" s="109">
         <v>46234</v>
       </c>
@@ -67573,7 +67575,7 @@
       <c r="AL739" s="102"/>
       <c r="AP739" s="7"/>
     </row>
-    <row r="740" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A740" s="112">
         <v>46234</v>
       </c>
@@ -67639,7 +67641,7 @@
       <c r="AL740" s="127"/>
       <c r="AP740" s="7"/>
     </row>
-    <row r="741" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A741" s="109">
         <v>46234</v>
       </c>
@@ -67711,7 +67713,7 @@
       <c r="AL741" s="102"/>
       <c r="AP741" s="7"/>
     </row>
-    <row r="742" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A742" s="109">
         <v>46234</v>
       </c>
@@ -68009,7 +68011,7 @@
       </c>
       <c r="AP744" s="7"/>
     </row>
-    <row r="745" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A745" s="90"/>
       <c r="B745" s="72"/>
       <c r="C745" s="90"/>
@@ -68059,7 +68061,7 @@
       <c r="AL745" s="90"/>
       <c r="AP745" s="7"/>
     </row>
-    <row r="746" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A746" s="90"/>
       <c r="B746" s="72"/>
       <c r="C746" s="90"/>
@@ -68130,7 +68132,7 @@
       <c r="AL746" s="90"/>
       <c r="AP746" s="7"/>
     </row>
-    <row r="747" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A747" s="90"/>
       <c r="B747" s="72"/>
       <c r="C747" s="90"/>
@@ -68173,7 +68175,7 @@
       <c r="AL747" s="90"/>
       <c r="AP747" s="7"/>
     </row>
-    <row r="748" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="B748" s="76"/>
       <c r="D748" s="77"/>
       <c r="J748" s="132" t="s">
@@ -68215,7 +68217,7 @@
       <c r="AB748" s="7"/>
       <c r="AF748"/>
     </row>
-    <row r="749" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="B749" s="73"/>
       <c r="D749" s="117"/>
       <c r="I749" s="42" t="s">
@@ -69395,6 +69397,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP749" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Shakoor"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="10" showButton="0"/>
     <filterColumn colId="11" showButton="0"/>
     <filterColumn colId="12" showButton="0"/>
@@ -69409,14 +69416,13 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -69429,13 +69435,14 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Behind/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/Behind/july 2026/Daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622E9A1F-B1A0-4911-A0E4-F0F574C1BCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FC5048-1289-459D-8AE9-7CFC493992A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -3285,6 +3285,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3327,7 +3328,6 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3646,7 +3646,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP800"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3694,116 +3693,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="138" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="138" t="s">
+      <c r="A1" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="138" t="s">
+      <c r="C1" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="138" t="s">
+      <c r="D1" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="138" t="s">
+      <c r="E1" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="138" t="s">
+      <c r="F1" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="138" t="s">
+      <c r="G1" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="138" t="s">
+      <c r="H1" s="139" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J1" s="41"/>
-      <c r="K1" s="138" t="s">
+      <c r="K1" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="140" t="s">
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="136" t="s">
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="139" t="s">
+      <c r="T1" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139" t="s">
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="139"/>
-      <c r="AA1" s="139"/>
-      <c r="AB1" s="136" t="s">
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="140"/>
+      <c r="AA1" s="140"/>
+      <c r="AB1" s="137" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="136" t="s">
+      <c r="AC1" s="137" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="136" t="s">
+      <c r="AD1" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="136" t="s">
+      <c r="AE1" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="136" t="s">
+      <c r="AF1" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="136" t="s">
+      <c r="AG1" s="137" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="80">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="136" t="s">
+      <c r="AI1" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="136" t="s">
+      <c r="AJ1" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="136" t="s">
+      <c r="AK1" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="136" t="s">
+      <c r="AL1" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="136" t="s">
+      <c r="AM1" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="134" t="s">
+      <c r="AN1" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="134" t="s">
+      <c r="AO1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="136" t="s">
+      <c r="AP1" s="137" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:42" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="138"/>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
+    <row r="2" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="139"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -3834,7 +3833,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="137"/>
+      <c r="S2" s="138"/>
       <c r="T2" s="79" t="s">
         <v>73</v>
       </c>
@@ -3859,23 +3858,23 @@
       <c r="AA2" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="137"/>
-      <c r="AC2" s="137"/>
-      <c r="AD2" s="137"/>
-      <c r="AE2" s="137"/>
-      <c r="AF2" s="137"/>
-      <c r="AG2" s="137"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="138"/>
+      <c r="AG2" s="138"/>
       <c r="AH2" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="137"/>
-      <c r="AJ2" s="137"/>
-      <c r="AK2" s="137"/>
-      <c r="AL2" s="137"/>
-      <c r="AM2" s="137"/>
-      <c r="AN2" s="135"/>
-      <c r="AO2" s="135"/>
-      <c r="AP2" s="137"/>
+      <c r="AI2" s="138"/>
+      <c r="AJ2" s="138"/>
+      <c r="AK2" s="138"/>
+      <c r="AL2" s="138"/>
+      <c r="AM2" s="138"/>
+      <c r="AN2" s="136"/>
+      <c r="AO2" s="136"/>
+      <c r="AP2" s="138"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="81">
@@ -5286,7 +5285,7 @@
       </c>
       <c r="AP15" s="88"/>
     </row>
-    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A16" s="81">
         <v>46204</v>
       </c>
@@ -5384,7 +5383,7 @@
       </c>
       <c r="AP16" s="88"/>
     </row>
-    <row r="17" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A17" s="81">
         <v>46204</v>
       </c>
@@ -5482,7 +5481,7 @@
       </c>
       <c r="AP17" s="88"/>
     </row>
-    <row r="18" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18" s="81">
         <v>46204</v>
       </c>
@@ -5584,7 +5583,7 @@
       </c>
       <c r="AP18" s="88"/>
     </row>
-    <row r="19" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A19" s="81">
         <v>46204</v>
       </c>
@@ -5686,7 +5685,7 @@
       </c>
       <c r="AP19" s="88"/>
     </row>
-    <row r="20" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20" s="81">
         <v>46204</v>
       </c>
@@ -5792,7 +5791,7 @@
       </c>
       <c r="AP20" s="88"/>
     </row>
-    <row r="21" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21" s="81">
         <v>46204</v>
       </c>
@@ -5892,7 +5891,7 @@
       </c>
       <c r="AP21" s="88"/>
     </row>
-    <row r="22" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22" s="81">
         <v>46204</v>
       </c>
@@ -5994,7 +5993,7 @@
       </c>
       <c r="AP22" s="88"/>
     </row>
-    <row r="23" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23" s="81">
         <v>46204</v>
       </c>
@@ -6092,7 +6091,7 @@
       </c>
       <c r="AP23" s="88"/>
     </row>
-    <row r="24" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24" s="81">
         <v>46204</v>
       </c>
@@ -6194,7 +6193,7 @@
       </c>
       <c r="AP24" s="88"/>
     </row>
-    <row r="25" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25" s="81">
         <v>46204</v>
       </c>
@@ -6292,7 +6291,7 @@
       </c>
       <c r="AP25" s="88"/>
     </row>
-    <row r="26" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A26" s="81">
         <v>46204</v>
       </c>
@@ -6392,7 +6391,7 @@
       </c>
       <c r="AP26" s="88"/>
     </row>
-    <row r="27" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A27" s="81">
         <v>46204</v>
       </c>
@@ -6490,7 +6489,7 @@
       </c>
       <c r="AP27" s="88"/>
     </row>
-    <row r="28" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A28" s="81">
         <v>46204</v>
       </c>
@@ -6592,7 +6591,7 @@
       </c>
       <c r="AP28" s="88"/>
     </row>
-    <row r="29" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A29" s="81">
         <v>46204</v>
       </c>
@@ -6692,7 +6691,7 @@
       </c>
       <c r="AP29" s="88"/>
     </row>
-    <row r="30" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A30" s="81">
         <v>46204</v>
       </c>
@@ -6790,7 +6789,7 @@
       </c>
       <c r="AP30" s="88"/>
     </row>
-    <row r="31" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A31" s="81">
         <v>46204</v>
       </c>
@@ -6888,7 +6887,7 @@
       </c>
       <c r="AP31" s="88"/>
     </row>
-    <row r="32" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A32" s="81">
         <v>46204</v>
       </c>
@@ -6986,7 +6985,7 @@
       </c>
       <c r="AP32" s="88"/>
     </row>
-    <row r="33" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A33" s="81">
         <v>46204</v>
       </c>
@@ -7094,7 +7093,7 @@
       </c>
       <c r="AP33" s="88"/>
     </row>
-    <row r="34" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" s="81">
         <v>46204</v>
       </c>
@@ -7192,7 +7191,7 @@
       </c>
       <c r="AP34" s="88"/>
     </row>
-    <row r="35" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" s="81">
         <v>46204</v>
       </c>
@@ -7290,7 +7289,7 @@
       </c>
       <c r="AP35" s="88"/>
     </row>
-    <row r="36" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A36" s="81">
         <v>46204</v>
       </c>
@@ -7394,7 +7393,7 @@
       </c>
       <c r="AP36" s="88"/>
     </row>
-    <row r="37" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A37" s="81">
         <v>46204</v>
       </c>
@@ -7496,7 +7495,7 @@
       </c>
       <c r="AP37" s="88"/>
     </row>
-    <row r="38" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A38" s="81">
         <v>46204</v>
       </c>
@@ -7598,7 +7597,7 @@
       </c>
       <c r="AP38" s="88"/>
     </row>
-    <row r="39" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A39" s="81">
         <v>46205</v>
       </c>
@@ -7706,7 +7705,7 @@
       </c>
       <c r="AP39" s="88"/>
     </row>
-    <row r="40" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A40" s="81">
         <v>46205</v>
       </c>
@@ -7810,7 +7809,7 @@
       </c>
       <c r="AP40" s="88"/>
     </row>
-    <row r="41" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A41" s="81">
         <v>46205</v>
       </c>
@@ -7912,7 +7911,7 @@
       </c>
       <c r="AP41" s="88"/>
     </row>
-    <row r="42" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A42" s="81">
         <v>46205</v>
       </c>
@@ -8014,7 +8013,7 @@
       </c>
       <c r="AP42" s="88"/>
     </row>
-    <row r="43" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A43" s="81">
         <v>46205</v>
       </c>
@@ -8115,7 +8114,7 @@
       </c>
       <c r="AP43" s="88"/>
     </row>
-    <row r="44" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A44" s="81">
         <v>46205</v>
       </c>
@@ -8223,7 +8222,7 @@
       </c>
       <c r="AP44" s="88"/>
     </row>
-    <row r="45" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A45" s="81">
         <v>46205</v>
       </c>
@@ -8325,7 +8324,7 @@
       </c>
       <c r="AP45" s="88"/>
     </row>
-    <row r="46" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A46" s="81">
         <v>46205</v>
       </c>
@@ -8427,7 +8426,7 @@
       </c>
       <c r="AP46" s="88"/>
     </row>
-    <row r="47" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A47" s="81">
         <v>46205</v>
       </c>
@@ -8527,7 +8526,7 @@
       </c>
       <c r="AP47" s="88"/>
     </row>
-    <row r="48" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A48" s="81">
         <v>46205</v>
       </c>
@@ -8629,7 +8628,7 @@
       </c>
       <c r="AP48" s="88"/>
     </row>
-    <row r="49" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A49" s="81">
         <v>46205</v>
       </c>
@@ -8727,7 +8726,7 @@
       </c>
       <c r="AP49" s="88"/>
     </row>
-    <row r="50" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A50" s="81">
         <v>46205</v>
       </c>
@@ -8829,7 +8828,7 @@
       </c>
       <c r="AP50" s="88"/>
     </row>
-    <row r="51" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A51" s="81">
         <v>46205</v>
       </c>
@@ -8937,7 +8936,7 @@
       </c>
       <c r="AP51" s="88"/>
     </row>
-    <row r="52" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A52" s="81">
         <v>46205</v>
       </c>
@@ -9041,7 +9040,7 @@
       </c>
       <c r="AP52" s="88"/>
     </row>
-    <row r="53" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A53" s="81">
         <v>46205</v>
       </c>
@@ -9147,7 +9146,7 @@
       </c>
       <c r="AP53" s="88"/>
     </row>
-    <row r="54" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A54" s="81">
         <v>46205</v>
       </c>
@@ -9255,7 +9254,7 @@
       </c>
       <c r="AP54" s="88"/>
     </row>
-    <row r="55" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A55" s="81">
         <v>46205</v>
       </c>
@@ -9363,7 +9362,7 @@
       </c>
       <c r="AP55" s="88"/>
     </row>
-    <row r="56" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A56" s="81">
         <v>46205</v>
       </c>
@@ -9471,7 +9470,7 @@
       </c>
       <c r="AP56" s="88"/>
     </row>
-    <row r="57" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A57" s="81">
         <v>46205</v>
       </c>
@@ -9569,7 +9568,7 @@
       </c>
       <c r="AP57" s="88"/>
     </row>
-    <row r="58" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A58" s="81">
         <v>46205</v>
       </c>
@@ -9669,7 +9668,7 @@
       </c>
       <c r="AP58" s="88"/>
     </row>
-    <row r="59" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A59" s="81">
         <v>46205</v>
       </c>
@@ -9767,7 +9766,7 @@
       </c>
       <c r="AP59" s="88"/>
     </row>
-    <row r="60" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A60" s="81">
         <v>46205</v>
       </c>
@@ -9865,7 +9864,7 @@
       </c>
       <c r="AP60" s="88"/>
     </row>
-    <row r="61" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A61" s="81">
         <v>46205</v>
       </c>
@@ -9963,7 +9962,7 @@
       </c>
       <c r="AP61" s="88"/>
     </row>
-    <row r="62" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A62" s="81">
         <v>46205</v>
       </c>
@@ -10061,7 +10060,7 @@
       </c>
       <c r="AP62" s="88"/>
     </row>
-    <row r="63" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A63" s="81">
         <v>46205</v>
       </c>
@@ -10159,7 +10158,7 @@
       </c>
       <c r="AP63" s="88"/>
     </row>
-    <row r="64" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A64" s="81">
         <v>46205</v>
       </c>
@@ -10257,7 +10256,7 @@
       </c>
       <c r="AP64" s="88"/>
     </row>
-    <row r="65" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A65" s="81">
         <v>46205</v>
       </c>
@@ -10355,7 +10354,7 @@
       </c>
       <c r="AP65" s="88"/>
     </row>
-    <row r="66" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A66" s="81">
         <v>46205</v>
       </c>
@@ -10455,7 +10454,7 @@
       </c>
       <c r="AP66" s="88"/>
     </row>
-    <row r="67" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A67" s="81">
         <v>46205</v>
       </c>
@@ -10557,7 +10556,7 @@
       </c>
       <c r="AP67" s="88"/>
     </row>
-    <row r="68" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A68" s="81">
         <v>46205</v>
       </c>
@@ -10659,7 +10658,7 @@
       </c>
       <c r="AP68" s="88"/>
     </row>
-    <row r="69" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A69" s="81">
         <v>46205</v>
       </c>
@@ -10767,7 +10766,7 @@
       </c>
       <c r="AP69" s="88"/>
     </row>
-    <row r="70" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70" s="81">
         <v>46205</v>
       </c>
@@ -10873,7 +10872,7 @@
       </c>
       <c r="AP70" s="88"/>
     </row>
-    <row r="71" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A71" s="81">
         <v>46205</v>
       </c>
@@ -10971,7 +10970,7 @@
       </c>
       <c r="AP71" s="88"/>
     </row>
-    <row r="72" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A72" s="81">
         <v>46205</v>
       </c>
@@ -11069,7 +11068,7 @@
       </c>
       <c r="AP72" s="88"/>
     </row>
-    <row r="73" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A73" s="81">
         <v>46205</v>
       </c>
@@ -11899,7 +11898,7 @@
       </c>
       <c r="AP80" s="88"/>
     </row>
-    <row r="81" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A81" s="81">
         <v>46206</v>
       </c>
@@ -12001,7 +12000,7 @@
       </c>
       <c r="AP81" s="88"/>
     </row>
-    <row r="82" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A82" s="81">
         <v>46206</v>
       </c>
@@ -12099,7 +12098,7 @@
       </c>
       <c r="AP82" s="88"/>
     </row>
-    <row r="83" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A83" s="81">
         <v>46206</v>
       </c>
@@ -12201,7 +12200,7 @@
       </c>
       <c r="AP83" s="88"/>
     </row>
-    <row r="84" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A84" s="81">
         <v>46206</v>
       </c>
@@ -12301,7 +12300,7 @@
       </c>
       <c r="AP84" s="88"/>
     </row>
-    <row r="85" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A85" s="81">
         <v>46206</v>
       </c>
@@ -12403,7 +12402,7 @@
       </c>
       <c r="AP85" s="88"/>
     </row>
-    <row r="86" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A86" s="81">
         <v>46206</v>
       </c>
@@ -12505,7 +12504,7 @@
       </c>
       <c r="AP86" s="88"/>
     </row>
-    <row r="87" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A87" s="81">
         <v>46206</v>
       </c>
@@ -12605,7 +12604,7 @@
       </c>
       <c r="AP87" s="88"/>
     </row>
-    <row r="88" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A88" s="81">
         <v>46206</v>
       </c>
@@ -12707,7 +12706,7 @@
       </c>
       <c r="AP88" s="88"/>
     </row>
-    <row r="89" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A89" s="81">
         <v>46206</v>
       </c>
@@ -12809,7 +12808,7 @@
       </c>
       <c r="AP89" s="88"/>
     </row>
-    <row r="90" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A90" s="81">
         <v>46206</v>
       </c>
@@ -12907,7 +12906,7 @@
       </c>
       <c r="AP90" s="88"/>
     </row>
-    <row r="91" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A91" s="81">
         <v>46206</v>
       </c>
@@ -13009,7 +13008,7 @@
       </c>
       <c r="AP91" s="88"/>
     </row>
-    <row r="92" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A92" s="81">
         <v>46206</v>
       </c>
@@ -13111,7 +13110,7 @@
       </c>
       <c r="AP92" s="88"/>
     </row>
-    <row r="93" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A93" s="81">
         <v>46206</v>
       </c>
@@ -13215,7 +13214,7 @@
       </c>
       <c r="AP93" s="88"/>
     </row>
-    <row r="94" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A94" s="81">
         <v>46206</v>
       </c>
@@ -13313,7 +13312,7 @@
       </c>
       <c r="AP94" s="88"/>
     </row>
-    <row r="95" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A95" s="81">
         <v>46206</v>
       </c>
@@ -13421,7 +13420,7 @@
       </c>
       <c r="AP95" s="88"/>
     </row>
-    <row r="96" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A96" s="81">
         <v>46206</v>
       </c>
@@ -13525,7 +13524,7 @@
       </c>
       <c r="AP96" s="88"/>
     </row>
-    <row r="97" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A97" s="81">
         <v>46206</v>
       </c>
@@ -13629,7 +13628,7 @@
       </c>
       <c r="AP97" s="88"/>
     </row>
-    <row r="98" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A98" s="81">
         <v>46206</v>
       </c>
@@ -13727,7 +13726,7 @@
       </c>
       <c r="AP98" s="88"/>
     </row>
-    <row r="99" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A99" s="81">
         <v>46206</v>
       </c>
@@ -13827,7 +13826,7 @@
       </c>
       <c r="AP99" s="88"/>
     </row>
-    <row r="100" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A100" s="81">
         <v>46206</v>
       </c>
@@ -13925,7 +13924,7 @@
       </c>
       <c r="AP100" s="88"/>
     </row>
-    <row r="101" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A101" s="81">
         <v>46206</v>
       </c>
@@ -14023,7 +14022,7 @@
       </c>
       <c r="AP101" s="88"/>
     </row>
-    <row r="102" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A102" s="81">
         <v>46206</v>
       </c>
@@ -14125,7 +14124,7 @@
       </c>
       <c r="AP102" s="88"/>
     </row>
-    <row r="103" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A103" s="81">
         <v>46206</v>
       </c>
@@ -14233,7 +14232,7 @@
       </c>
       <c r="AP103" s="88"/>
     </row>
-    <row r="104" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A104" s="81">
         <v>46206</v>
       </c>
@@ -14335,7 +14334,7 @@
       </c>
       <c r="AP104" s="88"/>
     </row>
-    <row r="105" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A105" s="81">
         <v>46206</v>
       </c>
@@ -14433,7 +14432,7 @@
       </c>
       <c r="AP105" s="88"/>
     </row>
-    <row r="106" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A106" s="81">
         <v>46206</v>
       </c>
@@ -14531,7 +14530,7 @@
       </c>
       <c r="AP106" s="88"/>
     </row>
-    <row r="107" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A107" s="81">
         <v>46206</v>
       </c>
@@ -14633,7 +14632,7 @@
       </c>
       <c r="AP107" s="88"/>
     </row>
-    <row r="108" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A108" s="81">
         <v>46206</v>
       </c>
@@ -14735,7 +14734,7 @@
       </c>
       <c r="AP108" s="88"/>
     </row>
-    <row r="109" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A109" s="81">
         <v>46206</v>
       </c>
@@ -14837,7 +14836,7 @@
       </c>
       <c r="AP109" s="88"/>
     </row>
-    <row r="110" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A110" s="81">
         <v>46206</v>
       </c>
@@ -14939,7 +14938,7 @@
       </c>
       <c r="AP110" s="88"/>
     </row>
-    <row r="111" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A111" s="81">
         <v>46206</v>
       </c>
@@ -15037,7 +15036,7 @@
       </c>
       <c r="AP111" s="88"/>
     </row>
-    <row r="112" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A112" s="81">
         <v>46206</v>
       </c>
@@ -15141,7 +15140,7 @@
       </c>
       <c r="AP112" s="88"/>
     </row>
-    <row r="113" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A113" s="81">
         <v>46206</v>
       </c>
@@ -15243,7 +15242,7 @@
       </c>
       <c r="AP113" s="88"/>
     </row>
-    <row r="114" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A114" s="81">
         <v>46206</v>
       </c>
@@ -15343,7 +15342,7 @@
       </c>
       <c r="AP114" s="88"/>
     </row>
-    <row r="115" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A115" s="81">
         <v>46206</v>
       </c>
@@ -15445,7 +15444,7 @@
       </c>
       <c r="AP115" s="88"/>
     </row>
-    <row r="116" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A116" s="81">
         <v>46206</v>
       </c>
@@ -15549,7 +15548,7 @@
       </c>
       <c r="AP116" s="88"/>
     </row>
-    <row r="117" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A117" s="81">
         <v>46207</v>
       </c>
@@ -15629,7 +15628,7 @@
       <c r="AL117" s="102"/>
       <c r="AP117" s="105"/>
     </row>
-    <row r="118" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A118" s="81">
         <v>46207</v>
       </c>
@@ -15731,7 +15730,7 @@
       </c>
       <c r="AP118" s="88"/>
     </row>
-    <row r="119" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A119" s="81">
         <v>46207</v>
       </c>
@@ -15835,7 +15834,7 @@
       </c>
       <c r="AP119" s="88"/>
     </row>
-    <row r="120" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A120" s="81">
         <v>46207</v>
       </c>
@@ -15939,7 +15938,7 @@
       </c>
       <c r="AP120" s="88"/>
     </row>
-    <row r="121" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A121" s="81">
         <v>46207</v>
       </c>
@@ -16041,7 +16040,7 @@
       </c>
       <c r="AP121" s="88"/>
     </row>
-    <row r="122" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A122" s="81">
         <v>46207</v>
       </c>
@@ -16145,7 +16144,7 @@
       </c>
       <c r="AP122" s="88"/>
     </row>
-    <row r="123" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A123" s="81">
         <v>46207</v>
       </c>
@@ -16253,7 +16252,7 @@
       </c>
       <c r="AP123" s="88"/>
     </row>
-    <row r="124" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A124" s="81">
         <v>46207</v>
       </c>
@@ -16355,7 +16354,7 @@
       </c>
       <c r="AP124" s="88"/>
     </row>
-    <row r="125" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A125" s="81">
         <v>46207</v>
       </c>
@@ -16457,7 +16456,7 @@
       </c>
       <c r="AP125" s="88"/>
     </row>
-    <row r="126" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A126" s="81">
         <v>46207</v>
       </c>
@@ -16557,7 +16556,7 @@
       </c>
       <c r="AP126" s="88"/>
     </row>
-    <row r="127" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A127" s="81">
         <v>46207</v>
       </c>
@@ -16655,7 +16654,7 @@
       </c>
       <c r="AP127" s="88"/>
     </row>
-    <row r="128" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A128" s="81">
         <v>46207</v>
       </c>
@@ -16753,7 +16752,7 @@
       </c>
       <c r="AP128" s="88"/>
     </row>
-    <row r="129" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A129" s="81">
         <v>46207</v>
       </c>
@@ -16851,7 +16850,7 @@
       </c>
       <c r="AP129" s="88"/>
     </row>
-    <row r="130" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A130" s="81">
         <v>46207</v>
       </c>
@@ -16949,7 +16948,7 @@
       </c>
       <c r="AP130" s="88"/>
     </row>
-    <row r="131" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A131" s="81">
         <v>46207</v>
       </c>
@@ -17047,7 +17046,7 @@
       </c>
       <c r="AP131" s="88"/>
     </row>
-    <row r="132" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A132" s="81">
         <v>46207</v>
       </c>
@@ -17145,7 +17144,7 @@
       </c>
       <c r="AP132" s="88"/>
     </row>
-    <row r="133" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A133" s="81">
         <v>46207</v>
       </c>
@@ -17243,7 +17242,7 @@
       </c>
       <c r="AP133" s="88"/>
     </row>
-    <row r="134" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A134" s="81">
         <v>46207</v>
       </c>
@@ -17347,7 +17346,7 @@
       </c>
       <c r="AP134" s="88"/>
     </row>
-    <row r="135" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A135" s="81">
         <v>46207</v>
       </c>
@@ -17447,7 +17446,7 @@
       </c>
       <c r="AP135" s="88"/>
     </row>
-    <row r="136" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A136" s="81">
         <v>46207</v>
       </c>
@@ -17549,7 +17548,7 @@
       </c>
       <c r="AP136" s="88"/>
     </row>
-    <row r="137" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A137" s="81">
         <v>46207</v>
       </c>
@@ -17653,7 +17652,7 @@
       </c>
       <c r="AP137" s="88"/>
     </row>
-    <row r="138" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A138" s="81">
         <v>46207</v>
       </c>
@@ -17751,7 +17750,7 @@
       </c>
       <c r="AP138" s="88"/>
     </row>
-    <row r="139" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A139" s="81">
         <v>46207</v>
       </c>
@@ -17853,7 +17852,7 @@
       </c>
       <c r="AP139" s="88"/>
     </row>
-    <row r="140" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A140" s="81">
         <v>46207</v>
       </c>
@@ -17955,7 +17954,7 @@
       </c>
       <c r="AP140" s="88"/>
     </row>
-    <row r="141" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A141" s="81">
         <v>46207</v>
       </c>
@@ -18059,7 +18058,7 @@
       </c>
       <c r="AP141" s="88"/>
     </row>
-    <row r="142" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A142" s="81">
         <v>46207</v>
       </c>
@@ -18157,7 +18156,7 @@
       </c>
       <c r="AP142" s="88"/>
     </row>
-    <row r="143" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A143" s="81">
         <v>46207</v>
       </c>
@@ -18259,7 +18258,7 @@
       </c>
       <c r="AP143" s="88"/>
     </row>
-    <row r="144" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A144" s="81">
         <v>46209</v>
       </c>
@@ -18361,7 +18360,7 @@
       </c>
       <c r="AP144" s="88"/>
     </row>
-    <row r="145" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A145" s="81">
         <v>46209</v>
       </c>
@@ -18463,7 +18462,7 @@
       </c>
       <c r="AP145" s="88"/>
     </row>
-    <row r="146" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A146" s="81">
         <v>46209</v>
       </c>
@@ -18569,7 +18568,7 @@
       </c>
       <c r="AP146" s="88"/>
     </row>
-    <row r="147" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A147" s="81">
         <v>46209</v>
       </c>
@@ -18667,7 +18666,7 @@
       </c>
       <c r="AP147" s="88"/>
     </row>
-    <row r="148" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A148" s="81">
         <v>46209</v>
       </c>
@@ -18767,7 +18766,7 @@
       </c>
       <c r="AP148" s="88"/>
     </row>
-    <row r="149" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A149" s="81">
         <v>46209</v>
       </c>
@@ -18869,7 +18868,7 @@
       </c>
       <c r="AP149" s="88"/>
     </row>
-    <row r="150" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A150" s="81">
         <v>46209</v>
       </c>
@@ -18967,7 +18966,7 @@
       </c>
       <c r="AP150" s="88"/>
     </row>
-    <row r="151" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A151" s="81">
         <v>46209</v>
       </c>
@@ -19069,7 +19068,7 @@
       </c>
       <c r="AP151" s="88"/>
     </row>
-    <row r="152" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A152" s="81">
         <v>46209</v>
       </c>
@@ -19171,7 +19170,7 @@
       </c>
       <c r="AP152" s="88"/>
     </row>
-    <row r="153" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A153" s="81">
         <v>46209</v>
       </c>
@@ -19273,7 +19272,7 @@
       </c>
       <c r="AP153" s="88"/>
     </row>
-    <row r="154" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A154" s="81">
         <v>46209</v>
       </c>
@@ -19379,7 +19378,7 @@
       </c>
       <c r="AP154" s="88"/>
     </row>
-    <row r="155" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A155" s="81">
         <v>46209</v>
       </c>
@@ -19487,7 +19486,7 @@
       </c>
       <c r="AP155" s="88"/>
     </row>
-    <row r="156" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A156" s="81">
         <v>46209</v>
       </c>
@@ -19589,7 +19588,7 @@
       </c>
       <c r="AP156" s="88"/>
     </row>
-    <row r="157" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A157" s="81">
         <v>46209</v>
       </c>
@@ -19695,7 +19694,7 @@
       </c>
       <c r="AP157" s="88"/>
     </row>
-    <row r="158" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A158" s="81">
         <v>46209</v>
       </c>
@@ -19793,7 +19792,7 @@
       </c>
       <c r="AP158" s="88"/>
     </row>
-    <row r="159" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A159" s="81">
         <v>46209</v>
       </c>
@@ -19891,7 +19890,7 @@
       </c>
       <c r="AP159" s="88"/>
     </row>
-    <row r="160" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A160" s="81">
         <v>46209</v>
       </c>
@@ -19989,7 +19988,7 @@
       </c>
       <c r="AP160" s="88"/>
     </row>
-    <row r="161" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A161" s="81">
         <v>46209</v>
       </c>
@@ -20093,7 +20092,7 @@
       </c>
       <c r="AP161" s="88"/>
     </row>
-    <row r="162" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A162" s="81">
         <v>46209</v>
       </c>
@@ -20191,7 +20190,7 @@
       </c>
       <c r="AP162" s="88"/>
     </row>
-    <row r="163" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A163" s="81">
         <v>46209</v>
       </c>
@@ -20289,7 +20288,7 @@
       </c>
       <c r="AP163" s="88"/>
     </row>
-    <row r="164" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A164" s="81">
         <v>46209</v>
       </c>
@@ -20387,7 +20386,7 @@
       </c>
       <c r="AP164" s="88"/>
     </row>
-    <row r="165" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A165" s="81">
         <v>46209</v>
       </c>
@@ -20485,7 +20484,7 @@
       </c>
       <c r="AP165" s="88"/>
     </row>
-    <row r="166" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A166" s="81">
         <v>46209</v>
       </c>
@@ -20583,7 +20582,7 @@
       </c>
       <c r="AP166" s="88"/>
     </row>
-    <row r="167" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A167" s="81">
         <v>46209</v>
       </c>
@@ -20687,7 +20686,7 @@
       </c>
       <c r="AP167" s="88"/>
     </row>
-    <row r="168" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A168" s="81">
         <v>46210</v>
       </c>
@@ -20787,7 +20786,7 @@
       </c>
       <c r="AP168" s="88"/>
     </row>
-    <row r="169" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A169" s="81">
         <v>46210</v>
       </c>
@@ -20887,7 +20886,7 @@
       </c>
       <c r="AP169" s="88"/>
     </row>
-    <row r="170" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A170" s="81">
         <v>46210</v>
       </c>
@@ -20985,7 +20984,7 @@
       </c>
       <c r="AP170" s="88"/>
     </row>
-    <row r="171" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A171" s="81">
         <v>46210</v>
       </c>
@@ -21093,7 +21092,7 @@
       </c>
       <c r="AP171" s="88"/>
     </row>
-    <row r="172" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A172" s="81">
         <v>46210</v>
       </c>
@@ -21191,7 +21190,7 @@
       </c>
       <c r="AP172" s="88"/>
     </row>
-    <row r="173" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A173" s="81">
         <v>46210</v>
       </c>
@@ -21293,7 +21292,7 @@
       </c>
       <c r="AP173" s="88"/>
     </row>
-    <row r="174" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A174" s="81">
         <v>46210</v>
       </c>
@@ -21395,7 +21394,7 @@
       </c>
       <c r="AP174" s="88"/>
     </row>
-    <row r="175" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A175" s="81">
         <v>46210</v>
       </c>
@@ -21497,7 +21496,7 @@
       </c>
       <c r="AP175" s="88"/>
     </row>
-    <row r="176" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A176" s="81">
         <v>46210</v>
       </c>
@@ -21599,7 +21598,7 @@
       </c>
       <c r="AP176" s="88"/>
     </row>
-    <row r="177" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A177" s="81">
         <v>46210</v>
       </c>
@@ -21699,7 +21698,7 @@
       </c>
       <c r="AP177" s="88"/>
     </row>
-    <row r="178" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A178" s="81">
         <v>46210</v>
       </c>
@@ -21799,7 +21798,7 @@
       </c>
       <c r="AP178" s="88"/>
     </row>
-    <row r="179" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A179" s="81">
         <v>46210</v>
       </c>
@@ -21897,7 +21896,7 @@
       </c>
       <c r="AP179" s="88"/>
     </row>
-    <row r="180" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A180" s="81">
         <v>46210</v>
       </c>
@@ -21999,7 +21998,7 @@
       </c>
       <c r="AP180" s="88"/>
     </row>
-    <row r="181" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A181" s="81">
         <v>46210</v>
       </c>
@@ -22103,7 +22102,7 @@
       </c>
       <c r="AP181" s="88"/>
     </row>
-    <row r="182" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A182" s="81">
         <v>46210</v>
       </c>
@@ -22209,7 +22208,7 @@
       </c>
       <c r="AP182" s="88"/>
     </row>
-    <row r="183" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A183" s="81">
         <v>46210</v>
       </c>
@@ -22311,7 +22310,7 @@
       </c>
       <c r="AP183" s="88"/>
     </row>
-    <row r="184" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A184" s="81">
         <v>46210</v>
       </c>
@@ -22413,7 +22412,7 @@
       </c>
       <c r="AP184" s="88"/>
     </row>
-    <row r="185" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A185" s="81">
         <v>46210</v>
       </c>
@@ -22515,7 +22514,7 @@
       </c>
       <c r="AP185" s="88"/>
     </row>
-    <row r="186" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A186" s="81">
         <v>46210</v>
       </c>
@@ -22613,7 +22612,7 @@
       </c>
       <c r="AP186" s="88"/>
     </row>
-    <row r="187" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A187" s="81">
         <v>46210</v>
       </c>
@@ -22711,7 +22710,7 @@
       </c>
       <c r="AP187" s="88"/>
     </row>
-    <row r="188" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A188" s="81">
         <v>46210</v>
       </c>
@@ -22809,7 +22808,7 @@
       </c>
       <c r="AP188" s="88"/>
     </row>
-    <row r="189" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A189" s="81">
         <v>46210</v>
       </c>
@@ -22907,7 +22906,7 @@
       </c>
       <c r="AP189" s="88"/>
     </row>
-    <row r="190" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A190" s="81">
         <v>46210</v>
       </c>
@@ -23011,7 +23010,7 @@
       </c>
       <c r="AP190" s="88"/>
     </row>
-    <row r="191" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A191" s="81">
         <v>46210</v>
       </c>
@@ -23109,7 +23108,7 @@
       </c>
       <c r="AP191" s="88"/>
     </row>
-    <row r="192" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A192" s="81">
         <v>46210</v>
       </c>
@@ -23207,7 +23206,7 @@
       </c>
       <c r="AP192" s="88"/>
     </row>
-    <row r="193" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A193" s="81">
         <v>46210</v>
       </c>
@@ -23305,7 +23304,7 @@
       </c>
       <c r="AP193" s="88"/>
     </row>
-    <row r="194" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A194" s="81">
         <v>46210</v>
       </c>
@@ -23403,7 +23402,7 @@
       </c>
       <c r="AP194" s="88"/>
     </row>
-    <row r="195" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A195" s="81">
         <v>46210</v>
       </c>
@@ -23501,7 +23500,7 @@
       </c>
       <c r="AP195" s="88"/>
     </row>
-    <row r="196" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A196" s="81">
         <v>46210</v>
       </c>
@@ -23599,7 +23598,7 @@
       </c>
       <c r="AP196" s="88"/>
     </row>
-    <row r="197" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A197" s="81">
         <v>46210</v>
       </c>
@@ -23701,7 +23700,7 @@
       </c>
       <c r="AP197" s="88"/>
     </row>
-    <row r="198" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A198" s="81">
         <v>46210</v>
       </c>
@@ -23799,7 +23798,7 @@
       </c>
       <c r="AP198" s="88"/>
     </row>
-    <row r="199" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A199" s="81">
         <v>46210</v>
       </c>
@@ -23897,7 +23896,7 @@
       </c>
       <c r="AP199" s="88"/>
     </row>
-    <row r="200" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A200" s="81">
         <v>46210</v>
       </c>
@@ -23995,7 +23994,7 @@
       </c>
       <c r="AP200" s="88"/>
     </row>
-    <row r="201" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A201" s="81">
         <v>46210</v>
       </c>
@@ -24093,7 +24092,7 @@
       </c>
       <c r="AP201" s="88"/>
     </row>
-    <row r="202" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A202" s="81">
         <v>46211</v>
       </c>
@@ -24191,7 +24190,7 @@
       </c>
       <c r="AP202" s="88"/>
     </row>
-    <row r="203" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A203" s="81">
         <v>46211</v>
       </c>
@@ -24289,7 +24288,7 @@
       </c>
       <c r="AP203" s="88"/>
     </row>
-    <row r="204" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A204" s="81">
         <v>46211</v>
       </c>
@@ -24389,7 +24388,7 @@
       </c>
       <c r="AP204" s="88"/>
     </row>
-    <row r="205" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A205" s="81">
         <v>46211</v>
       </c>
@@ -24491,7 +24490,7 @@
       </c>
       <c r="AP205" s="88"/>
     </row>
-    <row r="206" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A206" s="81">
         <v>46211</v>
       </c>
@@ -24593,7 +24592,7 @@
       </c>
       <c r="AP206" s="88"/>
     </row>
-    <row r="207" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A207" s="81">
         <v>46211</v>
       </c>
@@ -24697,7 +24696,7 @@
       </c>
       <c r="AP207" s="88"/>
     </row>
-    <row r="208" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A208" s="81">
         <v>46211</v>
       </c>
@@ -24795,7 +24794,7 @@
       </c>
       <c r="AP208" s="88"/>
     </row>
-    <row r="209" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A209" s="81">
         <v>46211</v>
       </c>
@@ -24893,7 +24892,7 @@
       </c>
       <c r="AP209" s="88"/>
     </row>
-    <row r="210" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A210" s="81">
         <v>46211</v>
       </c>
@@ -24991,7 +24990,7 @@
       </c>
       <c r="AP210" s="88"/>
     </row>
-    <row r="211" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A211" s="81">
         <v>46211</v>
       </c>
@@ -25089,7 +25088,7 @@
       </c>
       <c r="AP211" s="88"/>
     </row>
-    <row r="212" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A212" s="81">
         <v>46211</v>
       </c>
@@ -25191,7 +25190,7 @@
       </c>
       <c r="AP212" s="88"/>
     </row>
-    <row r="213" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A213" s="81">
         <v>46211</v>
       </c>
@@ -25295,7 +25294,7 @@
       </c>
       <c r="AP213" s="88"/>
     </row>
-    <row r="214" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A214" s="81">
         <v>46211</v>
       </c>
@@ -25399,7 +25398,7 @@
       </c>
       <c r="AP214" s="88"/>
     </row>
-    <row r="215" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A215" s="81">
         <v>46211</v>
       </c>
@@ -25497,7 +25496,7 @@
       </c>
       <c r="AP215" s="88"/>
     </row>
-    <row r="216" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A216" s="81">
         <v>46211</v>
       </c>
@@ -25595,7 +25594,7 @@
       </c>
       <c r="AP216" s="88"/>
     </row>
-    <row r="217" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A217" s="81">
         <v>46211</v>
       </c>
@@ -25697,7 +25696,7 @@
       </c>
       <c r="AP217" s="88"/>
     </row>
-    <row r="218" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A218" s="81">
         <v>46211</v>
       </c>
@@ -25795,7 +25794,7 @@
       </c>
       <c r="AP218" s="88"/>
     </row>
-    <row r="219" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A219" s="81">
         <v>46211</v>
       </c>
@@ -25897,7 +25896,7 @@
       </c>
       <c r="AP219" s="88"/>
     </row>
-    <row r="220" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A220" s="81">
         <v>46211</v>
       </c>
@@ -26001,7 +26000,7 @@
       </c>
       <c r="AP220" s="88"/>
     </row>
-    <row r="221" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A221" s="81">
         <v>46211</v>
       </c>
@@ -26099,7 +26098,7 @@
       </c>
       <c r="AP221" s="88"/>
     </row>
-    <row r="222" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A222" s="81">
         <v>46211</v>
       </c>
@@ -26197,7 +26196,7 @@
       </c>
       <c r="AP222" s="88"/>
     </row>
-    <row r="223" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A223" s="81">
         <v>46211</v>
       </c>
@@ -26295,7 +26294,7 @@
       </c>
       <c r="AP223" s="88"/>
     </row>
-    <row r="224" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A224" s="81">
         <v>46211</v>
       </c>
@@ -26393,7 +26392,7 @@
       </c>
       <c r="AP224" s="88"/>
     </row>
-    <row r="225" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A225" s="81">
         <v>46211</v>
       </c>
@@ -26491,7 +26490,7 @@
       </c>
       <c r="AP225" s="88"/>
     </row>
-    <row r="226" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A226" s="81">
         <v>46211</v>
       </c>
@@ -26589,7 +26588,7 @@
       </c>
       <c r="AP226" s="88"/>
     </row>
-    <row r="227" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A227" s="81">
         <v>46211</v>
       </c>
@@ -26693,7 +26692,7 @@
       </c>
       <c r="AP227" s="88"/>
     </row>
-    <row r="228" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A228" s="81">
         <v>46211</v>
       </c>
@@ -27101,7 +27100,7 @@
       </c>
       <c r="AP231" s="88"/>
     </row>
-    <row r="232" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A232" s="81">
         <v>46212</v>
       </c>
@@ -27199,7 +27198,7 @@
       </c>
       <c r="AP232" s="88"/>
     </row>
-    <row r="233" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A233" s="81">
         <v>46212</v>
       </c>
@@ -27301,7 +27300,7 @@
       </c>
       <c r="AP233" s="88"/>
     </row>
-    <row r="234" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A234" s="81">
         <v>46212</v>
       </c>
@@ -27401,7 +27400,7 @@
       </c>
       <c r="AP234" s="88"/>
     </row>
-    <row r="235" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A235" s="81">
         <v>46212</v>
       </c>
@@ -27509,7 +27508,7 @@
       </c>
       <c r="AP235" s="88"/>
     </row>
-    <row r="236" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A236" s="81">
         <v>46212</v>
       </c>
@@ -27613,7 +27612,7 @@
       </c>
       <c r="AP236" s="88"/>
     </row>
-    <row r="237" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A237" s="81">
         <v>46212</v>
       </c>
@@ -27713,7 +27712,7 @@
       </c>
       <c r="AP237" s="88"/>
     </row>
-    <row r="238" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A238" s="81">
         <v>46212</v>
       </c>
@@ -27815,7 +27814,7 @@
       </c>
       <c r="AP238" s="88"/>
     </row>
-    <row r="239" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A239" s="81">
         <v>46212</v>
       </c>
@@ -27917,7 +27916,7 @@
       </c>
       <c r="AP239" s="88"/>
     </row>
-    <row r="240" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A240" s="81">
         <v>46212</v>
       </c>
@@ -28017,7 +28016,7 @@
       </c>
       <c r="AP240" s="88"/>
     </row>
-    <row r="241" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A241" s="81">
         <v>46212</v>
       </c>
@@ -28119,7 +28118,7 @@
       </c>
       <c r="AP241" s="88"/>
     </row>
-    <row r="242" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A242" s="81">
         <v>46212</v>
       </c>
@@ -28217,7 +28216,7 @@
       </c>
       <c r="AP242" s="88"/>
     </row>
-    <row r="243" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A243" s="81">
         <v>46212</v>
       </c>
@@ -28319,7 +28318,7 @@
       </c>
       <c r="AP243" s="88"/>
     </row>
-    <row r="244" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A244" s="81">
         <v>46212</v>
       </c>
@@ -28419,7 +28418,7 @@
       </c>
       <c r="AP244" s="88"/>
     </row>
-    <row r="245" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A245" s="81">
         <v>46212</v>
       </c>
@@ -28517,7 +28516,7 @@
       </c>
       <c r="AP245" s="88"/>
     </row>
-    <row r="246" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A246" s="81">
         <v>46212</v>
       </c>
@@ -28619,7 +28618,7 @@
       </c>
       <c r="AP246" s="88"/>
     </row>
-    <row r="247" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A247" s="81">
         <v>46212</v>
       </c>
@@ -28721,7 +28720,7 @@
       </c>
       <c r="AP247" s="88"/>
     </row>
-    <row r="248" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A248" s="81">
         <v>46212</v>
       </c>
@@ -28823,7 +28822,7 @@
       </c>
       <c r="AP248" s="88"/>
     </row>
-    <row r="249" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A249" s="81">
         <v>46212</v>
       </c>
@@ -28925,7 +28924,7 @@
       </c>
       <c r="AP249" s="88"/>
     </row>
-    <row r="250" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A250" s="81">
         <v>46212</v>
       </c>
@@ -29025,7 +29024,7 @@
       </c>
       <c r="AP250" s="88"/>
     </row>
-    <row r="251" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A251" s="81">
         <v>46212</v>
       </c>
@@ -29125,7 +29124,7 @@
       </c>
       <c r="AP251" s="88"/>
     </row>
-    <row r="252" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A252" s="81">
         <v>46212</v>
       </c>
@@ -29227,7 +29226,7 @@
       </c>
       <c r="AP252" s="88"/>
     </row>
-    <row r="253" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A253" s="81">
         <v>46212</v>
       </c>
@@ -29331,7 +29330,7 @@
       </c>
       <c r="AP253" s="88"/>
     </row>
-    <row r="254" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A254" s="81">
         <v>46212</v>
       </c>
@@ -29433,7 +29432,7 @@
       </c>
       <c r="AP254" s="88"/>
     </row>
-    <row r="255" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A255" s="81">
         <v>46212</v>
       </c>
@@ -30159,7 +30158,7 @@
       </c>
       <c r="AP261" s="88"/>
     </row>
-    <row r="262" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A262" s="81">
         <v>46213</v>
       </c>
@@ -30261,7 +30260,7 @@
       </c>
       <c r="AP262" s="88"/>
     </row>
-    <row r="263" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A263" s="81">
         <v>46213</v>
       </c>
@@ -30359,7 +30358,7 @@
       </c>
       <c r="AP263" s="88"/>
     </row>
-    <row r="264" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A264" s="81">
         <v>46213</v>
       </c>
@@ -30459,7 +30458,7 @@
       </c>
       <c r="AP264" s="88"/>
     </row>
-    <row r="265" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A265" s="81">
         <v>46213</v>
       </c>
@@ -30559,7 +30558,7 @@
       </c>
       <c r="AP265" s="88"/>
     </row>
-    <row r="266" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A266" s="81">
         <v>46213</v>
       </c>
@@ -30661,7 +30660,7 @@
       </c>
       <c r="AP266" s="88"/>
     </row>
-    <row r="267" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A267" s="81">
         <v>46213</v>
       </c>
@@ -30769,7 +30768,7 @@
       </c>
       <c r="AP267" s="88"/>
     </row>
-    <row r="268" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A268" s="81">
         <v>46213</v>
       </c>
@@ -30871,7 +30870,7 @@
       </c>
       <c r="AP268" s="88"/>
     </row>
-    <row r="269" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A269" s="81">
         <v>46213</v>
       </c>
@@ -30973,7 +30972,7 @@
       </c>
       <c r="AP269" s="88"/>
     </row>
-    <row r="270" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A270" s="81">
         <v>46213</v>
       </c>
@@ -31071,7 +31070,7 @@
       </c>
       <c r="AP270" s="88"/>
     </row>
-    <row r="271" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A271" s="81">
         <v>46213</v>
       </c>
@@ -31169,7 +31168,7 @@
       </c>
       <c r="AP271" s="88"/>
     </row>
-    <row r="272" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A272" s="81">
         <v>46213</v>
       </c>
@@ -31267,7 +31266,7 @@
       </c>
       <c r="AP272" s="88"/>
     </row>
-    <row r="273" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A273" s="81">
         <v>46213</v>
       </c>
@@ -31365,7 +31364,7 @@
       </c>
       <c r="AP273" s="88"/>
     </row>
-    <row r="274" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A274" s="81">
         <v>46213</v>
       </c>
@@ -31463,7 +31462,7 @@
       </c>
       <c r="AP274" s="88"/>
     </row>
-    <row r="275" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A275" s="81">
         <v>46213</v>
       </c>
@@ -31571,7 +31570,7 @@
       </c>
       <c r="AP275" s="88"/>
     </row>
-    <row r="276" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A276" s="81">
         <v>46213</v>
       </c>
@@ -31669,7 +31668,7 @@
       </c>
       <c r="AP276" s="88"/>
     </row>
-    <row r="277" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A277" s="81">
         <v>46213</v>
       </c>
@@ -31767,7 +31766,7 @@
       </c>
       <c r="AP277" s="88"/>
     </row>
-    <row r="278" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A278" s="81">
         <v>46213</v>
       </c>
@@ -31865,7 +31864,7 @@
       </c>
       <c r="AP278" s="88"/>
     </row>
-    <row r="279" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A279" s="81">
         <v>46214</v>
       </c>
@@ -31967,7 +31966,7 @@
       </c>
       <c r="AP279" s="88"/>
     </row>
-    <row r="280" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A280" s="81">
         <v>46214</v>
       </c>
@@ -32073,7 +32072,7 @@
       </c>
       <c r="AP280" s="88"/>
     </row>
-    <row r="281" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A281" s="81">
         <v>46214</v>
       </c>
@@ -32175,7 +32174,7 @@
       </c>
       <c r="AP281" s="88"/>
     </row>
-    <row r="282" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A282" s="81">
         <v>46214</v>
       </c>
@@ -32273,7 +32272,7 @@
       </c>
       <c r="AP282" s="88"/>
     </row>
-    <row r="283" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A283" s="81">
         <v>46214</v>
       </c>
@@ -32381,7 +32380,7 @@
       </c>
       <c r="AP283" s="88"/>
     </row>
-    <row r="284" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A284" s="81">
         <v>46214</v>
       </c>
@@ -32481,7 +32480,7 @@
       </c>
       <c r="AP284" s="88"/>
     </row>
-    <row r="285" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A285" s="81">
         <v>46214</v>
       </c>
@@ -32581,7 +32580,7 @@
       </c>
       <c r="AP285" s="88"/>
     </row>
-    <row r="286" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A286" s="81">
         <v>46214</v>
       </c>
@@ -32683,7 +32682,7 @@
       </c>
       <c r="AP286" s="88"/>
     </row>
-    <row r="287" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A287" s="81">
         <v>46214</v>
       </c>
@@ -32791,7 +32790,7 @@
       </c>
       <c r="AP287" s="88"/>
     </row>
-    <row r="288" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A288" s="81">
         <v>46214</v>
       </c>
@@ -32899,7 +32898,7 @@
       </c>
       <c r="AP288" s="88"/>
     </row>
-    <row r="289" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A289" s="81">
         <v>46214</v>
       </c>
@@ -33001,7 +33000,7 @@
       </c>
       <c r="AP289" s="88"/>
     </row>
-    <row r="290" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A290" s="81">
         <v>46214</v>
       </c>
@@ -33103,7 +33102,7 @@
       </c>
       <c r="AP290" s="88"/>
     </row>
-    <row r="291" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A291" s="81">
         <v>46214</v>
       </c>
@@ -33205,7 +33204,7 @@
       </c>
       <c r="AP291" s="88"/>
     </row>
-    <row r="292" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A292" s="81">
         <v>46214</v>
       </c>
@@ -33307,7 +33306,7 @@
       </c>
       <c r="AP292" s="88"/>
     </row>
-    <row r="293" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A293" s="81">
         <v>46214</v>
       </c>
@@ -33407,7 +33406,7 @@
       </c>
       <c r="AP293" s="88"/>
     </row>
-    <row r="294" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A294" s="81">
         <v>46214</v>
       </c>
@@ -33513,7 +33512,7 @@
       </c>
       <c r="AP294" s="88"/>
     </row>
-    <row r="295" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A295" s="81">
         <v>46214</v>
       </c>
@@ -33613,7 +33612,7 @@
       </c>
       <c r="AP295" s="88"/>
     </row>
-    <row r="296" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A296" s="81">
         <v>46214</v>
       </c>
@@ -33713,7 +33712,7 @@
       </c>
       <c r="AP296" s="88"/>
     </row>
-    <row r="297" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A297" s="81">
         <v>46214</v>
       </c>
@@ -33817,7 +33816,7 @@
       </c>
       <c r="AP297" s="88"/>
     </row>
-    <row r="298" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A298" s="81">
         <v>46214</v>
       </c>
@@ -33915,7 +33914,7 @@
       </c>
       <c r="AP298" s="88"/>
     </row>
-    <row r="299" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A299" s="81">
         <v>46214</v>
       </c>
@@ -34017,7 +34016,7 @@
       </c>
       <c r="AP299" s="88"/>
     </row>
-    <row r="300" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A300" s="81">
         <v>46214</v>
       </c>
@@ -34125,7 +34124,7 @@
       </c>
       <c r="AP300" s="88"/>
     </row>
-    <row r="301" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A301" s="81">
         <v>46214</v>
       </c>
@@ -34227,7 +34226,7 @@
       </c>
       <c r="AP301" s="88"/>
     </row>
-    <row r="302" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A302" s="81">
         <v>46214</v>
       </c>
@@ -34327,7 +34326,7 @@
       </c>
       <c r="AP302" s="88"/>
     </row>
-    <row r="303" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A303" s="81">
         <v>46214</v>
       </c>
@@ -34425,7 +34424,7 @@
       </c>
       <c r="AP303" s="88"/>
     </row>
-    <row r="304" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A304" s="81">
         <v>46214</v>
       </c>
@@ -34523,7 +34522,7 @@
       </c>
       <c r="AP304" s="88"/>
     </row>
-    <row r="305" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A305" s="81">
         <v>46214</v>
       </c>
@@ -34621,7 +34620,7 @@
       </c>
       <c r="AP305" s="88"/>
     </row>
-    <row r="306" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A306" s="81">
         <v>46214</v>
       </c>
@@ -34719,7 +34718,7 @@
       </c>
       <c r="AP306" s="88"/>
     </row>
-    <row r="307" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A307" s="81">
         <v>46214</v>
       </c>
@@ -34817,7 +34816,7 @@
       </c>
       <c r="AP307" s="88"/>
     </row>
-    <row r="308" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A308" s="81">
         <v>46214</v>
       </c>
@@ -34915,7 +34914,7 @@
       </c>
       <c r="AP308" s="88"/>
     </row>
-    <row r="309" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A309" s="81">
         <v>46214</v>
       </c>
@@ -35429,7 +35428,7 @@
       </c>
       <c r="AP313" s="88"/>
     </row>
-    <row r="314" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A314" s="81">
         <v>46214</v>
       </c>
@@ -35527,7 +35526,7 @@
       </c>
       <c r="AP314" s="88"/>
     </row>
-    <row r="315" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A315" s="81">
         <v>46205</v>
       </c>
@@ -35733,7 +35732,7 @@
       </c>
       <c r="AP316" s="7"/>
     </row>
-    <row r="317" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A317" s="81">
         <v>46216</v>
       </c>
@@ -35829,7 +35828,7 @@
       </c>
       <c r="AP317" s="7"/>
     </row>
-    <row r="318" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A318" s="81">
         <v>46216</v>
       </c>
@@ -35919,7 +35918,7 @@
       </c>
       <c r="AP318" s="7"/>
     </row>
-    <row r="319" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A319" s="81">
         <v>46216</v>
       </c>
@@ -36013,7 +36012,7 @@
       </c>
       <c r="AP319" s="7"/>
     </row>
-    <row r="320" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A320" s="81">
         <v>46216</v>
       </c>
@@ -36111,7 +36110,7 @@
       </c>
       <c r="AP320" s="7"/>
     </row>
-    <row r="321" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A321" s="81">
         <v>46216</v>
       </c>
@@ -36201,7 +36200,7 @@
       </c>
       <c r="AP321" s="7"/>
     </row>
-    <row r="322" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A322" s="81">
         <v>46216</v>
       </c>
@@ -36293,7 +36292,7 @@
       </c>
       <c r="AP322" s="7"/>
     </row>
-    <row r="323" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A323" s="81">
         <v>46216</v>
       </c>
@@ -36383,7 +36382,7 @@
       </c>
       <c r="AP323" s="7"/>
     </row>
-    <row r="324" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A324" s="81">
         <v>46216</v>
       </c>
@@ -36479,7 +36478,7 @@
       </c>
       <c r="AP324" s="7"/>
     </row>
-    <row r="325" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A325" s="81">
         <v>46216</v>
       </c>
@@ -36575,7 +36574,7 @@
       </c>
       <c r="AP325" s="7"/>
     </row>
-    <row r="326" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A326" s="81">
         <v>46216</v>
       </c>
@@ -36665,7 +36664,7 @@
       </c>
       <c r="AP326" s="7"/>
     </row>
-    <row r="327" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A327" s="81">
         <v>46216</v>
       </c>
@@ -36755,7 +36754,7 @@
       </c>
       <c r="AP327" s="7"/>
     </row>
-    <row r="328" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A328" s="81">
         <v>46216</v>
       </c>
@@ -36853,7 +36852,7 @@
       </c>
       <c r="AP328" s="7"/>
     </row>
-    <row r="329" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A329" s="81">
         <v>46216</v>
       </c>
@@ -36943,7 +36942,7 @@
       </c>
       <c r="AP329" s="7"/>
     </row>
-    <row r="330" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A330" s="81">
         <v>46216</v>
       </c>
@@ -37043,7 +37042,7 @@
       </c>
       <c r="AP330" s="7"/>
     </row>
-    <row r="331" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A331" s="81">
         <v>46216</v>
       </c>
@@ -37143,7 +37142,7 @@
       </c>
       <c r="AP331" s="7"/>
     </row>
-    <row r="332" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A332" s="81">
         <v>46216</v>
       </c>
@@ -37233,7 +37232,7 @@
       </c>
       <c r="AP332" s="7"/>
     </row>
-    <row r="333" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A333" s="81">
         <v>46216</v>
       </c>
@@ -37997,7 +37996,7 @@
       </c>
       <c r="AP340" s="7"/>
     </row>
-    <row r="341" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A341" s="81">
         <v>46217</v>
       </c>
@@ -38089,7 +38088,7 @@
       </c>
       <c r="AP341" s="7"/>
     </row>
-    <row r="342" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A342" s="81">
         <v>46217</v>
       </c>
@@ -38185,7 +38184,7 @@
       </c>
       <c r="AP342" s="7"/>
     </row>
-    <row r="343" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A343" s="81">
         <v>46217</v>
       </c>
@@ -38275,7 +38274,7 @@
       </c>
       <c r="AP343" s="7"/>
     </row>
-    <row r="344" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A344" s="81">
         <v>46217</v>
       </c>
@@ -38367,7 +38366,7 @@
       </c>
       <c r="AP344" s="7"/>
     </row>
-    <row r="345" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A345" s="81">
         <v>46217</v>
       </c>
@@ -38457,7 +38456,7 @@
       </c>
       <c r="AP345" s="7"/>
     </row>
-    <row r="346" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A346" s="81">
         <v>46217</v>
       </c>
@@ -38553,7 +38552,7 @@
       </c>
       <c r="AP346" s="7"/>
     </row>
-    <row r="347" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A347" s="81">
         <v>46217</v>
       </c>
@@ -38647,7 +38646,7 @@
       </c>
       <c r="AP347" s="7"/>
     </row>
-    <row r="348" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A348" s="81">
         <v>46217</v>
       </c>
@@ -38741,7 +38740,7 @@
       </c>
       <c r="AP348" s="7"/>
     </row>
-    <row r="349" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A349" s="81">
         <v>46217</v>
       </c>
@@ -38831,7 +38830,7 @@
       </c>
       <c r="AP349" s="7"/>
     </row>
-    <row r="350" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A350" s="81">
         <v>46217</v>
       </c>
@@ -38923,7 +38922,7 @@
       </c>
       <c r="AP350" s="7"/>
     </row>
-    <row r="351" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A351" s="81">
         <v>46217</v>
       </c>
@@ -39017,7 +39016,7 @@
       </c>
       <c r="AP351" s="7"/>
     </row>
-    <row r="352" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A352" s="81">
         <v>46217</v>
       </c>
@@ -39109,7 +39108,7 @@
       </c>
       <c r="AP352" s="7"/>
     </row>
-    <row r="353" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A353" s="81">
         <v>46217</v>
       </c>
@@ -39199,7 +39198,7 @@
       </c>
       <c r="AP353" s="7"/>
     </row>
-    <row r="354" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A354" s="81">
         <v>46217</v>
       </c>
@@ -39293,7 +39292,7 @@
       </c>
       <c r="AP354" s="7"/>
     </row>
-    <row r="355" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A355" s="81">
         <v>46217</v>
       </c>
@@ -39387,7 +39386,7 @@
       </c>
       <c r="AP355" s="7"/>
     </row>
-    <row r="356" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A356" s="81">
         <v>46217</v>
       </c>
@@ -39479,7 +39478,7 @@
       </c>
       <c r="AP356" s="7"/>
     </row>
-    <row r="357" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A357" s="81">
         <v>46217</v>
       </c>
@@ -39569,7 +39568,7 @@
       </c>
       <c r="AP357" s="7"/>
     </row>
-    <row r="358" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A358" s="81">
         <v>46217</v>
       </c>
@@ -39659,7 +39658,7 @@
       </c>
       <c r="AP358" s="7"/>
     </row>
-    <row r="359" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A359" s="81">
         <v>46217</v>
       </c>
@@ -39749,7 +39748,7 @@
       </c>
       <c r="AP359" s="7"/>
     </row>
-    <row r="360" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A360" s="81">
         <v>46217</v>
       </c>
@@ -39839,7 +39838,7 @@
       </c>
       <c r="AP360" s="7"/>
     </row>
-    <row r="361" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A361" s="81">
         <v>46217</v>
       </c>
@@ -39929,7 +39928,7 @@
       </c>
       <c r="AP361" s="7"/>
     </row>
-    <row r="362" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A362" s="81">
         <v>46217</v>
       </c>
@@ -40019,7 +40018,7 @@
       </c>
       <c r="AP362" s="7"/>
     </row>
-    <row r="363" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A363" s="81">
         <v>46217</v>
       </c>
@@ -40111,7 +40110,7 @@
       </c>
       <c r="AP363" s="7"/>
     </row>
-    <row r="364" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A364" s="81">
         <v>46217</v>
       </c>
@@ -40201,7 +40200,7 @@
       </c>
       <c r="AP364" s="7"/>
     </row>
-    <row r="365" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A365" s="81">
         <v>46217</v>
       </c>
@@ -40295,7 +40294,7 @@
       </c>
       <c r="AP365" s="7"/>
     </row>
-    <row r="366" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A366" s="81">
         <v>46217</v>
       </c>
@@ -40389,7 +40388,7 @@
       </c>
       <c r="AP366" s="7"/>
     </row>
-    <row r="367" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A367" s="81">
         <v>46217</v>
       </c>
@@ -40479,7 +40478,7 @@
       </c>
       <c r="AP367" s="7"/>
     </row>
-    <row r="368" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A368" s="81">
         <v>46217</v>
       </c>
@@ -40569,7 +40568,7 @@
       </c>
       <c r="AP368" s="7"/>
     </row>
-    <row r="369" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A369" s="81">
         <v>46217</v>
       </c>
@@ -40659,7 +40658,7 @@
       </c>
       <c r="AP369" s="7"/>
     </row>
-    <row r="370" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A370" s="81">
         <v>46217</v>
       </c>
@@ -40749,7 +40748,7 @@
       </c>
       <c r="AP370" s="7"/>
     </row>
-    <row r="371" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A371" s="81">
         <v>46217</v>
       </c>
@@ -40839,7 +40838,7 @@
       </c>
       <c r="AP371" s="7"/>
     </row>
-    <row r="372" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A372" s="81">
         <v>46217</v>
       </c>
@@ -40929,7 +40928,7 @@
       </c>
       <c r="AP372" s="7"/>
     </row>
-    <row r="373" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A373" s="81">
         <v>46217</v>
       </c>
@@ -41019,7 +41018,7 @@
       </c>
       <c r="AP373" s="7"/>
     </row>
-    <row r="374" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A374" s="81">
         <v>46217</v>
       </c>
@@ -41109,7 +41108,7 @@
       </c>
       <c r="AP374" s="7"/>
     </row>
-    <row r="375" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A375" s="81">
         <v>46217</v>
       </c>
@@ -41199,7 +41198,7 @@
       </c>
       <c r="AP375" s="7"/>
     </row>
-    <row r="376" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A376" s="81">
         <v>46217</v>
       </c>
@@ -41293,7 +41292,7 @@
       </c>
       <c r="AP376" s="7"/>
     </row>
-    <row r="377" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A377" s="81">
         <v>46217</v>
       </c>
@@ -41391,7 +41390,7 @@
       </c>
       <c r="AP377" s="7"/>
     </row>
-    <row r="378" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A378" s="81">
         <v>46217</v>
       </c>
@@ -41491,7 +41490,7 @@
       </c>
       <c r="AP378" s="7"/>
     </row>
-    <row r="379" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A379" s="81">
         <v>46217</v>
       </c>
@@ -41581,7 +41580,7 @@
       </c>
       <c r="AP379" s="7"/>
     </row>
-    <row r="380" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A380" s="81">
         <v>46217</v>
       </c>
@@ -41671,7 +41670,7 @@
       </c>
       <c r="AP380" s="7"/>
     </row>
-    <row r="381" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A381" s="81">
         <v>46217</v>
       </c>
@@ -41761,7 +41760,7 @@
       </c>
       <c r="AP381" s="7"/>
     </row>
-    <row r="382" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A382" s="81">
         <v>46217</v>
       </c>
@@ -41851,7 +41850,7 @@
       </c>
       <c r="AP382" s="7"/>
     </row>
-    <row r="383" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A383" s="81">
         <v>46217</v>
       </c>
@@ -41941,7 +41940,7 @@
       </c>
       <c r="AP383" s="7"/>
     </row>
-    <row r="384" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A384" s="81">
         <v>46218</v>
       </c>
@@ -42035,7 +42034,7 @@
       </c>
       <c r="AP384" s="7"/>
     </row>
-    <row r="385" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A385" s="81">
         <v>46218</v>
       </c>
@@ -42125,7 +42124,7 @@
       </c>
       <c r="AP385" s="7"/>
     </row>
-    <row r="386" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A386" s="81">
         <v>46218</v>
       </c>
@@ -42219,7 +42218,7 @@
       </c>
       <c r="AP386" s="7"/>
     </row>
-    <row r="387" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A387" s="81">
         <v>46218</v>
       </c>
@@ -42311,7 +42310,7 @@
       </c>
       <c r="AP387" s="7"/>
     </row>
-    <row r="388" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A388" s="81">
         <v>46218</v>
       </c>
@@ -42405,7 +42404,7 @@
       </c>
       <c r="AP388" s="7"/>
     </row>
-    <row r="389" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A389" s="81">
         <v>46218</v>
       </c>
@@ -42505,7 +42504,7 @@
       </c>
       <c r="AP389" s="7"/>
     </row>
-    <row r="390" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A390" s="81">
         <v>46218</v>
       </c>
@@ -42597,7 +42596,7 @@
       </c>
       <c r="AP390" s="7"/>
     </row>
-    <row r="391" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A391" s="81">
         <v>46218</v>
       </c>
@@ -42691,7 +42690,7 @@
       </c>
       <c r="AP391" s="7"/>
     </row>
-    <row r="392" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A392" s="81">
         <v>46218</v>
       </c>
@@ -42785,7 +42784,7 @@
       </c>
       <c r="AP392" s="7"/>
     </row>
-    <row r="393" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A393" s="81">
         <v>46218</v>
       </c>
@@ -42885,7 +42884,7 @@
       </c>
       <c r="AP393" s="7"/>
     </row>
-    <row r="394" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A394" s="81">
         <v>46218</v>
       </c>
@@ -42985,7 +42984,7 @@
       </c>
       <c r="AP394" s="7"/>
     </row>
-    <row r="395" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A395" s="81">
         <v>46218</v>
       </c>
@@ -43085,7 +43084,7 @@
       </c>
       <c r="AP395" s="7"/>
     </row>
-    <row r="396" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A396" s="81">
         <v>46218</v>
       </c>
@@ -43177,7 +43176,7 @@
       </c>
       <c r="AP396" s="7"/>
     </row>
-    <row r="397" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A397" s="81">
         <v>46218</v>
       </c>
@@ -43267,7 +43266,7 @@
       </c>
       <c r="AP397" s="7"/>
     </row>
-    <row r="398" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A398" s="81">
         <v>46218</v>
       </c>
@@ -43357,7 +43356,7 @@
       </c>
       <c r="AP398" s="7"/>
     </row>
-    <row r="399" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A399" s="81">
         <v>46218</v>
       </c>
@@ -43449,7 +43448,7 @@
       </c>
       <c r="AP399" s="7"/>
     </row>
-    <row r="400" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A400" s="81">
         <v>46218</v>
       </c>
@@ -43539,7 +43538,7 @@
       </c>
       <c r="AP400" s="7"/>
     </row>
-    <row r="401" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A401" s="81">
         <v>46218</v>
       </c>
@@ -43633,7 +43632,7 @@
       </c>
       <c r="AP401" s="7"/>
     </row>
-    <row r="402" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A402" s="81">
         <v>46218</v>
       </c>
@@ -43727,7 +43726,7 @@
       </c>
       <c r="AP402" s="7"/>
     </row>
-    <row r="403" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A403" s="81">
         <v>46218</v>
       </c>
@@ -43819,7 +43818,7 @@
       </c>
       <c r="AP403" s="7"/>
     </row>
-    <row r="404" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A404" s="81">
         <v>46218</v>
       </c>
@@ -43911,7 +43910,7 @@
       </c>
       <c r="AP404" s="7"/>
     </row>
-    <row r="405" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A405" s="81">
         <v>46218</v>
       </c>
@@ -44003,7 +44002,7 @@
       </c>
       <c r="AP405" s="7"/>
     </row>
-    <row r="406" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A406" s="81">
         <v>46218</v>
       </c>
@@ -44095,7 +44094,7 @@
       </c>
       <c r="AP406" s="7"/>
     </row>
-    <row r="407" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A407" s="81">
         <v>46218</v>
       </c>
@@ -44185,7 +44184,7 @@
       </c>
       <c r="AP407" s="7"/>
     </row>
-    <row r="408" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A408" s="81">
         <v>46218</v>
       </c>
@@ -44279,7 +44278,7 @@
       </c>
       <c r="AP408" s="7"/>
     </row>
-    <row r="409" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A409" s="81">
         <v>46218</v>
       </c>
@@ -44369,7 +44368,7 @@
       </c>
       <c r="AP409" s="7"/>
     </row>
-    <row r="410" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A410" s="81">
         <v>46218</v>
       </c>
@@ -44459,7 +44458,7 @@
       </c>
       <c r="AP410" s="7"/>
     </row>
-    <row r="411" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A411" s="81">
         <v>46218</v>
       </c>
@@ -44549,7 +44548,7 @@
       </c>
       <c r="AP411" s="7"/>
     </row>
-    <row r="412" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A412" s="81">
         <v>46218</v>
       </c>
@@ -44639,7 +44638,7 @@
       </c>
       <c r="AP412" s="7"/>
     </row>
-    <row r="413" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A413" s="81">
         <v>46218</v>
       </c>
@@ -44834,7 +44833,7 @@
       </c>
       <c r="AP414" s="7"/>
     </row>
-    <row r="415" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A415" s="81">
         <v>46219</v>
       </c>
@@ -44928,7 +44927,7 @@
       </c>
       <c r="AP415" s="7"/>
     </row>
-    <row r="416" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A416" s="81">
         <v>46219</v>
       </c>
@@ -45018,7 +45017,7 @@
       </c>
       <c r="AP416" s="7"/>
     </row>
-    <row r="417" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A417" s="81">
         <v>46219</v>
       </c>
@@ -45110,7 +45109,7 @@
       </c>
       <c r="AP417" s="7"/>
     </row>
-    <row r="418" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A418" s="81">
         <v>46219</v>
       </c>
@@ -45200,7 +45199,7 @@
       </c>
       <c r="AP418" s="7"/>
     </row>
-    <row r="419" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A419" s="81">
         <v>46219</v>
       </c>
@@ -45292,7 +45291,7 @@
       </c>
       <c r="AP419" s="7"/>
     </row>
-    <row r="420" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A420" s="81">
         <v>46219</v>
       </c>
@@ -45384,7 +45383,7 @@
       </c>
       <c r="AP420" s="7"/>
     </row>
-    <row r="421" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A421" s="81">
         <v>46219</v>
       </c>
@@ -45476,7 +45475,7 @@
       </c>
       <c r="AP421" s="7"/>
     </row>
-    <row r="422" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A422" s="81">
         <v>46219</v>
       </c>
@@ -45568,7 +45567,7 @@
       </c>
       <c r="AP422" s="7"/>
     </row>
-    <row r="423" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A423" s="81">
         <v>46219</v>
       </c>
@@ -45660,7 +45659,7 @@
       </c>
       <c r="AP423" s="7"/>
     </row>
-    <row r="424" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A424" s="81">
         <v>46219</v>
       </c>
@@ -45752,7 +45751,7 @@
       </c>
       <c r="AP424" s="7"/>
     </row>
-    <row r="425" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A425" s="81">
         <v>46219</v>
       </c>
@@ -45844,7 +45843,7 @@
       </c>
       <c r="AP425" s="7"/>
     </row>
-    <row r="426" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A426" s="81">
         <v>46219</v>
       </c>
@@ -45934,7 +45933,7 @@
       </c>
       <c r="AP426" s="7"/>
     </row>
-    <row r="427" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A427" s="81">
         <v>46219</v>
       </c>
@@ -46026,7 +46025,7 @@
       </c>
       <c r="AP427" s="7"/>
     </row>
-    <row r="428" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A428" s="81">
         <v>46219</v>
       </c>
@@ -46116,7 +46115,7 @@
       </c>
       <c r="AP428" s="7"/>
     </row>
-    <row r="429" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A429" s="81">
         <v>46219</v>
       </c>
@@ -46206,7 +46205,7 @@
       </c>
       <c r="AP429" s="7"/>
     </row>
-    <row r="430" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A430" s="81">
         <v>46219</v>
       </c>
@@ -46296,7 +46295,7 @@
       </c>
       <c r="AP430" s="7"/>
     </row>
-    <row r="431" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A431" s="81">
         <v>46219</v>
       </c>
@@ -46388,7 +46387,7 @@
       </c>
       <c r="AP431" s="7"/>
     </row>
-    <row r="432" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A432" s="81">
         <v>46219</v>
       </c>
@@ -46478,7 +46477,7 @@
       </c>
       <c r="AP432" s="7"/>
     </row>
-    <row r="433" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A433" s="81">
         <v>46219</v>
       </c>
@@ -46568,7 +46567,7 @@
       </c>
       <c r="AP433" s="7"/>
     </row>
-    <row r="434" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A434" s="81">
         <v>46219</v>
       </c>
@@ -47140,7 +47139,7 @@
       </c>
       <c r="AP439" s="7"/>
     </row>
-    <row r="440" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A440" s="81">
         <v>46220</v>
       </c>
@@ -47232,7 +47231,7 @@
       </c>
       <c r="AP440" s="7"/>
     </row>
-    <row r="441" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A441" s="81">
         <v>46220</v>
       </c>
@@ -47324,7 +47323,7 @@
       </c>
       <c r="AP441" s="7"/>
     </row>
-    <row r="442" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A442" s="81">
         <v>46220</v>
       </c>
@@ -47418,7 +47417,7 @@
       </c>
       <c r="AP442" s="7"/>
     </row>
-    <row r="443" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A443" s="81">
         <v>46220</v>
       </c>
@@ -47510,7 +47509,7 @@
       </c>
       <c r="AP443" s="7"/>
     </row>
-    <row r="444" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A444" s="81">
         <v>46220</v>
       </c>
@@ -47604,7 +47603,7 @@
       </c>
       <c r="AP444" s="7"/>
     </row>
-    <row r="445" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A445" s="81">
         <v>46220</v>
       </c>
@@ -47702,7 +47701,7 @@
       </c>
       <c r="AP445" s="7"/>
     </row>
-    <row r="446" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A446" s="81">
         <v>46220</v>
       </c>
@@ -47792,7 +47791,7 @@
       </c>
       <c r="AP446" s="7"/>
     </row>
-    <row r="447" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A447" s="81">
         <v>46220</v>
       </c>
@@ -47882,7 +47881,7 @@
       </c>
       <c r="AP447" s="7"/>
     </row>
-    <row r="448" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A448" s="81">
         <v>46220</v>
       </c>
@@ -47972,7 +47971,7 @@
       </c>
       <c r="AP448" s="7"/>
     </row>
-    <row r="449" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A449" s="81">
         <v>46220</v>
       </c>
@@ -48062,7 +48061,7 @@
       </c>
       <c r="AP449" s="7"/>
     </row>
-    <row r="450" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A450" s="81">
         <v>46220</v>
       </c>
@@ -48154,7 +48153,7 @@
       </c>
       <c r="AP450" s="7"/>
     </row>
-    <row r="451" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A451" s="81">
         <v>46220</v>
       </c>
@@ -48244,7 +48243,7 @@
       </c>
       <c r="AP451" s="7"/>
     </row>
-    <row r="452" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A452" s="81">
         <v>46220</v>
       </c>
@@ -48334,7 +48333,7 @@
       </c>
       <c r="AP452" s="7"/>
     </row>
-    <row r="453" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A453" s="81">
         <v>46220</v>
       </c>
@@ -48424,7 +48423,7 @@
       </c>
       <c r="AP453" s="7"/>
     </row>
-    <row r="454" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A454" s="81">
         <v>46220</v>
       </c>
@@ -48514,7 +48513,7 @@
       </c>
       <c r="AP454" s="7"/>
     </row>
-    <row r="455" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A455" s="81">
         <v>46220</v>
       </c>
@@ -48608,7 +48607,7 @@
       </c>
       <c r="AP455" s="7"/>
     </row>
-    <row r="456" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A456" s="81">
         <v>46220</v>
       </c>
@@ -48698,7 +48697,7 @@
       </c>
       <c r="AP456" s="7"/>
     </row>
-    <row r="457" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A457" s="81">
         <v>46220</v>
       </c>
@@ -48788,7 +48787,7 @@
       </c>
       <c r="AP457" s="7"/>
     </row>
-    <row r="458" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A458" s="81">
         <v>46220</v>
       </c>
@@ -48882,7 +48881,7 @@
       </c>
       <c r="AP458" s="7"/>
     </row>
-    <row r="459" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A459" s="81">
         <v>46220</v>
       </c>
@@ -48977,7 +48976,7 @@
       </c>
       <c r="AP459" s="7"/>
     </row>
-    <row r="460" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A460" s="81">
         <v>46220</v>
       </c>
@@ -49079,7 +49078,7 @@
       </c>
       <c r="AP460" s="7"/>
     </row>
-    <row r="461" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A461" s="81">
         <v>46220</v>
       </c>
@@ -49173,7 +49172,7 @@
       </c>
       <c r="AP461" s="7"/>
     </row>
-    <row r="462" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A462" s="81">
         <v>46220</v>
       </c>
@@ -49271,7 +49270,7 @@
       </c>
       <c r="AP462" s="7"/>
     </row>
-    <row r="463" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A463" s="81">
         <v>46220</v>
       </c>
@@ -49369,7 +49368,7 @@
       </c>
       <c r="AP463" s="7"/>
     </row>
-    <row r="464" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A464" s="81">
         <v>46220</v>
       </c>
@@ -49459,7 +49458,7 @@
       </c>
       <c r="AP464" s="7"/>
     </row>
-    <row r="465" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A465" s="81">
         <v>46220</v>
       </c>
@@ -49549,7 +49548,7 @@
       </c>
       <c r="AP465" s="7"/>
     </row>
-    <row r="466" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A466" s="81">
         <v>46220</v>
       </c>
@@ -49639,7 +49638,7 @@
       </c>
       <c r="AP466" s="7"/>
     </row>
-    <row r="467" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A467" s="81">
         <v>46220</v>
       </c>
@@ -49729,7 +49728,7 @@
       </c>
       <c r="AP467" s="7"/>
     </row>
-    <row r="468" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A468" s="81">
         <v>46220</v>
       </c>
@@ -49819,7 +49818,7 @@
       </c>
       <c r="AP468" s="7"/>
     </row>
-    <row r="469" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A469" s="81">
         <v>46220</v>
       </c>
@@ -49909,7 +49908,7 @@
       </c>
       <c r="AP469" s="7"/>
     </row>
-    <row r="470" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A470" s="81">
         <v>46220</v>
       </c>
@@ -49971,7 +49970,7 @@
       <c r="AL470" s="102"/>
       <c r="AP470" s="7"/>
     </row>
-    <row r="471" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A471" s="81">
         <v>46220</v>
       </c>
@@ -50033,7 +50032,7 @@
       <c r="AL471" s="102"/>
       <c r="AP471" s="7"/>
     </row>
-    <row r="472" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A472" s="81">
         <v>46220</v>
       </c>
@@ -50095,7 +50094,7 @@
       <c r="AL472" s="102"/>
       <c r="AP472" s="7"/>
     </row>
-    <row r="473" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A473" s="81">
         <v>46220</v>
       </c>
@@ -50157,7 +50156,7 @@
       <c r="AL473" s="102"/>
       <c r="AP473" s="7"/>
     </row>
-    <row r="474" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A474" s="81">
         <v>46220</v>
       </c>
@@ -50227,7 +50226,7 @@
       <c r="AL474" s="102"/>
       <c r="AP474" s="7"/>
     </row>
-    <row r="475" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A475" s="81">
         <v>46220</v>
       </c>
@@ -50763,7 +50762,7 @@
       <c r="AL482" s="102"/>
       <c r="AP482" s="7"/>
     </row>
-    <row r="483" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A483" s="81">
         <v>46221</v>
       </c>
@@ -50827,7 +50826,7 @@
       <c r="AL483" s="102"/>
       <c r="AP483" s="7"/>
     </row>
-    <row r="484" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A484" s="81">
         <v>46221</v>
       </c>
@@ -50893,7 +50892,7 @@
       <c r="AL484" s="102"/>
       <c r="AP484" s="7"/>
     </row>
-    <row r="485" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A485" s="81">
         <v>46221</v>
       </c>
@@ -50955,7 +50954,7 @@
       <c r="AL485" s="102"/>
       <c r="AP485" s="7"/>
     </row>
-    <row r="486" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A486" s="81">
         <v>46221</v>
       </c>
@@ -51025,7 +51024,7 @@
       <c r="AL486" s="102"/>
       <c r="AP486" s="7"/>
     </row>
-    <row r="487" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A487" s="81">
         <v>46221</v>
       </c>
@@ -51087,7 +51086,7 @@
       <c r="AL487" s="102"/>
       <c r="AP487" s="7"/>
     </row>
-    <row r="488" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A488" s="81">
         <v>46221</v>
       </c>
@@ -51153,7 +51152,7 @@
       <c r="AL488" s="102"/>
       <c r="AP488" s="7"/>
     </row>
-    <row r="489" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A489" s="81">
         <v>46221</v>
       </c>
@@ -51217,7 +51216,7 @@
       <c r="AL489" s="102"/>
       <c r="AP489" s="7"/>
     </row>
-    <row r="490" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A490" s="81">
         <v>46221</v>
       </c>
@@ -51283,7 +51282,7 @@
       <c r="AL490" s="102"/>
       <c r="AP490" s="7"/>
     </row>
-    <row r="491" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A491" s="81">
         <v>46221</v>
       </c>
@@ -51407,7 +51406,7 @@
       <c r="AL492" s="102"/>
       <c r="AP492" s="7"/>
     </row>
-    <row r="493" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A493" s="81">
         <v>46221</v>
       </c>
@@ -51471,7 +51470,7 @@
       <c r="AL493" s="102"/>
       <c r="AP493" s="7"/>
     </row>
-    <row r="494" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A494" s="81">
         <v>46221</v>
       </c>
@@ -51535,7 +51534,7 @@
       <c r="AL494" s="102"/>
       <c r="AP494" s="7"/>
     </row>
-    <row r="495" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A495" s="81">
         <v>46221</v>
       </c>
@@ -51599,7 +51598,7 @@
       <c r="AL495" s="102"/>
       <c r="AP495" s="7"/>
     </row>
-    <row r="496" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A496" s="81">
         <v>46221</v>
       </c>
@@ -51661,7 +51660,7 @@
       <c r="AL496" s="102"/>
       <c r="AP496" s="7"/>
     </row>
-    <row r="497" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A497" s="81">
         <v>46221</v>
       </c>
@@ -51727,7 +51726,7 @@
       <c r="AL497" s="102"/>
       <c r="AP497" s="7"/>
     </row>
-    <row r="498" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A498" s="81">
         <v>46221</v>
       </c>
@@ -51797,7 +51796,7 @@
       <c r="AL498" s="102"/>
       <c r="AP498" s="7"/>
     </row>
-    <row r="499" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A499" s="81">
         <v>46221</v>
       </c>
@@ -51859,7 +51858,7 @@
       <c r="AL499" s="102"/>
       <c r="AP499" s="7"/>
     </row>
-    <row r="500" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A500" s="81">
         <v>46221</v>
       </c>
@@ -51921,7 +51920,7 @@
       <c r="AL500" s="102"/>
       <c r="AP500" s="7"/>
     </row>
-    <row r="501" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A501" s="81">
         <v>46221</v>
       </c>
@@ -51983,7 +51982,7 @@
       <c r="AL501" s="102"/>
       <c r="AP501" s="7"/>
     </row>
-    <row r="502" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A502" s="81">
         <v>46221</v>
       </c>
@@ -52045,7 +52044,7 @@
       <c r="AL502" s="102"/>
       <c r="AP502" s="7"/>
     </row>
-    <row r="503" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A503" s="81">
         <v>46221</v>
       </c>
@@ -52107,7 +52106,7 @@
       <c r="AL503" s="102"/>
       <c r="AP503" s="7"/>
     </row>
-    <row r="504" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A504" s="81">
         <v>46221</v>
       </c>
@@ -52169,7 +52168,7 @@
       <c r="AL504" s="102"/>
       <c r="AP504" s="7"/>
     </row>
-    <row r="505" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A505" s="81">
         <v>46221</v>
       </c>
@@ -52231,7 +52230,7 @@
       <c r="AL505" s="102"/>
       <c r="AP505" s="7"/>
     </row>
-    <row r="506" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A506" s="81">
         <v>46221</v>
       </c>
@@ -52293,7 +52292,7 @@
       <c r="AL506" s="102"/>
       <c r="AP506" s="7"/>
     </row>
-    <row r="507" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A507" s="81">
         <v>46221</v>
       </c>
@@ -52355,7 +52354,7 @@
       <c r="AL507" s="102"/>
       <c r="AP507" s="7"/>
     </row>
-    <row r="508" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A508" s="81">
         <v>46221</v>
       </c>
@@ -52417,7 +52416,7 @@
       <c r="AL508" s="102"/>
       <c r="AP508" s="7"/>
     </row>
-    <row r="509" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A509" s="81">
         <v>46221</v>
       </c>
@@ -52479,7 +52478,7 @@
       <c r="AL509" s="102"/>
       <c r="AP509" s="7"/>
     </row>
-    <row r="510" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A510" s="81">
         <v>46221</v>
       </c>
@@ -52541,7 +52540,7 @@
       <c r="AL510" s="102"/>
       <c r="AP510" s="7"/>
     </row>
-    <row r="511" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A511" s="81">
         <v>46221</v>
       </c>
@@ -52745,7 +52744,7 @@
       <c r="AL513" s="102"/>
       <c r="AP513" s="7"/>
     </row>
-    <row r="514" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A514" s="81">
         <v>46223</v>
       </c>
@@ -52809,7 +52808,7 @@
       <c r="AL514" s="102"/>
       <c r="AP514" s="7"/>
     </row>
-    <row r="515" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A515" s="81">
         <v>46223</v>
       </c>
@@ -52871,7 +52870,7 @@
       <c r="AL515" s="102"/>
       <c r="AP515" s="7"/>
     </row>
-    <row r="516" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A516" s="81">
         <v>46223</v>
       </c>
@@ -52935,7 +52934,7 @@
       <c r="AL516" s="102"/>
       <c r="AP516" s="7"/>
     </row>
-    <row r="517" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A517" s="81">
         <v>46223</v>
       </c>
@@ -52997,7 +52996,7 @@
       <c r="AL517" s="102"/>
       <c r="AP517" s="7"/>
     </row>
-    <row r="518" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A518" s="81">
         <v>46223</v>
       </c>
@@ -53059,7 +53058,7 @@
       <c r="AL518" s="102"/>
       <c r="AP518" s="7"/>
     </row>
-    <row r="519" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A519" s="81">
         <v>46223</v>
       </c>
@@ -53125,7 +53124,7 @@
       <c r="AL519" s="102"/>
       <c r="AP519" s="7"/>
     </row>
-    <row r="520" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A520" s="81">
         <v>46223</v>
       </c>
@@ -53187,7 +53186,7 @@
       <c r="AL520" s="102"/>
       <c r="AP520" s="7"/>
     </row>
-    <row r="521" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A521" s="81">
         <v>46223</v>
       </c>
@@ -53253,7 +53252,7 @@
       <c r="AL521" s="102"/>
       <c r="AP521" s="7"/>
     </row>
-    <row r="522" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A522" s="81">
         <v>46223</v>
       </c>
@@ -53315,7 +53314,7 @@
       <c r="AL522" s="102"/>
       <c r="AP522" s="7"/>
     </row>
-    <row r="523" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A523" s="81">
         <v>46223</v>
       </c>
@@ -53377,7 +53376,7 @@
       <c r="AL523" s="102"/>
       <c r="AP523" s="7"/>
     </row>
-    <row r="524" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A524" s="81">
         <v>46223</v>
       </c>
@@ -53441,7 +53440,7 @@
       <c r="AL524" s="102"/>
       <c r="AP524" s="7"/>
     </row>
-    <row r="525" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A525" s="81">
         <v>46223</v>
       </c>
@@ -53503,7 +53502,7 @@
       <c r="AL525" s="102"/>
       <c r="AP525" s="7"/>
     </row>
-    <row r="526" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A526" s="81">
         <v>46223</v>
       </c>
@@ -53565,7 +53564,7 @@
       <c r="AL526" s="102"/>
       <c r="AP526" s="7"/>
     </row>
-    <row r="527" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A527" s="81">
         <v>46223</v>
       </c>
@@ -53627,7 +53626,7 @@
       <c r="AL527" s="102"/>
       <c r="AP527" s="7"/>
     </row>
-    <row r="528" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A528" s="81">
         <v>46223</v>
       </c>
@@ -53689,7 +53688,7 @@
       <c r="AL528" s="102"/>
       <c r="AP528" s="7"/>
     </row>
-    <row r="529" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A529" s="81">
         <v>46223</v>
       </c>
@@ -53751,7 +53750,7 @@
       <c r="AL529" s="102"/>
       <c r="AP529" s="7"/>
     </row>
-    <row r="530" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A530" s="81">
         <v>46223</v>
       </c>
@@ -53813,7 +53812,7 @@
       <c r="AL530" s="102"/>
       <c r="AP530" s="7"/>
     </row>
-    <row r="531" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A531" s="81">
         <v>46223</v>
       </c>
@@ -53875,7 +53874,7 @@
       <c r="AL531" s="102"/>
       <c r="AP531" s="7"/>
     </row>
-    <row r="532" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A532" s="81">
         <v>46223</v>
       </c>
@@ -53945,7 +53944,7 @@
       <c r="AL532" s="102"/>
       <c r="AP532" s="7"/>
     </row>
-    <row r="533" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A533" s="81">
         <v>46223</v>
       </c>
@@ -54007,7 +54006,7 @@
       <c r="AL533" s="102"/>
       <c r="AP533" s="7"/>
     </row>
-    <row r="534" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A534" s="81">
         <v>46223</v>
       </c>
@@ -54069,7 +54068,7 @@
       <c r="AL534" s="102"/>
       <c r="AP534" s="7"/>
     </row>
-    <row r="535" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A535" s="81">
         <v>46223</v>
       </c>
@@ -54131,7 +54130,7 @@
       <c r="AL535" s="102"/>
       <c r="AP535" s="7"/>
     </row>
-    <row r="536" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A536" s="81">
         <v>46223</v>
       </c>
@@ -54193,7 +54192,7 @@
       <c r="AL536" s="102"/>
       <c r="AP536" s="7"/>
     </row>
-    <row r="537" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A537" s="81">
         <v>46223</v>
       </c>
@@ -54615,7 +54614,7 @@
       <c r="AL542" s="102"/>
       <c r="AP542" s="7"/>
     </row>
-    <row r="543" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A543" s="81">
         <v>46224</v>
       </c>
@@ -54688,7 +54687,7 @@
       <c r="AL543" s="102"/>
       <c r="AP543" s="7"/>
     </row>
-    <row r="544" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A544" s="81">
         <v>46224</v>
       </c>
@@ -54754,7 +54753,7 @@
       <c r="AL544" s="102"/>
       <c r="AP544" s="7"/>
     </row>
-    <row r="545" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A545" s="81">
         <v>46224</v>
       </c>
@@ -54820,7 +54819,7 @@
       <c r="AL545" s="102"/>
       <c r="AP545" s="7"/>
     </row>
-    <row r="546" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A546" s="81">
         <v>46224</v>
       </c>
@@ -54882,7 +54881,7 @@
       <c r="AL546" s="102"/>
       <c r="AP546" s="7"/>
     </row>
-    <row r="547" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A547" s="81">
         <v>46224</v>
       </c>
@@ -54944,7 +54943,7 @@
       <c r="AL547" s="102"/>
       <c r="AP547" s="7"/>
     </row>
-    <row r="548" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A548" s="81">
         <v>46224</v>
       </c>
@@ -55016,7 +55015,7 @@
       <c r="AL548" s="102"/>
       <c r="AP548" s="7"/>
     </row>
-    <row r="549" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A549" s="81">
         <v>46224</v>
       </c>
@@ -55082,7 +55081,7 @@
       <c r="AL549" s="102"/>
       <c r="AP549" s="7"/>
     </row>
-    <row r="550" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A550" s="81">
         <v>46224</v>
       </c>
@@ -55148,7 +55147,7 @@
       <c r="AL550" s="102"/>
       <c r="AP550" s="7"/>
     </row>
-    <row r="551" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A551" s="81">
         <v>46224</v>
       </c>
@@ -55214,7 +55213,7 @@
       <c r="AL551" s="102"/>
       <c r="AP551" s="7"/>
     </row>
-    <row r="552" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A552" s="81">
         <v>46224</v>
       </c>
@@ -55280,7 +55279,7 @@
       <c r="AL552" s="102"/>
       <c r="AP552" s="7"/>
     </row>
-    <row r="553" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A553" s="81">
         <v>46224</v>
       </c>
@@ -55342,7 +55341,7 @@
       <c r="AL553" s="102"/>
       <c r="AP553" s="7"/>
     </row>
-    <row r="554" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A554" s="81">
         <v>46224</v>
       </c>
@@ -55406,7 +55405,7 @@
       <c r="AL554" s="102"/>
       <c r="AP554" s="7"/>
     </row>
-    <row r="555" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A555" s="81">
         <v>46224</v>
       </c>
@@ -55472,7 +55471,7 @@
       <c r="AL555" s="102"/>
       <c r="AP555" s="7"/>
     </row>
-    <row r="556" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A556" s="81">
         <v>46224</v>
       </c>
@@ -55534,7 +55533,7 @@
       <c r="AL556" s="102"/>
       <c r="AP556" s="7"/>
     </row>
-    <row r="557" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A557" s="81">
         <v>46224</v>
       </c>
@@ -55596,7 +55595,7 @@
       <c r="AL557" s="102"/>
       <c r="AP557" s="7"/>
     </row>
-    <row r="558" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A558" s="81">
         <v>46224</v>
       </c>
@@ -55658,7 +55657,7 @@
       <c r="AL558" s="102"/>
       <c r="AP558" s="7"/>
     </row>
-    <row r="559" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A559" s="81">
         <v>46224</v>
       </c>
@@ -55726,7 +55725,7 @@
       <c r="AL559" s="102"/>
       <c r="AP559" s="7"/>
     </row>
-    <row r="560" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A560" s="81">
         <v>46224</v>
       </c>
@@ -55788,7 +55787,7 @@
       <c r="AL560" s="102"/>
       <c r="AP560" s="7"/>
     </row>
-    <row r="561" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A561" s="81">
         <v>46224</v>
       </c>
@@ -55850,7 +55849,7 @@
       <c r="AL561" s="102"/>
       <c r="AP561" s="7"/>
     </row>
-    <row r="562" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A562" s="81">
         <v>46224</v>
       </c>
@@ -55912,7 +55911,7 @@
       <c r="AL562" s="102"/>
       <c r="AP562" s="7"/>
     </row>
-    <row r="563" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A563" s="81">
         <v>46224</v>
       </c>
@@ -55974,7 +55973,7 @@
       <c r="AL563" s="102"/>
       <c r="AP563" s="7"/>
     </row>
-    <row r="564" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A564" s="81">
         <v>46224</v>
       </c>
@@ -56036,7 +56035,7 @@
       <c r="AL564" s="102"/>
       <c r="AP564" s="7"/>
     </row>
-    <row r="565" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A565" s="81">
         <v>46224</v>
       </c>
@@ -56098,7 +56097,7 @@
       <c r="AL565" s="102"/>
       <c r="AP565" s="7"/>
     </row>
-    <row r="566" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A566" s="81">
         <v>46224</v>
       </c>
@@ -56160,7 +56159,7 @@
       <c r="AL566" s="102"/>
       <c r="AP566" s="7"/>
     </row>
-    <row r="567" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A567" s="81">
         <v>46224</v>
       </c>
@@ -56222,7 +56221,7 @@
       <c r="AL567" s="102"/>
       <c r="AP567" s="7"/>
     </row>
-    <row r="568" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A568" s="81">
         <v>46224</v>
       </c>
@@ -56290,7 +56289,7 @@
       <c r="AL568" s="102"/>
       <c r="AP568" s="7"/>
     </row>
-    <row r="569" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A569" s="81">
         <v>46225</v>
       </c>
@@ -56356,7 +56355,7 @@
       <c r="AL569" s="102"/>
       <c r="AP569" s="7"/>
     </row>
-    <row r="570" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A570" s="81">
         <v>46225</v>
       </c>
@@ -56418,7 +56417,7 @@
       <c r="AL570" s="102"/>
       <c r="AP570" s="7"/>
     </row>
-    <row r="571" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A571" s="81">
         <v>46225</v>
       </c>
@@ -56480,7 +56479,7 @@
       <c r="AL571" s="102"/>
       <c r="AP571" s="7"/>
     </row>
-    <row r="572" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A572" s="81">
         <v>46225</v>
       </c>
@@ -56542,7 +56541,7 @@
       <c r="AL572" s="102"/>
       <c r="AP572" s="7"/>
     </row>
-    <row r="573" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A573" s="81">
         <v>46225</v>
       </c>
@@ -56606,7 +56605,7 @@
       <c r="AL573" s="102"/>
       <c r="AP573" s="7"/>
     </row>
-    <row r="574" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A574" s="81">
         <v>46225</v>
       </c>
@@ -56670,7 +56669,7 @@
       <c r="AL574" s="102"/>
       <c r="AP574" s="7"/>
     </row>
-    <row r="575" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A575" s="81">
         <v>46225</v>
       </c>
@@ -56734,7 +56733,7 @@
       <c r="AL575" s="102"/>
       <c r="AP575" s="7"/>
     </row>
-    <row r="576" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A576" s="81">
         <v>46225</v>
       </c>
@@ -56800,7 +56799,7 @@
       <c r="AL576" s="102"/>
       <c r="AP576" s="7"/>
     </row>
-    <row r="577" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A577" s="81">
         <v>46225</v>
       </c>
@@ -56862,7 +56861,7 @@
       <c r="AL577" s="102"/>
       <c r="AP577" s="7"/>
     </row>
-    <row r="578" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A578" s="81">
         <v>46225</v>
       </c>
@@ -56924,7 +56923,7 @@
       <c r="AL578" s="102"/>
       <c r="AP578" s="7"/>
     </row>
-    <row r="579" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A579" s="81">
         <v>46225</v>
       </c>
@@ -56986,7 +56985,7 @@
       <c r="AL579" s="102"/>
       <c r="AP579" s="7"/>
     </row>
-    <row r="580" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A580" s="81">
         <v>46225</v>
       </c>
@@ -57048,7 +57047,7 @@
       <c r="AL580" s="102"/>
       <c r="AP580" s="7"/>
     </row>
-    <row r="581" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A581" s="81">
         <v>46225</v>
       </c>
@@ -57114,7 +57113,7 @@
       <c r="AL581" s="102"/>
       <c r="AP581" s="7"/>
     </row>
-    <row r="582" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A582" s="81">
         <v>46225</v>
       </c>
@@ -57176,7 +57175,7 @@
       <c r="AL582" s="102"/>
       <c r="AP582" s="7"/>
     </row>
-    <row r="583" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A583" s="81">
         <v>46225</v>
       </c>
@@ -57238,7 +57237,7 @@
       <c r="AL583" s="102"/>
       <c r="AP583" s="7"/>
     </row>
-    <row r="584" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A584" s="81">
         <v>46225</v>
       </c>
@@ -57300,7 +57299,7 @@
       <c r="AL584" s="102"/>
       <c r="AP584" s="7"/>
     </row>
-    <row r="585" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A585" s="81">
         <v>46225</v>
       </c>
@@ -57366,7 +57365,7 @@
       <c r="AL585" s="102"/>
       <c r="AP585" s="7"/>
     </row>
-    <row r="586" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A586" s="81">
         <v>46225</v>
       </c>
@@ -57428,7 +57427,7 @@
       <c r="AL586" s="102"/>
       <c r="AP586" s="7"/>
     </row>
-    <row r="587" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A587" s="81">
         <v>46225</v>
       </c>
@@ -57490,7 +57489,7 @@
       <c r="AL587" s="102"/>
       <c r="AP587" s="7"/>
     </row>
-    <row r="588" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A588" s="81">
         <v>46225</v>
       </c>
@@ -57552,7 +57551,7 @@
       <c r="AL588" s="102"/>
       <c r="AP588" s="7"/>
     </row>
-    <row r="589" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A589" s="81">
         <v>46225</v>
       </c>
@@ -57614,7 +57613,7 @@
       <c r="AL589" s="102"/>
       <c r="AP589" s="7"/>
     </row>
-    <row r="590" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A590" s="81">
         <v>46225</v>
       </c>
@@ -57676,7 +57675,7 @@
       <c r="AL590" s="102"/>
       <c r="AP590" s="7"/>
     </row>
-    <row r="591" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A591" s="81">
         <v>46225</v>
       </c>
@@ -57740,7 +57739,7 @@
       <c r="AL591" s="102"/>
       <c r="AP591" s="7"/>
     </row>
-    <row r="592" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A592" s="81">
         <v>46225</v>
       </c>
@@ -58418,7 +58417,7 @@
       <c r="AL601" s="102"/>
       <c r="AP601" s="7"/>
     </row>
-    <row r="602" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A602" s="81">
         <v>46226</v>
       </c>
@@ -58482,7 +58481,7 @@
       <c r="AL602" s="102"/>
       <c r="AP602" s="7"/>
     </row>
-    <row r="603" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A603" s="81">
         <v>46226</v>
       </c>
@@ -58548,7 +58547,7 @@
       <c r="AL603" s="102"/>
       <c r="AP603" s="7"/>
     </row>
-    <row r="604" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A604" s="81">
         <v>46226</v>
       </c>
@@ -58614,7 +58613,7 @@
       <c r="AL604" s="102"/>
       <c r="AP604" s="7"/>
     </row>
-    <row r="605" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A605" s="81">
         <v>46226</v>
       </c>
@@ -58680,7 +58679,7 @@
       <c r="AL605" s="102"/>
       <c r="AP605" s="7"/>
     </row>
-    <row r="606" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A606" s="81">
         <v>46226</v>
       </c>
@@ -58742,7 +58741,7 @@
       <c r="AL606" s="102"/>
       <c r="AP606" s="7"/>
     </row>
-    <row r="607" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A607" s="81">
         <v>46226</v>
       </c>
@@ -58804,7 +58803,7 @@
       <c r="AL607" s="102"/>
       <c r="AP607" s="7"/>
     </row>
-    <row r="608" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A608" s="81">
         <v>46226</v>
       </c>
@@ -58872,7 +58871,7 @@
       <c r="AL608" s="102"/>
       <c r="AP608" s="7"/>
     </row>
-    <row r="609" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A609" s="81">
         <v>46226</v>
       </c>
@@ -58938,7 +58937,7 @@
       <c r="AL609" s="102"/>
       <c r="AP609" s="7"/>
     </row>
-    <row r="610" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A610" s="81">
         <v>46226</v>
       </c>
@@ -59006,7 +59005,7 @@
       <c r="AL610" s="102"/>
       <c r="AP610" s="7"/>
     </row>
-    <row r="611" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A611" s="81">
         <v>46226</v>
       </c>
@@ -59078,7 +59077,7 @@
       <c r="AL611" s="102"/>
       <c r="AP611" s="7"/>
     </row>
-    <row r="612" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A612" s="81">
         <v>46226</v>
       </c>
@@ -59426,7 +59425,7 @@
       <c r="AL616" s="102"/>
       <c r="AP616" s="7"/>
     </row>
-    <row r="617" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A617" s="81">
         <v>46227</v>
       </c>
@@ -59492,7 +59491,7 @@
       <c r="AL617" s="102"/>
       <c r="AP617" s="7"/>
     </row>
-    <row r="618" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A618" s="81">
         <v>46227</v>
       </c>
@@ -59564,7 +59563,7 @@
       <c r="AL618" s="102"/>
       <c r="AP618" s="7"/>
     </row>
-    <row r="619" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A619" s="81">
         <v>46228</v>
       </c>
@@ -60036,7 +60035,7 @@
       <c r="AL625" s="102"/>
       <c r="AP625" s="7"/>
     </row>
-    <row r="626" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A626" s="81">
         <v>46230</v>
       </c>
@@ -60104,7 +60103,7 @@
       <c r="AL626" s="102"/>
       <c r="AP626" s="7"/>
     </row>
-    <row r="627" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A627" s="81">
         <v>46230</v>
       </c>
@@ -60170,7 +60169,7 @@
       <c r="AL627" s="102"/>
       <c r="AP627" s="7"/>
     </row>
-    <row r="628" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A628" s="81">
         <v>46230</v>
       </c>
@@ -60238,7 +60237,7 @@
       <c r="AL628" s="102"/>
       <c r="AP628" s="7"/>
     </row>
-    <row r="629" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A629" s="81">
         <v>46230</v>
       </c>
@@ -60304,7 +60303,7 @@
       <c r="AL629" s="102"/>
       <c r="AP629" s="7"/>
     </row>
-    <row r="630" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A630" s="81">
         <v>46230</v>
       </c>
@@ -60366,7 +60365,7 @@
       <c r="AL630" s="102"/>
       <c r="AP630" s="7"/>
     </row>
-    <row r="631" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A631" s="81">
         <v>46230</v>
       </c>
@@ -60428,7 +60427,7 @@
       <c r="AL631" s="102"/>
       <c r="AP631" s="7"/>
     </row>
-    <row r="632" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A632" s="81">
         <v>46230</v>
       </c>
@@ -60500,7 +60499,7 @@
       <c r="AL632" s="102"/>
       <c r="AP632" s="7"/>
     </row>
-    <row r="633" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A633" s="81">
         <v>46230</v>
       </c>
@@ -60568,7 +60567,7 @@
       <c r="AL633" s="102"/>
       <c r="AP633" s="7"/>
     </row>
-    <row r="634" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A634" s="81">
         <v>46230</v>
       </c>
@@ -60634,7 +60633,7 @@
       <c r="AL634" s="102"/>
       <c r="AP634" s="7"/>
     </row>
-    <row r="635" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A635" s="81">
         <v>46230</v>
       </c>
@@ -60702,7 +60701,7 @@
       <c r="AL635" s="102"/>
       <c r="AP635" s="7"/>
     </row>
-    <row r="636" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A636" s="81">
         <v>46230</v>
       </c>
@@ -60772,7 +60771,7 @@
       <c r="AL636" s="102"/>
       <c r="AP636" s="7"/>
     </row>
-    <row r="637" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A637" s="81">
         <v>46230</v>
       </c>
@@ -60838,7 +60837,7 @@
       <c r="AL637" s="102"/>
       <c r="AP637" s="7"/>
     </row>
-    <row r="638" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A638" s="81">
         <v>46230</v>
       </c>
@@ -60900,7 +60899,7 @@
       <c r="AL638" s="102"/>
       <c r="AP638" s="7"/>
     </row>
-    <row r="639" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A639" s="81">
         <v>46230</v>
       </c>
@@ -60962,7 +60961,7 @@
       <c r="AL639" s="102"/>
       <c r="AP639" s="7"/>
     </row>
-    <row r="640" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A640" s="81">
         <v>46230</v>
       </c>
@@ -61030,7 +61029,7 @@
       <c r="AL640" s="102"/>
       <c r="AP640" s="7"/>
     </row>
-    <row r="641" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A641" s="81">
         <v>46230</v>
       </c>
@@ -61102,7 +61101,7 @@
       <c r="AL641" s="102"/>
       <c r="AP641" s="7"/>
     </row>
-    <row r="642" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A642" s="81">
         <v>46230</v>
       </c>
@@ -61174,7 +61173,7 @@
       <c r="AL642" s="102"/>
       <c r="AP642" s="7"/>
     </row>
-    <row r="643" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A643" s="81">
         <v>46230</v>
       </c>
@@ -61236,7 +61235,7 @@
       <c r="AL643" s="102"/>
       <c r="AP643" s="7"/>
     </row>
-    <row r="644" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A644" s="81">
         <v>46230</v>
       </c>
@@ -61298,7 +61297,7 @@
       <c r="AL644" s="102"/>
       <c r="AP644" s="7"/>
     </row>
-    <row r="645" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A645" s="81">
         <v>46230</v>
       </c>
@@ -61640,7 +61639,7 @@
       <c r="AL649" s="102"/>
       <c r="AP649" s="7"/>
     </row>
-    <row r="650" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A650" s="81">
         <v>46231</v>
       </c>
@@ -61708,7 +61707,7 @@
       <c r="AL650" s="102"/>
       <c r="AP650" s="7"/>
     </row>
-    <row r="651" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A651" s="81">
         <v>46231</v>
       </c>
@@ -61776,7 +61775,7 @@
       <c r="AL651" s="102"/>
       <c r="AP651" s="7"/>
     </row>
-    <row r="652" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A652" s="81">
         <v>46231</v>
       </c>
@@ -61846,7 +61845,7 @@
       <c r="AL652" s="102"/>
       <c r="AP652" s="7"/>
     </row>
-    <row r="653" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A653" s="81">
         <v>46231</v>
       </c>
@@ -61916,7 +61915,7 @@
       <c r="AL653" s="102"/>
       <c r="AP653" s="7"/>
     </row>
-    <row r="654" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A654" s="81">
         <v>46231</v>
       </c>
@@ -61980,7 +61979,7 @@
       <c r="AL654" s="102"/>
       <c r="AP654" s="7"/>
     </row>
-    <row r="655" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A655" s="81">
         <v>46231</v>
       </c>
@@ -62046,7 +62045,7 @@
       <c r="AL655" s="102"/>
       <c r="AP655" s="7"/>
     </row>
-    <row r="656" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A656" s="81">
         <v>46231</v>
       </c>
@@ -62108,7 +62107,7 @@
       <c r="AL656" s="102"/>
       <c r="AP656" s="7"/>
     </row>
-    <row r="657" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A657" s="81">
         <v>46231</v>
       </c>
@@ -62180,7 +62179,7 @@
       <c r="AL657" s="102"/>
       <c r="AP657" s="7"/>
     </row>
-    <row r="658" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A658" s="81">
         <v>46231</v>
       </c>
@@ -62248,7 +62247,7 @@
       <c r="AL658" s="102"/>
       <c r="AP658" s="7"/>
     </row>
-    <row r="659" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A659" s="81">
         <v>46231</v>
       </c>
@@ -62314,7 +62313,7 @@
       <c r="AL659" s="102"/>
       <c r="AP659" s="7"/>
     </row>
-    <row r="660" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A660" s="81">
         <v>46231</v>
       </c>
@@ -62386,7 +62385,7 @@
       <c r="AL660" s="102"/>
       <c r="AP660" s="7"/>
     </row>
-    <row r="661" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A661" s="81">
         <v>46231</v>
       </c>
@@ -62448,7 +62447,7 @@
       <c r="AL661" s="102"/>
       <c r="AP661" s="7"/>
     </row>
-    <row r="662" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A662" s="81">
         <v>46231</v>
       </c>
@@ -62510,7 +62509,7 @@
       <c r="AL662" s="102"/>
       <c r="AP662" s="7"/>
     </row>
-    <row r="663" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A663" s="81">
         <v>46231</v>
       </c>
@@ -62582,7 +62581,7 @@
       <c r="AL663" s="102"/>
       <c r="AP663" s="7"/>
     </row>
-    <row r="664" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A664" s="81">
         <v>46232</v>
       </c>
@@ -62650,7 +62649,7 @@
       <c r="AL664" s="102"/>
       <c r="AP664" s="7"/>
     </row>
-    <row r="665" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A665" s="81">
         <v>46232</v>
       </c>
@@ -62714,7 +62713,7 @@
       <c r="AL665" s="102"/>
       <c r="AP665" s="7"/>
     </row>
-    <row r="666" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A666" s="81">
         <v>46232</v>
       </c>
@@ -62780,7 +62779,7 @@
       <c r="AL666" s="102"/>
       <c r="AP666" s="7"/>
     </row>
-    <row r="667" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A667" s="81">
         <v>46232</v>
       </c>
@@ -62842,7 +62841,7 @@
       <c r="AL667" s="102"/>
       <c r="AP667" s="7"/>
     </row>
-    <row r="668" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A668" s="81">
         <v>46232</v>
       </c>
@@ -62914,7 +62913,7 @@
       <c r="AL668" s="102"/>
       <c r="AP668" s="7"/>
     </row>
-    <row r="669" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A669" s="81">
         <v>46232</v>
       </c>
@@ -62980,7 +62979,7 @@
       <c r="AL669" s="102"/>
       <c r="AP669" s="7"/>
     </row>
-    <row r="670" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A670" s="81">
         <v>46232</v>
       </c>
@@ -63046,7 +63045,7 @@
       <c r="AL670" s="102"/>
       <c r="AP670" s="7"/>
     </row>
-    <row r="671" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A671" s="81">
         <v>46232</v>
       </c>
@@ -63108,7 +63107,7 @@
       <c r="AL671" s="102"/>
       <c r="AP671" s="7"/>
     </row>
-    <row r="672" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A672" s="81">
         <v>46232</v>
       </c>
@@ -63170,7 +63169,7 @@
       <c r="AL672" s="102"/>
       <c r="AP672" s="7"/>
     </row>
-    <row r="673" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A673" s="81">
         <v>46232</v>
       </c>
@@ -63238,7 +63237,7 @@
       <c r="AL673" s="102"/>
       <c r="AP673" s="7"/>
     </row>
-    <row r="674" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A674" s="81">
         <v>46232</v>
       </c>
@@ -63304,7 +63303,7 @@
       <c r="AL674" s="102"/>
       <c r="AP674" s="7"/>
     </row>
-    <row r="675" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A675" s="81">
         <v>46232</v>
       </c>
@@ -63370,7 +63369,7 @@
       <c r="AL675" s="102"/>
       <c r="AP675" s="7"/>
     </row>
-    <row r="676" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A676" s="81">
         <v>46232</v>
       </c>
@@ -63432,7 +63431,7 @@
       <c r="AL676" s="102"/>
       <c r="AP676" s="7"/>
     </row>
-    <row r="677" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A677" s="81">
         <v>46232</v>
       </c>
@@ -63494,7 +63493,7 @@
       <c r="AL677" s="102"/>
       <c r="AP677" s="7"/>
     </row>
-    <row r="678" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A678" s="81">
         <v>46232</v>
       </c>
@@ -63556,7 +63555,7 @@
       <c r="AL678" s="102"/>
       <c r="AP678" s="7"/>
     </row>
-    <row r="679" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A679" s="81">
         <v>46232</v>
       </c>
@@ -63622,7 +63621,7 @@
       <c r="AL679" s="102"/>
       <c r="AP679" s="7"/>
     </row>
-    <row r="680" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A680" s="81">
         <v>46232</v>
       </c>
@@ -63688,7 +63687,7 @@
       <c r="AL680" s="102"/>
       <c r="AP680" s="7"/>
     </row>
-    <row r="681" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A681" s="81">
         <v>46232</v>
       </c>
@@ -63750,7 +63749,7 @@
       <c r="AL681" s="102"/>
       <c r="AP681" s="7"/>
     </row>
-    <row r="682" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A682" s="81">
         <v>46232</v>
       </c>
@@ -63812,7 +63811,7 @@
       <c r="AL682" s="102"/>
       <c r="AP682" s="7"/>
     </row>
-    <row r="683" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A683" s="81">
         <v>46232</v>
       </c>
@@ -63876,7 +63875,7 @@
       <c r="AL683" s="102"/>
       <c r="AP683" s="7"/>
     </row>
-    <row r="684" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A684" s="81">
         <v>46232</v>
       </c>
@@ -64012,7 +64011,7 @@
       <c r="AL685" s="102"/>
       <c r="AP685" s="7"/>
     </row>
-    <row r="686" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A686" s="81">
         <v>46233</v>
       </c>
@@ -64078,7 +64077,7 @@
       <c r="AL686" s="102"/>
       <c r="AP686" s="7"/>
     </row>
-    <row r="687" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A687" s="81">
         <v>46233</v>
       </c>
@@ -64146,7 +64145,7 @@
       <c r="AL687" s="102"/>
       <c r="AP687" s="7"/>
     </row>
-    <row r="688" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A688" s="81">
         <v>46233</v>
       </c>
@@ -64208,7 +64207,7 @@
       <c r="AL688" s="102"/>
       <c r="AP688" s="7"/>
     </row>
-    <row r="689" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A689" s="81">
         <v>46233</v>
       </c>
@@ -64272,7 +64271,7 @@
       <c r="AL689" s="102"/>
       <c r="AP689" s="7"/>
     </row>
-    <row r="690" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A690" s="81">
         <v>46233</v>
       </c>
@@ -64338,7 +64337,7 @@
       <c r="AL690" s="102"/>
       <c r="AP690" s="7"/>
     </row>
-    <row r="691" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A691" s="81">
         <v>46233</v>
       </c>
@@ -64410,7 +64409,7 @@
       <c r="AL691" s="102"/>
       <c r="AP691" s="7"/>
     </row>
-    <row r="692" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A692" s="81">
         <v>46233</v>
       </c>
@@ -64472,7 +64471,7 @@
       <c r="AL692" s="102"/>
       <c r="AP692" s="7"/>
     </row>
-    <row r="693" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A693" s="81">
         <v>46233</v>
       </c>
@@ -64536,7 +64535,7 @@
       <c r="AL693" s="102"/>
       <c r="AP693" s="7"/>
     </row>
-    <row r="694" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A694" s="81">
         <v>46233</v>
       </c>
@@ -64598,7 +64597,7 @@
       <c r="AL694" s="102"/>
       <c r="AP694" s="7"/>
     </row>
-    <row r="695" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A695" s="81">
         <v>46233</v>
       </c>
@@ -64660,7 +64659,7 @@
       <c r="AL695" s="102"/>
       <c r="AP695" s="7"/>
     </row>
-    <row r="696" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A696" s="81">
         <v>46233</v>
       </c>
@@ -64726,7 +64725,7 @@
       <c r="AL696" s="102"/>
       <c r="AP696" s="7"/>
     </row>
-    <row r="697" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A697" s="81">
         <v>46233</v>
       </c>
@@ -64788,7 +64787,7 @@
       <c r="AL697" s="102"/>
       <c r="AP697" s="7"/>
     </row>
-    <row r="698" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A698" s="81">
         <v>46233</v>
       </c>
@@ -64850,7 +64849,7 @@
       <c r="AL698" s="102"/>
       <c r="AP698" s="7"/>
     </row>
-    <row r="699" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A699" s="81">
         <v>46233</v>
       </c>
@@ -64912,7 +64911,7 @@
       <c r="AL699" s="102"/>
       <c r="AP699" s="7"/>
     </row>
-    <row r="700" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A700" s="81">
         <v>46233</v>
       </c>
@@ -64978,7 +64977,7 @@
       <c r="AL700" s="102"/>
       <c r="AP700" s="7"/>
     </row>
-    <row r="701" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A701" s="81">
         <v>46233</v>
       </c>
@@ -65040,7 +65039,7 @@
       <c r="AL701" s="102"/>
       <c r="AP701" s="7"/>
     </row>
-    <row r="702" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A702" s="81">
         <v>46233</v>
       </c>
@@ -65102,7 +65101,7 @@
       <c r="AL702" s="102"/>
       <c r="AP702" s="7"/>
     </row>
-    <row r="703" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A703" s="81">
         <v>46233</v>
       </c>
@@ -65170,7 +65169,7 @@
       <c r="AL703" s="102"/>
       <c r="AP703" s="7"/>
     </row>
-    <row r="704" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A704" s="81">
         <v>46233</v>
       </c>
@@ -65232,7 +65231,7 @@
       <c r="AL704" s="102"/>
       <c r="AP704" s="7"/>
     </row>
-    <row r="705" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A705" s="81">
         <v>46233</v>
       </c>
@@ -65294,7 +65293,7 @@
       <c r="AL705" s="102"/>
       <c r="AP705" s="7"/>
     </row>
-    <row r="706" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A706" s="81">
         <v>46233</v>
       </c>
@@ -65356,7 +65355,7 @@
       <c r="AL706" s="102"/>
       <c r="AP706" s="7"/>
     </row>
-    <row r="707" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A707" s="81">
         <v>46233</v>
       </c>
@@ -65418,7 +65417,7 @@
       <c r="AL707" s="102"/>
       <c r="AP707" s="7"/>
     </row>
-    <row r="708" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A708" s="81">
         <v>46233</v>
       </c>
@@ -65482,7 +65481,7 @@
       <c r="AL708" s="102"/>
       <c r="AP708" s="7"/>
     </row>
-    <row r="709" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A709" s="81">
         <v>46233</v>
       </c>
@@ -65548,7 +65547,7 @@
       <c r="AL709" s="102"/>
       <c r="AP709" s="7"/>
     </row>
-    <row r="710" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A710" s="81">
         <v>46233</v>
       </c>
@@ -65614,7 +65613,7 @@
       <c r="AL710" s="102"/>
       <c r="AP710" s="7"/>
     </row>
-    <row r="711" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A711" s="81">
         <v>46233</v>
       </c>
@@ -65686,7 +65685,7 @@
       <c r="AL711" s="102"/>
       <c r="AP711" s="7"/>
     </row>
-    <row r="712" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A712" s="81">
         <v>46233</v>
       </c>
@@ -65830,7 +65829,7 @@
       <c r="AL713" s="102"/>
       <c r="AP713" s="7"/>
     </row>
-    <row r="714" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A714" s="81">
         <v>46234</v>
       </c>
@@ -65920,7 +65919,7 @@
       <c r="F715" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="G715" s="148" t="s">
+      <c r="G715" s="134" t="s">
         <v>347</v>
       </c>
       <c r="H715" s="90" t="s">
@@ -66202,7 +66201,7 @@
       <c r="F719" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="G719" s="148" t="s">
+      <c r="G719" s="134" t="s">
         <v>727</v>
       </c>
       <c r="H719" s="90" t="s">
@@ -66521,7 +66520,7 @@
       <c r="AL723" s="102"/>
       <c r="AP723" s="7"/>
     </row>
-    <row r="724" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A724" s="81">
         <v>46234</v>
       </c>
@@ -66583,7 +66582,7 @@
       <c r="AL724" s="102"/>
       <c r="AP724" s="7"/>
     </row>
-    <row r="725" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A725" s="81">
         <v>46234</v>
       </c>
@@ -66655,7 +66654,7 @@
       <c r="AL725" s="102"/>
       <c r="AP725" s="7"/>
     </row>
-    <row r="726" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A726" s="81">
         <v>46234</v>
       </c>
@@ -66719,7 +66718,7 @@
       <c r="AL726" s="102"/>
       <c r="AP726" s="7"/>
     </row>
-    <row r="727" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A727" s="81">
         <v>46234</v>
       </c>
@@ -66785,7 +66784,7 @@
       <c r="AL727" s="102"/>
       <c r="AP727" s="7"/>
     </row>
-    <row r="728" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A728" s="81">
         <v>46234</v>
       </c>
@@ -66915,7 +66914,7 @@
       <c r="AL729" s="102"/>
       <c r="AP729" s="7"/>
     </row>
-    <row r="730" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A730" s="120">
         <v>46234</v>
       </c>
@@ -66983,7 +66982,7 @@
       <c r="AL730" s="102"/>
       <c r="AP730" s="7"/>
     </row>
-    <row r="731" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A731" s="81">
         <v>46234</v>
       </c>
@@ -67049,7 +67048,7 @@
       <c r="AL731" s="102"/>
       <c r="AP731" s="7"/>
     </row>
-    <row r="732" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A732" s="81">
         <v>46234</v>
       </c>
@@ -67111,7 +67110,7 @@
       <c r="AL732" s="102"/>
       <c r="AP732" s="7"/>
     </row>
-    <row r="733" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A733" s="81">
         <v>46234</v>
       </c>
@@ -67177,7 +67176,7 @@
       <c r="AL733" s="102"/>
       <c r="AP733" s="7"/>
     </row>
-    <row r="734" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A734" s="109">
         <v>46234</v>
       </c>
@@ -67243,7 +67242,7 @@
       <c r="AL734" s="102"/>
       <c r="AP734" s="7"/>
     </row>
-    <row r="735" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A735" s="109">
         <v>46234</v>
       </c>
@@ -67307,7 +67306,7 @@
       <c r="AL735" s="102"/>
       <c r="AP735" s="7"/>
     </row>
-    <row r="736" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A736" s="109">
         <v>46234</v>
       </c>
@@ -67375,7 +67374,7 @@
       <c r="AL736" s="102"/>
       <c r="AP736" s="7"/>
     </row>
-    <row r="737" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A737" s="109">
         <v>46234</v>
       </c>
@@ -67441,7 +67440,7 @@
       <c r="AL737" s="102"/>
       <c r="AP737" s="7"/>
     </row>
-    <row r="738" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A738" s="109">
         <v>46234</v>
       </c>
@@ -67505,7 +67504,7 @@
       <c r="AL738" s="102"/>
       <c r="AP738" s="7"/>
     </row>
-    <row r="739" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A739" s="109">
         <v>46234</v>
       </c>
@@ -67575,7 +67574,7 @@
       <c r="AL739" s="102"/>
       <c r="AP739" s="7"/>
     </row>
-    <row r="740" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A740" s="112">
         <v>46234</v>
       </c>
@@ -67641,7 +67640,7 @@
       <c r="AL740" s="127"/>
       <c r="AP740" s="7"/>
     </row>
-    <row r="741" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A741" s="109">
         <v>46234</v>
       </c>
@@ -67713,7 +67712,7 @@
       <c r="AL741" s="102"/>
       <c r="AP741" s="7"/>
     </row>
-    <row r="742" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A742" s="109">
         <v>46234</v>
       </c>
@@ -68011,7 +68010,7 @@
       </c>
       <c r="AP744" s="7"/>
     </row>
-    <row r="745" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A745" s="90"/>
       <c r="B745" s="72"/>
       <c r="C745" s="90"/>
@@ -68061,7 +68060,7 @@
       <c r="AL745" s="90"/>
       <c r="AP745" s="7"/>
     </row>
-    <row r="746" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A746" s="90"/>
       <c r="B746" s="72"/>
       <c r="C746" s="90"/>
@@ -68132,7 +68131,7 @@
       <c r="AL746" s="90"/>
       <c r="AP746" s="7"/>
     </row>
-    <row r="747" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A747" s="90"/>
       <c r="B747" s="72"/>
       <c r="C747" s="90"/>
@@ -68175,7 +68174,7 @@
       <c r="AL747" s="90"/>
       <c r="AP747" s="7"/>
     </row>
-    <row r="748" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:42" x14ac:dyDescent="0.35">
       <c r="B748" s="76"/>
       <c r="D748" s="77"/>
       <c r="J748" s="132" t="s">
@@ -68217,7 +68216,7 @@
       <c r="AB748" s="7"/>
       <c r="AF748"/>
     </row>
-    <row r="749" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:42" x14ac:dyDescent="0.35">
       <c r="B749" s="73"/>
       <c r="D749" s="117"/>
       <c r="I749" s="42" t="s">
@@ -69397,11 +69396,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP749" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="Shakoor"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="10" showButton="0"/>
     <filterColumn colId="11" showButton="0"/>
     <filterColumn colId="12" showButton="0"/>
@@ -69468,22 +69462,22 @@
   <sheetData>
     <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="4:8" ht="22.5" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="145"/>
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D6" s="10" t="s">
@@ -70038,10 +70032,10 @@
       </c>
     </row>
     <row r="31" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C31" s="146" t="s">
+      <c r="C31" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="147"/>
+      <c r="D31" s="148"/>
       <c r="E31" s="37">
         <f>SUM(E24:E30)</f>
         <v>8000</v>
